--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,6 +932,1107 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121388879</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57504</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>512611</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6732496</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Den lät som talltitor låter på hösten</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121388880</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57720</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>512611</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6732496</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121401275</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56563</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>512405</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6732680</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121399884</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97035</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>512569</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6732458</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121400201</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90983</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>658</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>512488</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6732674</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121388881</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57720</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>512593</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6732493</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Den lät som kungsfåglar låter på hösten.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121400189</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90983</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>658</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>512462</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6732670</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>stort granvindfälle</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121399873</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56563</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>512569</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6732458</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121401513</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>512544</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6732488</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121178299</v>
+        <v>121179502</v>
       </c>
       <c r="B2" t="n">
-        <v>90687</v>
+        <v>97035</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512460</v>
+        <v>512532</v>
       </c>
       <c r="R2" t="n">
-        <v>6732491</v>
+        <v>6732598</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -761,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,12 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>uppskattat antal dm²</t>
+          <t>10x3 m, uppskattat område</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121179502</v>
+        <v>121178299</v>
       </c>
       <c r="B3" t="n">
-        <v>97025</v>
+        <v>90697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,39 +817,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512532</v>
+        <v>512460</v>
       </c>
       <c r="R3" t="n">
-        <v>6732598</v>
+        <v>6732491</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>10x3 m, uppskattat område</t>
+          <t>uppskattat antal dm²</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388879</v>
+        <v>121399884</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>97035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,35 +946,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -982,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512611</v>
+        <v>512569</v>
       </c>
       <c r="R4" t="n">
-        <v>6732496</v>
+        <v>6732458</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1012,27 +1008,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Den lät som talltitor låter på hösten</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,6 +1032,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1179,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121401275</v>
+        <v>121400189</v>
       </c>
       <c r="B6" t="n">
-        <v>56563</v>
+        <v>90983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,35 +1183,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1227,13 +1218,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512405</v>
+        <v>512462</v>
       </c>
       <c r="R6" t="n">
-        <v>6732680</v>
+        <v>6732670</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1253,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1263,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
+          <t>stort granvindfälle</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,6 +1277,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1304,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121399884</v>
+        <v>121399873</v>
       </c>
       <c r="B7" t="n">
-        <v>97035</v>
+        <v>56563</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,27 +1312,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1383,7 +1379,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1393,7 +1389,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,7 +1398,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1421,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121400201</v>
+        <v>121388881</v>
       </c>
       <c r="B8" t="n">
-        <v>90983</v>
+        <v>57720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,34 +1428,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1468,13 +1464,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512488</v>
+        <v>512593</v>
       </c>
       <c r="R8" t="n">
-        <v>6732674</v>
+        <v>6732493</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,22 +1494,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Den lät som kungsfåglar låter på hösten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,7 +1523,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121388881</v>
+        <v>121401275</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>56563</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1557,21 +1557,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1579,7 +1579,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512593</v>
+        <v>512405</v>
       </c>
       <c r="R9" t="n">
-        <v>6732493</v>
+        <v>6732680</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,27 +1619,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Den lät som kungsfåglar låter på hösten.</t>
+          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1666,10 +1666,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121400189</v>
+        <v>121388879</v>
       </c>
       <c r="B10" t="n">
-        <v>90983</v>
+        <v>57504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1682,30 +1682,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1713,13 +1714,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512462</v>
+        <v>512611</v>
       </c>
       <c r="R10" t="n">
-        <v>6732670</v>
+        <v>6732496</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1743,27 +1744,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>stort granvindfälle</t>
+          <t>Den lät som talltitor låter på hösten</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,7 +1773,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1791,10 +1791,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121399873</v>
+        <v>121400201</v>
       </c>
       <c r="B11" t="n">
-        <v>56563</v>
+        <v>90983</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1803,35 +1803,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1839,13 +1838,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512569</v>
+        <v>512488</v>
       </c>
       <c r="R11" t="n">
-        <v>6732458</v>
+        <v>6732674</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1869,22 +1868,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,6 +1892,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2033,6 +2033,3226 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121423753</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91137</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>512549</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6732434</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121423742</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>512550</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6732432</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121423768</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91380</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>512478</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6732507</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121423790</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100347</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>512628</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6732540</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121423733</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>512568</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6732462</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121423785</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>512534</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6732503</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121426321</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56555</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>512598</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6732619</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121425051</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100347</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>512639</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6732526</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121423791</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100347</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>512638</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6732516</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121423765</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56555</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>512463</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6732461</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121425434</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>512583</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6732462</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gammla hack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121425050</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100347</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>512609</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6732541</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121425562</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>512478</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6732505</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121423772</v>
+      </c>
+      <c r="B26" t="n">
+        <v>90715</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>512535</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6732497</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121425052</v>
+      </c>
+      <c r="B27" t="n">
+        <v>100347</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>512626</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6732514</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121425292</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>512561</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6732464</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>varav ca 20 med blomställning</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121426318</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97037</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>512584</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6732486</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121423792</v>
+      </c>
+      <c r="B30" t="n">
+        <v>100347</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>512628</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6732517</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121423734</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>512545</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6732494</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121423787</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>512531</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6732485</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121423764</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>512489</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6732468</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121425291</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97035</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>512552</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6732510</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121423769</v>
+      </c>
+      <c r="B35" t="n">
+        <v>90711</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>512493</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6732572</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På syllstock av gammal husruin</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121423766</v>
+      </c>
+      <c r="B36" t="n">
+        <v>90910</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1618</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Hängticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Postia ceriflua</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>512622</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6732491</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121425154</v>
+      </c>
+      <c r="B37" t="n">
+        <v>90715</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>512529</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6732493</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121423754</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90983</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>658</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>512475</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6732663</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121423755</v>
+      </c>
+      <c r="B39" t="n">
+        <v>90983</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>658</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>512555</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6732434</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121423741</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>512543</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6732433</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>121423744</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>512454</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6732500</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121423740</v>
+      </c>
+      <c r="B42" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>512413</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6732688</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2884,10 +2884,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121423791</v>
+        <v>121425434</v>
       </c>
       <c r="B21" t="n">
-        <v>100347</v>
+        <v>57367</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2896,41 +2896,53 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512638</v>
+        <v>512583</v>
       </c>
       <c r="R21" t="n">
-        <v>6732516</v>
+        <v>6732462</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2960,6 +2972,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,22 +2991,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121423765</v>
+        <v>121425050</v>
       </c>
       <c r="B22" t="n">
-        <v>56555</v>
+        <v>100347</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2998,49 +3015,45 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512463</v>
+        <v>512609</v>
       </c>
       <c r="R22" t="n">
-        <v>6732461</v>
+        <v>6732541</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3067,39 +3080,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121425434</v>
+        <v>121423791</v>
       </c>
       <c r="B23" t="n">
-        <v>57367</v>
+        <v>100347</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3108,53 +3132,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512583</v>
+        <v>512638</v>
       </c>
       <c r="R23" t="n">
-        <v>6732462</v>
+        <v>6732516</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3184,11 +3196,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3203,22 +3210,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121425050</v>
+        <v>121423765</v>
       </c>
       <c r="B24" t="n">
-        <v>100347</v>
+        <v>56555</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3227,45 +3234,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512609</v>
+        <v>512463</v>
       </c>
       <c r="R24" t="n">
-        <v>6732541</v>
+        <v>6732461</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3292,40 +3303,29 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3781,10 +3781,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121426318</v>
+        <v>121423792</v>
       </c>
       <c r="B29" t="n">
-        <v>97037</v>
+        <v>100347</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3797,37 +3797,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>224363</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512584</v>
+        <v>512628</v>
       </c>
       <c r="R29" t="n">
-        <v>6732486</v>
+        <v>6732517</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3854,50 +3854,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121423792</v>
+        <v>121423734</v>
       </c>
       <c r="B30" t="n">
-        <v>100347</v>
+        <v>90662</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3910,21 +3899,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3934,10 +3923,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512628</v>
+        <v>512545</v>
       </c>
       <c r="R30" t="n">
-        <v>6732517</v>
+        <v>6732494</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3996,10 +3985,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121423734</v>
+        <v>121426318</v>
       </c>
       <c r="B31" t="n">
-        <v>90662</v>
+        <v>97037</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4012,37 +4001,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>224363</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512545</v>
+        <v>512584</v>
       </c>
       <c r="R31" t="n">
-        <v>6732494</v>
+        <v>6732486</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4069,39 +4058,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121423787</v>
+        <v>121423764</v>
       </c>
       <c r="B32" t="n">
-        <v>5169</v>
+        <v>98081</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4110,38 +4110,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512531</v>
+        <v>512489</v>
       </c>
       <c r="R32" t="n">
-        <v>6732485</v>
+        <v>6732468</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4200,10 +4209,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121423764</v>
+        <v>121423787</v>
       </c>
       <c r="B33" t="n">
-        <v>98081</v>
+        <v>5169</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4212,47 +4221,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512489</v>
+        <v>512531</v>
       </c>
       <c r="R33" t="n">
-        <v>6732468</v>
+        <v>6732485</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4311,10 +4311,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121425291</v>
+        <v>121423769</v>
       </c>
       <c r="B34" t="n">
-        <v>97035</v>
+        <v>90711</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4323,25 +4323,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4351,10 +4351,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512552</v>
+        <v>512493</v>
       </c>
       <c r="R34" t="n">
-        <v>6732510</v>
+        <v>6732572</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4389,6 +4389,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På syllstock av gammal husruin</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4401,22 +4406,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121423769</v>
+        <v>121425291</v>
       </c>
       <c r="B35" t="n">
-        <v>90711</v>
+        <v>97035</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4425,25 +4430,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4453,10 +4458,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512493</v>
+        <v>512552</v>
       </c>
       <c r="R35" t="n">
-        <v>6732572</v>
+        <v>6732510</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4491,11 +4496,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På syllstock av gammal husruin</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4508,12 +4508,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4745,7 +4745,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121423754</v>
+        <v>121423755</v>
       </c>
       <c r="B38" t="n">
         <v>90983</v>
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>512475</v>
+        <v>512555</v>
       </c>
       <c r="R38" t="n">
-        <v>6732663</v>
+        <v>6732434</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121423755</v>
+        <v>121423754</v>
       </c>
       <c r="B39" t="n">
         <v>90983</v>
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>512555</v>
+        <v>512475</v>
       </c>
       <c r="R39" t="n">
-        <v>6732434</v>
+        <v>6732663</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5253,6 +5253,130 @@
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>121426854</v>
+      </c>
+      <c r="B43" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>512582</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6732490</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Beke Regelin, Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121399884</v>
+        <v>121388881</v>
       </c>
       <c r="B4" t="n">
-        <v>97035</v>
+        <v>57720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,27 +950,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -978,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512569</v>
+        <v>512593</v>
       </c>
       <c r="R4" t="n">
-        <v>6732458</v>
+        <v>6732493</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1008,22 +1012,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Den lät som kungsfåglar låter på hösten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1041,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1051,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388880</v>
+        <v>121400201</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,35 +1071,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1099,13 +1106,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512611</v>
+        <v>512488</v>
       </c>
       <c r="R5" t="n">
-        <v>6732496</v>
+        <v>6732674</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1136,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,6 +1160,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1171,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121400189</v>
+        <v>121401275</v>
       </c>
       <c r="B6" t="n">
-        <v>90983</v>
+        <v>56563</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,34 +1191,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1218,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512462</v>
+        <v>512405</v>
       </c>
       <c r="R6" t="n">
-        <v>6732670</v>
+        <v>6732680</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1253,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1263,12 +1272,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>stort granvindfälle</t>
+          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,7 +1286,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1296,10 +1304,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121399873</v>
+        <v>121388880</v>
       </c>
       <c r="B7" t="n">
-        <v>56563</v>
+        <v>57720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1320,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1334,7 +1342,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1344,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512569</v>
+        <v>512611</v>
       </c>
       <c r="R7" t="n">
-        <v>6732458</v>
+        <v>6732496</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1374,22 +1382,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388881</v>
+        <v>121388879</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>57504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,25 +1436,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1464,10 +1472,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512593</v>
+        <v>512611</v>
       </c>
       <c r="R8" t="n">
-        <v>6732493</v>
+        <v>6732496</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1499,7 +1507,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1509,12 +1517,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Den lät som kungsfåglar låter på hösten.</t>
+          <t>Den lät som talltitor låter på hösten</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,7 +1549,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121401275</v>
+        <v>121399873</v>
       </c>
       <c r="B9" t="n">
         <v>56563</v>
@@ -1589,13 +1597,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512405</v>
+        <v>512569</v>
       </c>
       <c r="R9" t="n">
-        <v>6732680</v>
+        <v>6732458</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1624,7 +1632,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1634,12 +1642,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1666,10 +1669,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388879</v>
+        <v>121400189</v>
       </c>
       <c r="B10" t="n">
-        <v>57504</v>
+        <v>90983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1682,31 +1685,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1714,13 +1716,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512611</v>
+        <v>512462</v>
       </c>
       <c r="R10" t="n">
-        <v>6732496</v>
+        <v>6732670</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1744,27 +1746,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Den lät som talltitor låter på hösten</t>
+          <t>stort granvindfälle</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,6 +1775,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1791,10 +1794,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121400201</v>
+        <v>121399884</v>
       </c>
       <c r="B11" t="n">
-        <v>90983</v>
+        <v>97035</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1803,34 +1806,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512488</v>
+        <v>512569</v>
       </c>
       <c r="R11" t="n">
-        <v>6732674</v>
+        <v>6732458</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1868,22 +1868,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2035,10 +2035,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121423753</v>
+        <v>121423742</v>
       </c>
       <c r="B13" t="n">
-        <v>91137</v>
+        <v>90697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2047,25 +2047,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512549</v>
+        <v>512550</v>
       </c>
       <c r="R13" t="n">
-        <v>6732434</v>
+        <v>6732432</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2137,10 +2137,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121423742</v>
+        <v>121425050</v>
       </c>
       <c r="B14" t="n">
-        <v>90697</v>
+        <v>100347</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2149,41 +2149,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512550</v>
+        <v>512609</v>
       </c>
       <c r="R14" t="n">
-        <v>6732432</v>
+        <v>6732541</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,39 +2214,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121423768</v>
+        <v>121423741</v>
       </c>
       <c r="B15" t="n">
-        <v>91380</v>
+        <v>90697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,25 +2266,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2279,10 +2294,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512478</v>
+        <v>512543</v>
       </c>
       <c r="R15" t="n">
-        <v>6732507</v>
+        <v>6732433</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2341,10 +2356,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121423790</v>
+        <v>121423765</v>
       </c>
       <c r="B16" t="n">
-        <v>100347</v>
+        <v>56555</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2353,38 +2368,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512628</v>
+        <v>512463</v>
       </c>
       <c r="R16" t="n">
-        <v>6732540</v>
+        <v>6732461</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2443,10 +2466,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121423733</v>
+        <v>121425562</v>
       </c>
       <c r="B17" t="n">
-        <v>90662</v>
+        <v>90697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2455,41 +2478,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512568</v>
+        <v>512478</v>
       </c>
       <c r="R17" t="n">
-        <v>6732462</v>
+        <v>6732505</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2527,28 +2561,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121423785</v>
+        <v>121423772</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2561,21 +2596,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2585,10 +2620,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512534</v>
+        <v>512535</v>
       </c>
       <c r="R18" t="n">
-        <v>6732503</v>
+        <v>6732497</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2647,10 +2682,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121426321</v>
+        <v>121423753</v>
       </c>
       <c r="B19" t="n">
-        <v>56555</v>
+        <v>91137</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2659,49 +2694,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512598</v>
+        <v>512549</v>
       </c>
       <c r="R19" t="n">
-        <v>6732619</v>
+        <v>6732434</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2728,19 +2755,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,12 +2772,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2884,10 +2901,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121425434</v>
+        <v>121426318</v>
       </c>
       <c r="B21" t="n">
-        <v>57367</v>
+        <v>97037</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2896,53 +2913,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>224363</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512583</v>
+        <v>512584</v>
       </c>
       <c r="R21" t="n">
-        <v>6732462</v>
+        <v>6732486</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2969,14 +2974,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gammla hack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2985,25 +2995,26 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121425050</v>
+        <v>121423790</v>
       </c>
       <c r="B22" t="n">
         <v>100347</v>
@@ -3037,23 +3048,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512609</v>
+        <v>512628</v>
       </c>
       <c r="R22" t="n">
-        <v>6732541</v>
+        <v>6732540</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3080,50 +3087,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121423791</v>
+        <v>121423769</v>
       </c>
       <c r="B23" t="n">
-        <v>100347</v>
+        <v>90711</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3132,25 +3128,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3160,10 +3156,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512638</v>
+        <v>512493</v>
       </c>
       <c r="R23" t="n">
-        <v>6732516</v>
+        <v>6732572</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3196,6 +3192,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På syllstock av gammal husruin</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3222,10 +3223,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121423765</v>
+        <v>121425052</v>
       </c>
       <c r="B24" t="n">
-        <v>56555</v>
+        <v>100347</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3234,49 +3235,45 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512463</v>
+        <v>512626</v>
       </c>
       <c r="R24" t="n">
-        <v>6732461</v>
+        <v>6732514</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3303,39 +3300,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121425562</v>
+        <v>121423787</v>
       </c>
       <c r="B25" t="n">
-        <v>90697</v>
+        <v>5169</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3344,52 +3352,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512478</v>
+        <v>512531</v>
       </c>
       <c r="R25" t="n">
-        <v>6732505</v>
+        <v>6732485</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3427,29 +3424,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121423772</v>
+        <v>121423785</v>
       </c>
       <c r="B26" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3462,21 +3458,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3486,10 +3482,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512535</v>
+        <v>512534</v>
       </c>
       <c r="R26" t="n">
-        <v>6732497</v>
+        <v>6732503</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3548,10 +3544,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121425052</v>
+        <v>121423733</v>
       </c>
       <c r="B27" t="n">
-        <v>100347</v>
+        <v>90662</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3564,41 +3560,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512626</v>
+        <v>512568</v>
       </c>
       <c r="R27" t="n">
-        <v>6732514</v>
+        <v>6732462</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3625,50 +3617,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås, Evalena Sköld, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121425292</v>
+        <v>121425434</v>
       </c>
       <c r="B28" t="n">
-        <v>98081</v>
+        <v>57367</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3677,49 +3658,53 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512561</v>
+        <v>512583</v>
       </c>
       <c r="R28" t="n">
-        <v>6732464</v>
+        <v>6732462</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3753,7 +3738,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>varav ca 20 med blomställning</t>
+          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3762,29 +3747,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121423792</v>
+        <v>121423740</v>
       </c>
       <c r="B29" t="n">
-        <v>100347</v>
+        <v>90697</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3793,25 +3777,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3821,10 +3805,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512628</v>
+        <v>512413</v>
       </c>
       <c r="R29" t="n">
-        <v>6732517</v>
+        <v>6732688</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3883,10 +3867,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121423734</v>
+        <v>121423744</v>
       </c>
       <c r="B30" t="n">
-        <v>90662</v>
+        <v>90697</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3895,25 +3879,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3923,10 +3907,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512545</v>
+        <v>512454</v>
       </c>
       <c r="R30" t="n">
-        <v>6732494</v>
+        <v>6732500</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,10 +3969,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121426318</v>
+        <v>121423764</v>
       </c>
       <c r="B31" t="n">
-        <v>97037</v>
+        <v>98081</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3997,41 +3981,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>224363</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512584</v>
+        <v>512489</v>
       </c>
       <c r="R31" t="n">
-        <v>6732486</v>
+        <v>6732468</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4058,47 +4051,36 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121423764</v>
+        <v>121425292</v>
       </c>
       <c r="B32" t="n">
         <v>98081</v>
@@ -4133,24 +4115,23 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512489</v>
+        <v>512561</v>
       </c>
       <c r="R32" t="n">
-        <v>6732468</v>
+        <v>6732464</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4185,34 +4166,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>varav ca 20 med blomställning</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin, Irina Röjås</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121423787</v>
+        <v>121426321</v>
       </c>
       <c r="B33" t="n">
-        <v>5169</v>
+        <v>56555</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4221,41 +4208,49 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512531</v>
+        <v>512598</v>
       </c>
       <c r="R33" t="n">
-        <v>6732485</v>
+        <v>6732619</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4282,9 +4277,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4299,22 +4304,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121423769</v>
+        <v>121423792</v>
       </c>
       <c r="B34" t="n">
-        <v>90711</v>
+        <v>100347</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4323,25 +4328,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4351,10 +4356,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512493</v>
+        <v>512628</v>
       </c>
       <c r="R34" t="n">
-        <v>6732572</v>
+        <v>6732517</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4387,11 +4392,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På syllstock av gammal husruin</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121425291</v>
+        <v>121423755</v>
       </c>
       <c r="B35" t="n">
-        <v>97035</v>
+        <v>90983</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4430,25 +4430,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512552</v>
+        <v>512555</v>
       </c>
       <c r="R35" t="n">
-        <v>6732510</v>
+        <v>6732434</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4508,22 +4508,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121423766</v>
+        <v>121425154</v>
       </c>
       <c r="B36" t="n">
-        <v>90910</v>
+        <v>90715</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4532,44 +4532,52 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1618</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>512622</v>
+        <v>512529</v>
       </c>
       <c r="R36" t="n">
-        <v>6732491</v>
+        <v>6732493</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4599,6 +4607,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4614,22 +4627,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121425154</v>
+        <v>121423768</v>
       </c>
       <c r="B37" t="n">
-        <v>90715</v>
+        <v>91380</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4638,52 +4651,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>512529</v>
+        <v>512478</v>
       </c>
       <c r="R37" t="n">
-        <v>6732493</v>
+        <v>6732507</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4715,40 +4717,34 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121423755</v>
+        <v>121423791</v>
       </c>
       <c r="B38" t="n">
-        <v>90983</v>
+        <v>100347</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4757,25 +4753,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4785,10 +4781,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>512555</v>
+        <v>512638</v>
       </c>
       <c r="R38" t="n">
-        <v>6732434</v>
+        <v>6732516</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4847,10 +4843,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121423754</v>
+        <v>121425291</v>
       </c>
       <c r="B39" t="n">
-        <v>90983</v>
+        <v>97035</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4859,25 +4855,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4887,10 +4883,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>512475</v>
+        <v>512552</v>
       </c>
       <c r="R39" t="n">
-        <v>6732663</v>
+        <v>6732510</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4937,22 +4933,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121423741</v>
+        <v>121423734</v>
       </c>
       <c r="B40" t="n">
-        <v>90697</v>
+        <v>90662</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4961,25 +4957,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4989,10 +4985,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512543</v>
+        <v>512545</v>
       </c>
       <c r="R40" t="n">
-        <v>6732433</v>
+        <v>6732494</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5044,17 +5040,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin, Irina Röjås, Evalena Sköld, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121423744</v>
+        <v>121423766</v>
       </c>
       <c r="B41" t="n">
-        <v>90697</v>
+        <v>90910</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5063,38 +5059,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>1618</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512454</v>
+        <v>512622</v>
       </c>
       <c r="R41" t="n">
-        <v>6732500</v>
+        <v>6732491</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5135,6 +5134,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5153,10 +5153,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121423740</v>
+        <v>121423754</v>
       </c>
       <c r="B42" t="n">
-        <v>90697</v>
+        <v>90983</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512413</v>
+        <v>512475</v>
       </c>
       <c r="R42" t="n">
-        <v>6732688</v>
+        <v>6732663</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -1549,10 +1549,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121399873</v>
+        <v>121400189</v>
       </c>
       <c r="B9" t="n">
-        <v>56563</v>
+        <v>90983</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1561,35 +1561,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1597,13 +1596,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512569</v>
+        <v>512462</v>
       </c>
       <c r="R9" t="n">
-        <v>6732458</v>
+        <v>6732670</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1632,7 +1631,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1642,7 +1641,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>stort granvindfälle</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1651,6 +1655,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1669,10 +1674,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121400189</v>
+        <v>121399873</v>
       </c>
       <c r="B10" t="n">
-        <v>90983</v>
+        <v>56563</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1681,34 +1686,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1716,13 +1722,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512462</v>
+        <v>512569</v>
       </c>
       <c r="R10" t="n">
-        <v>6732670</v>
+        <v>6732458</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1751,7 +1757,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1761,12 +1767,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>stort granvindfälle</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,7 +1776,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121423753</v>
+        <v>121426318</v>
       </c>
       <c r="B19" t="n">
-        <v>91137</v>
+        <v>97037</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2694,41 +2694,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>224363</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512549</v>
+        <v>512584</v>
       </c>
       <c r="R19" t="n">
-        <v>6732434</v>
+        <v>6732486</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2755,29 +2755,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2901,10 +2912,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121426318</v>
+        <v>121423753</v>
       </c>
       <c r="B21" t="n">
-        <v>97037</v>
+        <v>91137</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2913,41 +2924,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>224363</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512584</v>
+        <v>512549</v>
       </c>
       <c r="R21" t="n">
-        <v>6732486</v>
+        <v>6732434</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2974,40 +2985,29 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121423787</v>
+        <v>121423785</v>
       </c>
       <c r="B25" t="n">
-        <v>5169</v>
+        <v>78601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512531</v>
+        <v>512534</v>
       </c>
       <c r="R25" t="n">
-        <v>6732485</v>
+        <v>6732503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121423785</v>
+        <v>121423787</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
+        <v>5169</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3454,25 +3454,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512534</v>
+        <v>512531</v>
       </c>
       <c r="R26" t="n">
-        <v>6732503</v>
+        <v>6732485</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121179502</v>
+        <v>121178299</v>
       </c>
       <c r="B2" t="n">
-        <v>97035</v>
+        <v>90709</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512532</v>
+        <v>512460</v>
       </c>
       <c r="R2" t="n">
-        <v>6732598</v>
+        <v>6732491</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -762,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +771,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>10x3 m, uppskattat område</t>
+          <t>uppskattat antal dm²</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121178299</v>
+        <v>121179502</v>
       </c>
       <c r="B3" t="n">
-        <v>90697</v>
+        <v>97048</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,38 +816,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512460</v>
+        <v>512532</v>
       </c>
       <c r="R3" t="n">
-        <v>6732491</v>
+        <v>6732598</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>uppskattat antal dm²</t>
+          <t>10x3 m, uppskattat område</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388881</v>
+        <v>121399873</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>56563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,21 +950,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -972,7 +972,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512593</v>
+        <v>512569</v>
       </c>
       <c r="R4" t="n">
-        <v>6732493</v>
+        <v>6732458</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1012,27 +1012,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Den lät som kungsfåglar låter på hösten.</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,7 +1057,7 @@
         <v>121400201</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>90995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1179,10 +1174,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121401275</v>
+        <v>121388881</v>
       </c>
       <c r="B6" t="n">
-        <v>56563</v>
+        <v>57720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,21 +1190,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1217,7 +1212,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1227,13 +1222,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512405</v>
+        <v>512593</v>
       </c>
       <c r="R6" t="n">
-        <v>6732680</v>
+        <v>6732493</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1257,27 +1252,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
+          <t>Den lät som kungsfåglar låter på hösten.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1304,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388880</v>
+        <v>121400189</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>90995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,35 +1311,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1352,13 +1346,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512611</v>
+        <v>512462</v>
       </c>
       <c r="R7" t="n">
-        <v>6732496</v>
+        <v>6732670</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1382,22 +1376,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>stort granvindfälle</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,6 +1405,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1549,10 +1549,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121400189</v>
+        <v>121401275</v>
       </c>
       <c r="B9" t="n">
-        <v>90983</v>
+        <v>56563</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1561,34 +1561,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1596,13 +1597,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512462</v>
+        <v>512405</v>
       </c>
       <c r="R9" t="n">
-        <v>6732670</v>
+        <v>6732680</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1631,7 +1632,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1641,12 +1642,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>stort granvindfälle</t>
+          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1655,7 +1656,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121399873</v>
+        <v>121388880</v>
       </c>
       <c r="B10" t="n">
-        <v>56563</v>
+        <v>57720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,21 +1690,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1712,7 +1712,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512569</v>
+        <v>512611</v>
       </c>
       <c r="R10" t="n">
-        <v>6732458</v>
+        <v>6732496</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1752,22 +1752,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1797,7 +1797,7 @@
         <v>121399884</v>
       </c>
       <c r="B11" t="n">
-        <v>97035</v>
+        <v>97048</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>121401513</v>
       </c>
       <c r="B12" t="n">
-        <v>90662</v>
+        <v>90674</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2035,10 +2035,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121423742</v>
+        <v>121425562</v>
       </c>
       <c r="B13" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2068,20 +2068,31 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512550</v>
+        <v>512478</v>
       </c>
       <c r="R13" t="n">
-        <v>6732432</v>
+        <v>6732505</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2119,28 +2130,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121425050</v>
+        <v>121423755</v>
       </c>
       <c r="B14" t="n">
-        <v>100347</v>
+        <v>90995</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2149,45 +2161,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512609</v>
+        <v>512555</v>
       </c>
       <c r="R14" t="n">
-        <v>6732541</v>
+        <v>6732434</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2214,50 +2222,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121423741</v>
+        <v>121423744</v>
       </c>
       <c r="B15" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2294,10 +2291,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512543</v>
+        <v>512454</v>
       </c>
       <c r="R15" t="n">
-        <v>6732433</v>
+        <v>6732500</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2356,10 +2353,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121423765</v>
+        <v>121425291</v>
       </c>
       <c r="B16" t="n">
-        <v>56555</v>
+        <v>97048</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2368,46 +2365,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512463</v>
+        <v>512552</v>
       </c>
       <c r="R16" t="n">
-        <v>6732461</v>
+        <v>6732510</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2454,22 +2443,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121425562</v>
+        <v>121425051</v>
       </c>
       <c r="B17" t="n">
-        <v>90697</v>
+        <v>100360</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2478,52 +2467,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512478</v>
+        <v>512639</v>
       </c>
       <c r="R17" t="n">
-        <v>6732505</v>
+        <v>6732526</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2550,9 +2532,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2568,22 +2560,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121423772</v>
+        <v>121423791</v>
       </c>
       <c r="B18" t="n">
-        <v>90715</v>
+        <v>100360</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2592,25 +2584,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2620,10 +2612,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512535</v>
+        <v>512638</v>
       </c>
       <c r="R18" t="n">
-        <v>6732497</v>
+        <v>6732516</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2682,10 +2674,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121426318</v>
+        <v>121423742</v>
       </c>
       <c r="B19" t="n">
-        <v>97037</v>
+        <v>90709</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2694,41 +2686,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>224363</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512584</v>
+        <v>512550</v>
       </c>
       <c r="R19" t="n">
-        <v>6732486</v>
+        <v>6732432</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2755,50 +2747,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121425051</v>
+        <v>121423787</v>
       </c>
       <c r="B20" t="n">
-        <v>100347</v>
+        <v>5169</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2811,41 +2792,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512639</v>
+        <v>512531</v>
       </c>
       <c r="R20" t="n">
-        <v>6732526</v>
+        <v>6732485</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2872,50 +2849,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121423753</v>
+        <v>121425050</v>
       </c>
       <c r="B21" t="n">
-        <v>91137</v>
+        <v>100360</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2924,41 +2890,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512549</v>
+        <v>512609</v>
       </c>
       <c r="R21" t="n">
-        <v>6732434</v>
+        <v>6732541</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2985,39 +2955,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121423790</v>
+        <v>121423740</v>
       </c>
       <c r="B22" t="n">
-        <v>100347</v>
+        <v>90709</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3026,25 +3007,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3035,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512628</v>
+        <v>512413</v>
       </c>
       <c r="R22" t="n">
-        <v>6732540</v>
+        <v>6732688</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3116,10 +3097,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121423769</v>
+        <v>121423753</v>
       </c>
       <c r="B23" t="n">
-        <v>90711</v>
+        <v>91149</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3128,25 +3109,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3156,10 +3137,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512493</v>
+        <v>512549</v>
       </c>
       <c r="R23" t="n">
-        <v>6732572</v>
+        <v>6732434</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3192,11 +3173,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På syllstock av gammal husruin</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3223,10 +3199,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121425052</v>
+        <v>121423792</v>
       </c>
       <c r="B24" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3257,23 +3233,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512626</v>
+        <v>512628</v>
       </c>
       <c r="R24" t="n">
-        <v>6732514</v>
+        <v>6732517</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3300,50 +3272,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121423785</v>
+        <v>121423766</v>
       </c>
       <c r="B25" t="n">
-        <v>78601</v>
+        <v>90922</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3352,38 +3313,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1618</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512534</v>
+        <v>512622</v>
       </c>
       <c r="R25" t="n">
-        <v>6732503</v>
+        <v>6732491</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3424,6 +3388,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3442,10 +3407,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121423787</v>
+        <v>121423764</v>
       </c>
       <c r="B26" t="n">
-        <v>5169</v>
+        <v>98094</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3454,38 +3419,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512531</v>
+        <v>512489</v>
       </c>
       <c r="R26" t="n">
-        <v>6732485</v>
+        <v>6732468</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3544,10 +3518,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121423733</v>
+        <v>121423769</v>
       </c>
       <c r="B27" t="n">
-        <v>90662</v>
+        <v>90723</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,25 +3530,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3584,10 +3558,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512568</v>
+        <v>512493</v>
       </c>
       <c r="R27" t="n">
-        <v>6732462</v>
+        <v>6732572</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3622,6 +3596,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På syllstock av gammal husruin</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3639,17 +3618,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Irina Röjås, Evalena Sköld, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121425434</v>
+        <v>121426321</v>
       </c>
       <c r="B28" t="n">
-        <v>57367</v>
+        <v>56555</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3662,16 +3641,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3679,32 +3658,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512583</v>
+        <v>512598</v>
       </c>
       <c r="R28" t="n">
-        <v>6732462</v>
+        <v>6732619</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3731,14 +3706,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gammla hack</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3753,22 +3733,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121423740</v>
+        <v>121425154</v>
       </c>
       <c r="B29" t="n">
-        <v>90697</v>
+        <v>90727</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3781,37 +3761,48 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512413</v>
+        <v>512529</v>
       </c>
       <c r="R29" t="n">
-        <v>6732688</v>
+        <v>6732493</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3843,34 +3834,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121423744</v>
+        <v>121425052</v>
       </c>
       <c r="B30" t="n">
-        <v>90697</v>
+        <v>100360</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3879,41 +3876,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512454</v>
+        <v>512626</v>
       </c>
       <c r="R30" t="n">
-        <v>6732500</v>
+        <v>6732514</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3940,39 +3941,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121423764</v>
+        <v>121423734</v>
       </c>
       <c r="B31" t="n">
-        <v>98081</v>
+        <v>90674</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3981,47 +3993,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512489</v>
+        <v>512545</v>
       </c>
       <c r="R31" t="n">
-        <v>6732468</v>
+        <v>6732494</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4080,10 +4083,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121425292</v>
+        <v>121423785</v>
       </c>
       <c r="B32" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4092,46 +4095,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512561</v>
+        <v>512534</v>
       </c>
       <c r="R32" t="n">
-        <v>6732464</v>
+        <v>6732503</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4166,40 +4161,34 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>varav ca 20 med blomställning</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121426321</v>
+        <v>121425434</v>
       </c>
       <c r="B33" t="n">
-        <v>56555</v>
+        <v>57367</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4212,16 +4201,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4229,28 +4218,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512598</v>
+        <v>512583</v>
       </c>
       <c r="R33" t="n">
-        <v>6732619</v>
+        <v>6732462</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4277,19 +4270,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:02</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4304,22 +4292,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121423792</v>
+        <v>121423768</v>
       </c>
       <c r="B34" t="n">
-        <v>100347</v>
+        <v>91392</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4332,21 +4320,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4356,10 +4344,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512628</v>
+        <v>512478</v>
       </c>
       <c r="R34" t="n">
-        <v>6732517</v>
+        <v>6732507</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4418,10 +4406,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121423755</v>
+        <v>121423733</v>
       </c>
       <c r="B35" t="n">
-        <v>90983</v>
+        <v>90674</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4430,25 +4418,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4458,10 +4446,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512555</v>
+        <v>512568</v>
       </c>
       <c r="R35" t="n">
-        <v>6732434</v>
+        <v>6732462</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4520,10 +4508,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121425154</v>
+        <v>121423790</v>
       </c>
       <c r="B36" t="n">
-        <v>90715</v>
+        <v>100360</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4532,52 +4520,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>512529</v>
+        <v>512628</v>
       </c>
       <c r="R36" t="n">
-        <v>6732493</v>
+        <v>6732540</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4609,40 +4586,34 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121423768</v>
+        <v>121423772</v>
       </c>
       <c r="B37" t="n">
-        <v>91380</v>
+        <v>90727</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4651,25 +4622,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4679,10 +4650,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>512478</v>
+        <v>512535</v>
       </c>
       <c r="R37" t="n">
-        <v>6732507</v>
+        <v>6732497</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4741,10 +4712,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121423791</v>
+        <v>121425292</v>
       </c>
       <c r="B38" t="n">
-        <v>100347</v>
+        <v>98094</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4753,38 +4724,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>512638</v>
+        <v>512561</v>
       </c>
       <c r="R38" t="n">
-        <v>6732516</v>
+        <v>6732464</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4819,34 +4798,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>varav ca 20 med blomställning</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin, Irina Röjås</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121425291</v>
+        <v>121423741</v>
       </c>
       <c r="B39" t="n">
-        <v>97035</v>
+        <v>90709</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4855,25 +4840,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4883,10 +4868,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>512552</v>
+        <v>512543</v>
       </c>
       <c r="R39" t="n">
-        <v>6732510</v>
+        <v>6732433</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4933,22 +4918,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121423734</v>
+        <v>121423765</v>
       </c>
       <c r="B40" t="n">
-        <v>90662</v>
+        <v>56555</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4957,38 +4942,46 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512545</v>
+        <v>512463</v>
       </c>
       <c r="R40" t="n">
-        <v>6732494</v>
+        <v>6732461</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5040,17 +5033,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås, Evalena Sköld, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121423766</v>
+        <v>121426318</v>
       </c>
       <c r="B41" t="n">
-        <v>90910</v>
+        <v>97050</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5059,44 +5052,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1618</v>
+        <v>224363</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512622</v>
+        <v>512584</v>
       </c>
       <c r="R41" t="n">
-        <v>6732491</v>
+        <v>6732486</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5123,9 +5113,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5141,12 +5141,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5156,7 +5156,7 @@
         <v>121423754</v>
       </c>
       <c r="B42" t="n">
-        <v>90983</v>
+        <v>90995</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>121426854</v>
       </c>
       <c r="B43" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121178299</v>
       </c>
       <c r="B2" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>121179502</v>
       </c>
       <c r="B3" t="n">
-        <v>97048</v>
+        <v>97049</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121399873</v>
+        <v>121401275</v>
       </c>
       <c r="B4" t="n">
         <v>56563</v>
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512569</v>
+        <v>512405</v>
       </c>
       <c r="R4" t="n">
-        <v>6732458</v>
+        <v>6732680</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +1027,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121400201</v>
+        <v>121388879</v>
       </c>
       <c r="B5" t="n">
-        <v>90995</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,30 +1075,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1101,13 +1107,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512488</v>
+        <v>512611</v>
       </c>
       <c r="R5" t="n">
-        <v>6732674</v>
+        <v>6732496</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,22 +1137,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Den lät som talltitor låter på hösten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1166,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1174,10 +1184,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388881</v>
+        <v>121400189</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>90996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,35 +1196,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1222,13 +1231,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512593</v>
+        <v>512462</v>
       </c>
       <c r="R6" t="n">
-        <v>6732493</v>
+        <v>6732670</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,27 +1261,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Den lät som kungsfåglar låter på hösten.</t>
+          <t>stort granvindfälle</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,6 +1290,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1299,10 +1309,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121400189</v>
+        <v>121388880</v>
       </c>
       <c r="B7" t="n">
-        <v>90995</v>
+        <v>57720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,34 +1321,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1346,13 +1357,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512462</v>
+        <v>512611</v>
       </c>
       <c r="R7" t="n">
-        <v>6732670</v>
+        <v>6732496</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,27 +1387,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>stort granvindfälle</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,7 +1411,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1424,10 +1429,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388879</v>
+        <v>121399884</v>
       </c>
       <c r="B8" t="n">
-        <v>57504</v>
+        <v>97049</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,35 +1441,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1472,10 +1473,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512611</v>
+        <v>512569</v>
       </c>
       <c r="R8" t="n">
-        <v>6732496</v>
+        <v>6732458</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1502,27 +1503,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Den lät som talltitor låter på hösten</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,6 +1527,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1549,7 +1546,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121401275</v>
+        <v>121399873</v>
       </c>
       <c r="B9" t="n">
         <v>56563</v>
@@ -1597,13 +1594,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512405</v>
+        <v>512569</v>
       </c>
       <c r="R9" t="n">
-        <v>6732680</v>
+        <v>6732458</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1632,7 +1629,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1642,12 +1639,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,7 +1666,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388880</v>
+        <v>121388881</v>
       </c>
       <c r="B10" t="n">
         <v>57720</v>
@@ -1722,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512611</v>
+        <v>512593</v>
       </c>
       <c r="R10" t="n">
-        <v>6732496</v>
+        <v>6732493</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1757,7 +1749,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1767,7 +1759,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Den lät som kungsfåglar låter på hösten.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1794,10 +1791,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121399884</v>
+        <v>121400201</v>
       </c>
       <c r="B11" t="n">
-        <v>97048</v>
+        <v>90996</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1806,31 +1803,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512569</v>
+        <v>512488</v>
       </c>
       <c r="R11" t="n">
-        <v>6732458</v>
+        <v>6732674</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1868,22 +1868,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1914,7 +1914,7 @@
         <v>121401513</v>
       </c>
       <c r="B12" t="n">
-        <v>90674</v>
+        <v>90675</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>121425562</v>
       </c>
       <c r="B13" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121423755</v>
+        <v>121423754</v>
       </c>
       <c r="B14" t="n">
-        <v>90995</v>
+        <v>90996</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512555</v>
+        <v>512475</v>
       </c>
       <c r="R14" t="n">
-        <v>6732434</v>
+        <v>6732663</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121423744</v>
+        <v>121423733</v>
       </c>
       <c r="B15" t="n">
-        <v>90709</v>
+        <v>90675</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2263,25 +2263,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512454</v>
+        <v>512568</v>
       </c>
       <c r="R15" t="n">
-        <v>6732500</v>
+        <v>6732462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121425291</v>
+        <v>121425154</v>
       </c>
       <c r="B16" t="n">
-        <v>97048</v>
+        <v>90728</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2365,41 +2365,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512552</v>
+        <v>512529</v>
       </c>
       <c r="R16" t="n">
-        <v>6732510</v>
+        <v>6732493</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2431,34 +2442,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121425051</v>
+        <v>121423742</v>
       </c>
       <c r="B17" t="n">
-        <v>100360</v>
+        <v>90710</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,45 +2484,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512639</v>
+        <v>512550</v>
       </c>
       <c r="R17" t="n">
-        <v>6732526</v>
+        <v>6732432</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2532,50 +2545,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121423791</v>
+        <v>121423740</v>
       </c>
       <c r="B18" t="n">
-        <v>100360</v>
+        <v>90710</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2584,25 +2586,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2612,10 +2614,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512638</v>
+        <v>512413</v>
       </c>
       <c r="R18" t="n">
-        <v>6732516</v>
+        <v>6732688</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2674,10 +2676,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121423742</v>
+        <v>121423741</v>
       </c>
       <c r="B19" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2714,10 +2716,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512550</v>
+        <v>512543</v>
       </c>
       <c r="R19" t="n">
-        <v>6732432</v>
+        <v>6732433</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2776,10 +2778,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121423787</v>
+        <v>121423768</v>
       </c>
       <c r="B20" t="n">
-        <v>5169</v>
+        <v>91393</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2792,21 +2794,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2816,10 +2818,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512531</v>
+        <v>512478</v>
       </c>
       <c r="R20" t="n">
-        <v>6732485</v>
+        <v>6732507</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2878,10 +2880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121425050</v>
+        <v>121425434</v>
       </c>
       <c r="B21" t="n">
-        <v>100360</v>
+        <v>57367</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2890,45 +2892,53 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512609</v>
+        <v>512583</v>
       </c>
       <c r="R21" t="n">
-        <v>6732541</v>
+        <v>6732462</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2955,19 +2965,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:50</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2976,29 +2981,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121423740</v>
+        <v>121426318</v>
       </c>
       <c r="B22" t="n">
-        <v>90709</v>
+        <v>97051</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3007,41 +3011,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>224363</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512413</v>
+        <v>512584</v>
       </c>
       <c r="R22" t="n">
-        <v>6732688</v>
+        <v>6732486</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3068,39 +3072,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121423753</v>
+        <v>121426321</v>
       </c>
       <c r="B23" t="n">
-        <v>91149</v>
+        <v>56555</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3109,41 +3124,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512549</v>
+        <v>512598</v>
       </c>
       <c r="R23" t="n">
-        <v>6732434</v>
+        <v>6732619</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3170,9 +3193,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3187,22 +3220,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121423792</v>
+        <v>121423766</v>
       </c>
       <c r="B24" t="n">
-        <v>100360</v>
+        <v>90923</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3211,38 +3244,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1618</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512628</v>
+        <v>512622</v>
       </c>
       <c r="R24" t="n">
-        <v>6732517</v>
+        <v>6732491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3283,6 +3319,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3301,10 +3338,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121423766</v>
+        <v>121423785</v>
       </c>
       <c r="B25" t="n">
-        <v>90922</v>
+        <v>78604</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3313,41 +3350,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1618</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512622</v>
+        <v>512534</v>
       </c>
       <c r="R25" t="n">
-        <v>6732491</v>
+        <v>6732503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3388,7 +3422,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3407,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121423764</v>
+        <v>121423765</v>
       </c>
       <c r="B26" t="n">
-        <v>98094</v>
+        <v>56555</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3419,47 +3452,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512489</v>
+        <v>512463</v>
       </c>
       <c r="R26" t="n">
-        <v>6732468</v>
+        <v>6732461</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3518,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121423769</v>
+        <v>121423787</v>
       </c>
       <c r="B27" t="n">
-        <v>90723</v>
+        <v>5169</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3530,25 +3562,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3558,10 +3590,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512493</v>
+        <v>512531</v>
       </c>
       <c r="R27" t="n">
-        <v>6732572</v>
+        <v>6732485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3594,11 +3626,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På syllstock av gammal husruin</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3625,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121426321</v>
+        <v>121423755</v>
       </c>
       <c r="B28" t="n">
-        <v>56555</v>
+        <v>90996</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3641,45 +3668,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512598</v>
+        <v>512555</v>
       </c>
       <c r="R28" t="n">
-        <v>6732619</v>
+        <v>6732434</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3706,19 +3725,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3733,22 +3742,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121425154</v>
+        <v>121423753</v>
       </c>
       <c r="B29" t="n">
-        <v>90727</v>
+        <v>91150</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3757,52 +3766,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512529</v>
+        <v>512549</v>
       </c>
       <c r="R29" t="n">
-        <v>6732493</v>
+        <v>6732434</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3834,40 +3832,34 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121425052</v>
+        <v>121423772</v>
       </c>
       <c r="B30" t="n">
-        <v>100360</v>
+        <v>90728</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3876,45 +3868,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512626</v>
+        <v>512535</v>
       </c>
       <c r="R30" t="n">
-        <v>6732514</v>
+        <v>6732497</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3941,50 +3929,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121423734</v>
+        <v>121425292</v>
       </c>
       <c r="B31" t="n">
-        <v>90674</v>
+        <v>98095</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3993,38 +3970,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512545</v>
+        <v>512561</v>
       </c>
       <c r="R31" t="n">
-        <v>6732494</v>
+        <v>6732464</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4059,34 +4044,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>varav ca 20 med blomställning</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin, Irina Röjås</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121423785</v>
+        <v>121425051</v>
       </c>
       <c r="B32" t="n">
-        <v>78604</v>
+        <v>100361</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4095,41 +4086,45 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512534</v>
+        <v>512639</v>
       </c>
       <c r="R32" t="n">
-        <v>6732503</v>
+        <v>6732526</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4156,39 +4151,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121425434</v>
+        <v>121423792</v>
       </c>
       <c r="B33" t="n">
-        <v>57367</v>
+        <v>100361</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4197,53 +4203,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512583</v>
+        <v>512628</v>
       </c>
       <c r="R33" t="n">
-        <v>6732462</v>
+        <v>6732517</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4273,11 +4267,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4292,22 +4281,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121423768</v>
+        <v>121423791</v>
       </c>
       <c r="B34" t="n">
-        <v>91392</v>
+        <v>100361</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4320,21 +4309,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4344,10 +4333,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512478</v>
+        <v>512638</v>
       </c>
       <c r="R34" t="n">
-        <v>6732507</v>
+        <v>6732516</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4406,10 +4395,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121423733</v>
+        <v>121423790</v>
       </c>
       <c r="B35" t="n">
-        <v>90674</v>
+        <v>100361</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4422,21 +4411,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4446,10 +4435,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512568</v>
+        <v>512628</v>
       </c>
       <c r="R35" t="n">
-        <v>6732462</v>
+        <v>6732540</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4508,10 +4497,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121423790</v>
+        <v>121423764</v>
       </c>
       <c r="B36" t="n">
-        <v>100360</v>
+        <v>98095</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4520,38 +4509,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>512628</v>
+        <v>512489</v>
       </c>
       <c r="R36" t="n">
-        <v>6732540</v>
+        <v>6732468</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4610,10 +4608,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121423772</v>
+        <v>121425052</v>
       </c>
       <c r="B37" t="n">
-        <v>90727</v>
+        <v>100361</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4622,41 +4620,45 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>512535</v>
+        <v>512626</v>
       </c>
       <c r="R37" t="n">
-        <v>6732497</v>
+        <v>6732514</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4683,39 +4685,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121425292</v>
+        <v>121425291</v>
       </c>
       <c r="B38" t="n">
-        <v>98094</v>
+        <v>97049</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4724,46 +4737,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>512561</v>
+        <v>512552</v>
       </c>
       <c r="R38" t="n">
-        <v>6732464</v>
+        <v>6732510</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4798,18 +4803,12 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>varav ca 20 med blomställning</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4821,17 +4820,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121423741</v>
+        <v>121423744</v>
       </c>
       <c r="B39" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4868,10 +4867,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>512543</v>
+        <v>512454</v>
       </c>
       <c r="R39" t="n">
-        <v>6732433</v>
+        <v>6732500</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4930,10 +4929,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121423765</v>
+        <v>121425050</v>
       </c>
       <c r="B40" t="n">
-        <v>56555</v>
+        <v>100361</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4942,49 +4941,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512463</v>
+        <v>512609</v>
       </c>
       <c r="R40" t="n">
-        <v>6732461</v>
+        <v>6732541</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5011,39 +5006,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121426318</v>
+        <v>121423769</v>
       </c>
       <c r="B41" t="n">
-        <v>97050</v>
+        <v>90724</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5052,41 +5058,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>224363</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512584</v>
+        <v>512493</v>
       </c>
       <c r="R41" t="n">
-        <v>6732486</v>
+        <v>6732572</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5113,19 +5119,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:48</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På syllstock av gammal husruin</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5134,29 +5135,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121423754</v>
+        <v>121423734</v>
       </c>
       <c r="B42" t="n">
-        <v>90995</v>
+        <v>90675</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5165,25 +5165,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512475</v>
+        <v>512545</v>
       </c>
       <c r="R42" t="n">
-        <v>6732663</v>
+        <v>6732494</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5258,7 +5258,7 @@
         <v>121426854</v>
       </c>
       <c r="B43" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Beke Regelin, Irina Röjås</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121178299</v>
       </c>
       <c r="B2" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>121179502</v>
       </c>
       <c r="B3" t="n">
-        <v>97049</v>
+        <v>97052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121401275</v>
+        <v>121388880</v>
       </c>
       <c r="B4" t="n">
-        <v>56563</v>
+        <v>57723</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,21 +950,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -972,7 +972,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512405</v>
+        <v>512611</v>
       </c>
       <c r="R4" t="n">
-        <v>6732680</v>
+        <v>6732496</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,27 +1012,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,7 +1057,7 @@
         <v>121388879</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1184,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121400189</v>
+        <v>121388881</v>
       </c>
       <c r="B6" t="n">
-        <v>90996</v>
+        <v>57723</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1196,34 +1191,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1231,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512462</v>
+        <v>512593</v>
       </c>
       <c r="R6" t="n">
-        <v>6732670</v>
+        <v>6732493</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1261,27 +1257,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>stort granvindfälle</t>
+          <t>Den lät som kungsfåglar låter på hösten.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,7 +1286,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1309,10 +1304,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388880</v>
+        <v>121399884</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>97052</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1325,31 +1320,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1357,10 +1348,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512611</v>
+        <v>512569</v>
       </c>
       <c r="R7" t="n">
-        <v>6732496</v>
+        <v>6732458</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1387,22 +1378,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,6 +1402,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1429,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121399884</v>
+        <v>121399873</v>
       </c>
       <c r="B8" t="n">
-        <v>97049</v>
+        <v>56566</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1445,27 +1437,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1508,7 +1504,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1518,7 +1514,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,7 +1523,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1546,10 +1541,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121399873</v>
+        <v>121401275</v>
       </c>
       <c r="B9" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1594,13 +1589,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512569</v>
+        <v>512405</v>
       </c>
       <c r="R9" t="n">
-        <v>6732458</v>
+        <v>6732680</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,7 +1624,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1639,7 +1634,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1666,10 +1666,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388881</v>
+        <v>121400201</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>90999</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1678,35 +1678,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1714,13 +1713,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512593</v>
+        <v>512488</v>
       </c>
       <c r="R10" t="n">
-        <v>6732493</v>
+        <v>6732674</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1744,27 +1743,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Den lät som kungsfåglar låter på hösten.</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,6 +1767,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1791,10 +1786,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121400201</v>
+        <v>121400189</v>
       </c>
       <c r="B11" t="n">
-        <v>90996</v>
+        <v>90999</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1826,7 +1821,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1838,10 +1833,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512488</v>
+        <v>512462</v>
       </c>
       <c r="R11" t="n">
-        <v>6732674</v>
+        <v>6732670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1868,22 +1863,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>stort granvindfälle</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1914,7 +1914,7 @@
         <v>121401513</v>
       </c>
       <c r="B12" t="n">
-        <v>90675</v>
+        <v>90678</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2035,10 +2035,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121425562</v>
+        <v>121425291</v>
       </c>
       <c r="B13" t="n">
-        <v>90710</v>
+        <v>97052</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2047,52 +2047,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512478</v>
+        <v>512552</v>
       </c>
       <c r="R13" t="n">
-        <v>6732505</v>
+        <v>6732510</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2130,29 +2119,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121423754</v>
+        <v>121423785</v>
       </c>
       <c r="B14" t="n">
-        <v>90996</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2165,21 +2153,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2189,10 +2177,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512475</v>
+        <v>512534</v>
       </c>
       <c r="R14" t="n">
-        <v>6732663</v>
+        <v>6732503</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2251,10 +2239,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121423733</v>
+        <v>121423769</v>
       </c>
       <c r="B15" t="n">
-        <v>90675</v>
+        <v>90727</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2263,25 +2251,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2291,10 +2279,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512568</v>
+        <v>512493</v>
       </c>
       <c r="R15" t="n">
-        <v>6732462</v>
+        <v>6732572</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2327,6 +2315,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På syllstock av gammal husruin</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,10 +2346,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121425154</v>
+        <v>121426318</v>
       </c>
       <c r="B16" t="n">
-        <v>90728</v>
+        <v>97054</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2365,38 +2358,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>224363</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2404,10 +2386,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512529</v>
+        <v>512584</v>
       </c>
       <c r="R16" t="n">
-        <v>6732493</v>
+        <v>6732486</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2437,14 +2419,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2465,17 +2452,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121423742</v>
+        <v>121423768</v>
       </c>
       <c r="B17" t="n">
-        <v>90710</v>
+        <v>91396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2484,25 +2471,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2512,10 +2499,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512550</v>
+        <v>512478</v>
       </c>
       <c r="R17" t="n">
-        <v>6732432</v>
+        <v>6732507</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2574,10 +2561,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121423740</v>
+        <v>121423742</v>
       </c>
       <c r="B18" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2614,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512413</v>
+        <v>512550</v>
       </c>
       <c r="R18" t="n">
-        <v>6732688</v>
+        <v>6732432</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2669,17 +2656,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin, Irina Röjås, Evalena Sköld, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121423741</v>
+        <v>121423790</v>
       </c>
       <c r="B19" t="n">
-        <v>90710</v>
+        <v>100364</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2688,25 +2675,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2716,10 +2703,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512543</v>
+        <v>512628</v>
       </c>
       <c r="R19" t="n">
-        <v>6732433</v>
+        <v>6732540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2778,10 +2765,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121423768</v>
+        <v>121423765</v>
       </c>
       <c r="B20" t="n">
-        <v>91393</v>
+        <v>56558</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2790,38 +2777,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512478</v>
+        <v>512463</v>
       </c>
       <c r="R20" t="n">
-        <v>6732507</v>
+        <v>6732461</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2880,10 +2875,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121425434</v>
+        <v>121426321</v>
       </c>
       <c r="B21" t="n">
-        <v>57367</v>
+        <v>56558</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2896,16 +2891,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2913,32 +2908,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512583</v>
+        <v>512598</v>
       </c>
       <c r="R21" t="n">
-        <v>6732462</v>
+        <v>6732619</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2965,14 +2956,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gammla hack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2987,22 +2983,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121426318</v>
+        <v>121423753</v>
       </c>
       <c r="B22" t="n">
-        <v>97051</v>
+        <v>91153</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3011,41 +3007,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>224363</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512584</v>
+        <v>512549</v>
       </c>
       <c r="R22" t="n">
-        <v>6732486</v>
+        <v>6732434</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3072,50 +3068,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121426321</v>
+        <v>121423766</v>
       </c>
       <c r="B23" t="n">
-        <v>56555</v>
+        <v>90926</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3124,49 +3109,44 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>1618</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512598</v>
+        <v>512622</v>
       </c>
       <c r="R23" t="n">
-        <v>6732619</v>
+        <v>6732491</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3193,49 +3173,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121423766</v>
+        <v>121423791</v>
       </c>
       <c r="B24" t="n">
-        <v>90923</v>
+        <v>100364</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3244,41 +3215,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1618</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512622</v>
+        <v>512638</v>
       </c>
       <c r="R24" t="n">
-        <v>6732491</v>
+        <v>6732516</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3319,7 +3287,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3331,17 +3298,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Philipp Weiss, Evalena Sköld, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121423785</v>
+        <v>121425051</v>
       </c>
       <c r="B25" t="n">
-        <v>78604</v>
+        <v>100364</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3350,41 +3317,45 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512534</v>
+        <v>512639</v>
       </c>
       <c r="R25" t="n">
-        <v>6732503</v>
+        <v>6732526</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3411,39 +3382,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121423765</v>
+        <v>121425154</v>
       </c>
       <c r="B26" t="n">
-        <v>56555</v>
+        <v>90731</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3456,45 +3438,48 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512463</v>
+        <v>512529</v>
       </c>
       <c r="R26" t="n">
-        <v>6732461</v>
+        <v>6732493</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3526,34 +3511,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121423787</v>
+        <v>121423733</v>
       </c>
       <c r="B27" t="n">
-        <v>5169</v>
+        <v>90678</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3557,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3590,10 +3581,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512531</v>
+        <v>512568</v>
       </c>
       <c r="R27" t="n">
-        <v>6732485</v>
+        <v>6732462</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,10 +3643,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121423755</v>
+        <v>121425052</v>
       </c>
       <c r="B28" t="n">
-        <v>90996</v>
+        <v>100364</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3664,41 +3655,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512555</v>
+        <v>512626</v>
       </c>
       <c r="R28" t="n">
-        <v>6732434</v>
+        <v>6732514</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3725,39 +3720,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121423753</v>
+        <v>121423792</v>
       </c>
       <c r="B29" t="n">
-        <v>91150</v>
+        <v>100364</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3766,25 +3772,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3794,10 +3800,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512549</v>
+        <v>512628</v>
       </c>
       <c r="R29" t="n">
-        <v>6732434</v>
+        <v>6732517</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3849,17 +3855,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Philipp Weiss, Evalena Sköld, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121423772</v>
+        <v>121423734</v>
       </c>
       <c r="B30" t="n">
-        <v>90728</v>
+        <v>90678</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3868,25 +3874,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3896,10 +3902,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512535</v>
+        <v>512545</v>
       </c>
       <c r="R30" t="n">
-        <v>6732497</v>
+        <v>6732494</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,10 +3964,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121425292</v>
+        <v>121425562</v>
       </c>
       <c r="B31" t="n">
-        <v>98095</v>
+        <v>90713</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3970,49 +3976,52 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512561</v>
+        <v>512478</v>
       </c>
       <c r="R31" t="n">
-        <v>6732464</v>
+        <v>6732505</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4042,11 +4051,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>varav ca 20 med blomställning</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4062,22 +4066,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121425051</v>
+        <v>121423754</v>
       </c>
       <c r="B32" t="n">
-        <v>100361</v>
+        <v>90999</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4086,45 +4090,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512639</v>
+        <v>512475</v>
       </c>
       <c r="R32" t="n">
-        <v>6732526</v>
+        <v>6732663</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4151,50 +4151,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121423792</v>
+        <v>121423772</v>
       </c>
       <c r="B33" t="n">
-        <v>100361</v>
+        <v>90731</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4203,25 +4192,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4231,10 +4220,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512628</v>
+        <v>512535</v>
       </c>
       <c r="R33" t="n">
-        <v>6732517</v>
+        <v>6732497</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4293,10 +4282,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121423791</v>
+        <v>121423787</v>
       </c>
       <c r="B34" t="n">
-        <v>100361</v>
+        <v>5172</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4309,21 +4298,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4333,10 +4322,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512638</v>
+        <v>512531</v>
       </c>
       <c r="R34" t="n">
-        <v>6732516</v>
+        <v>6732485</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4395,10 +4384,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121423790</v>
+        <v>121425292</v>
       </c>
       <c r="B35" t="n">
-        <v>100361</v>
+        <v>98098</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4407,38 +4396,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512628</v>
+        <v>512561</v>
       </c>
       <c r="R35" t="n">
-        <v>6732540</v>
+        <v>6732464</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4473,24 +4470,30 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>varav ca 20 med blomställning</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin, Irina Röjås</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4500,7 +4503,7 @@
         <v>121423764</v>
       </c>
       <c r="B36" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4608,10 +4611,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121425052</v>
+        <v>121425050</v>
       </c>
       <c r="B37" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4652,10 +4655,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>512626</v>
+        <v>512609</v>
       </c>
       <c r="R37" t="n">
-        <v>6732514</v>
+        <v>6732541</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4687,7 +4690,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4697,7 +4700,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4725,10 +4728,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121425291</v>
+        <v>121423741</v>
       </c>
       <c r="B38" t="n">
-        <v>97049</v>
+        <v>90713</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4737,25 +4740,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4765,10 +4768,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>512552</v>
+        <v>512543</v>
       </c>
       <c r="R38" t="n">
-        <v>6732510</v>
+        <v>6732433</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4815,12 +4818,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Beke Regelin, Irina Röjås, Evalena Sköld, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4830,7 +4833,7 @@
         <v>121423744</v>
       </c>
       <c r="B39" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4922,17 +4925,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin, Irina Röjås, Evalena Sköld, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121425050</v>
+        <v>121423755</v>
       </c>
       <c r="B40" t="n">
-        <v>100361</v>
+        <v>90999</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4941,45 +4944,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512609</v>
+        <v>512555</v>
       </c>
       <c r="R40" t="n">
-        <v>6732541</v>
+        <v>6732434</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5006,50 +5005,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121423769</v>
+        <v>121425434</v>
       </c>
       <c r="B41" t="n">
-        <v>90724</v>
+        <v>57370</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5062,37 +5050,49 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512493</v>
+        <v>512583</v>
       </c>
       <c r="R41" t="n">
-        <v>6732572</v>
+        <v>6732462</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På syllstock av gammal husruin</t>
+          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5141,22 +5141,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121423734</v>
+        <v>121423740</v>
       </c>
       <c r="B42" t="n">
-        <v>90675</v>
+        <v>90713</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5165,25 +5165,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512545</v>
+        <v>512413</v>
       </c>
       <c r="R42" t="n">
-        <v>6732494</v>
+        <v>6732688</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin, Irina Röjås, Evalena Sköld, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5258,7 +5258,7 @@
         <v>121426854</v>
       </c>
       <c r="B43" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Evalena Sköld, Philipp Weiss, Beke Regelin, Irina Röjås</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -934,7 +934,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388880</v>
+        <v>121388881</v>
       </c>
       <c r="B4" t="n">
         <v>57723</v>
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512611</v>
+        <v>512593</v>
       </c>
       <c r="R4" t="n">
-        <v>6732496</v>
+        <v>6732493</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +1027,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Den lät som kungsfåglar låter på hösten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388879</v>
+        <v>121388880</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>57723</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,25 +1071,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1150,11 +1155,6 @@
           <t>14:22</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Den lät som talltitor låter på hösten</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388881</v>
+        <v>121399873</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>56566</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1217,7 +1217,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512593</v>
+        <v>512569</v>
       </c>
       <c r="R6" t="n">
-        <v>6732493</v>
+        <v>6732458</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1257,27 +1257,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Den lät som kungsfåglar låter på hösten.</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1304,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121399884</v>
+        <v>121400201</v>
       </c>
       <c r="B7" t="n">
-        <v>97052</v>
+        <v>90999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,31 +1311,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1348,13 +1346,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512569</v>
+        <v>512488</v>
       </c>
       <c r="R7" t="n">
-        <v>6732458</v>
+        <v>6732674</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1378,22 +1376,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,7 +1419,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121399873</v>
+        <v>121401275</v>
       </c>
       <c r="B8" t="n">
         <v>56566</v>
@@ -1469,13 +1467,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512569</v>
+        <v>512405</v>
       </c>
       <c r="R8" t="n">
-        <v>6732458</v>
+        <v>6732680</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1504,7 +1502,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1514,7 +1512,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121401275</v>
+        <v>121400189</v>
       </c>
       <c r="B9" t="n">
-        <v>56566</v>
+        <v>90999</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1553,35 +1556,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1589,13 +1591,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512405</v>
+        <v>512462</v>
       </c>
       <c r="R9" t="n">
-        <v>6732680</v>
+        <v>6732670</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1624,7 +1626,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1634,12 +1636,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
+          <t>stort granvindfälle</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,6 +1650,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1666,10 +1669,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121400201</v>
+        <v>121399884</v>
       </c>
       <c r="B10" t="n">
-        <v>90999</v>
+        <v>97052</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1678,34 +1681,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512488</v>
+        <v>512569</v>
       </c>
       <c r="R10" t="n">
-        <v>6732674</v>
+        <v>6732458</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1743,22 +1743,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,10 +1786,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121400189</v>
+        <v>121388879</v>
       </c>
       <c r="B11" t="n">
-        <v>90999</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1802,30 +1802,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1833,13 +1834,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512462</v>
+        <v>512611</v>
       </c>
       <c r="R11" t="n">
-        <v>6732670</v>
+        <v>6732496</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1863,27 +1864,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>stort granvindfälle</t>
+          <t>Den lät som talltitor låter på hösten</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1892,7 +1893,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2035,10 +2035,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121425291</v>
+        <v>121423765</v>
       </c>
       <c r="B13" t="n">
-        <v>97052</v>
+        <v>56558</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2047,38 +2047,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512552</v>
+        <v>512463</v>
       </c>
       <c r="R13" t="n">
-        <v>6732510</v>
+        <v>6732461</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2125,22 +2133,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121423785</v>
+        <v>121423768</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>91396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2149,25 +2157,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2177,10 +2185,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512534</v>
+        <v>512478</v>
       </c>
       <c r="R14" t="n">
-        <v>6732503</v>
+        <v>6732507</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2239,10 +2247,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121423769</v>
+        <v>121425291</v>
       </c>
       <c r="B15" t="n">
-        <v>90727</v>
+        <v>97052</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,25 +2259,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2279,10 +2287,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512493</v>
+        <v>512552</v>
       </c>
       <c r="R15" t="n">
-        <v>6732572</v>
+        <v>6732510</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2317,11 +2325,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På syllstock av gammal husruin</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2334,22 +2337,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121426318</v>
+        <v>121423753</v>
       </c>
       <c r="B16" t="n">
-        <v>97054</v>
+        <v>91153</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2358,41 +2361,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>224363</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512584</v>
+        <v>512549</v>
       </c>
       <c r="R16" t="n">
-        <v>6732486</v>
+        <v>6732434</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2419,50 +2422,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121423768</v>
+        <v>121423733</v>
       </c>
       <c r="B17" t="n">
-        <v>91396</v>
+        <v>90678</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2475,21 +2467,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2499,10 +2491,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512478</v>
+        <v>512568</v>
       </c>
       <c r="R17" t="n">
-        <v>6732507</v>
+        <v>6732462</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2561,10 +2553,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121423742</v>
+        <v>121423734</v>
       </c>
       <c r="B18" t="n">
-        <v>90713</v>
+        <v>90678</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2573,25 +2565,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,10 +2593,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512550</v>
+        <v>512545</v>
       </c>
       <c r="R18" t="n">
-        <v>6732432</v>
+        <v>6732494</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2656,17 +2648,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås, Evalena Sköld, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121423790</v>
+        <v>121423772</v>
       </c>
       <c r="B19" t="n">
-        <v>100364</v>
+        <v>90731</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,25 +2667,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2703,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512628</v>
+        <v>512535</v>
       </c>
       <c r="R19" t="n">
-        <v>6732540</v>
+        <v>6732497</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121423765</v>
+        <v>121423755</v>
       </c>
       <c r="B20" t="n">
-        <v>56558</v>
+        <v>90999</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2781,42 +2773,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512463</v>
+        <v>512555</v>
       </c>
       <c r="R20" t="n">
-        <v>6732461</v>
+        <v>6732434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2875,10 +2859,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121426321</v>
+        <v>121423790</v>
       </c>
       <c r="B21" t="n">
-        <v>56558</v>
+        <v>100364</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2887,49 +2871,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512598</v>
+        <v>512628</v>
       </c>
       <c r="R21" t="n">
-        <v>6732619</v>
+        <v>6732540</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2956,19 +2932,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2983,22 +2949,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121423753</v>
+        <v>121423764</v>
       </c>
       <c r="B22" t="n">
-        <v>91153</v>
+        <v>98098</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3011,34 +2977,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512549</v>
+        <v>512489</v>
       </c>
       <c r="R22" t="n">
-        <v>6732434</v>
+        <v>6732468</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3097,10 +3072,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121423766</v>
+        <v>121423742</v>
       </c>
       <c r="B23" t="n">
-        <v>90926</v>
+        <v>90713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3109,41 +3084,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1618</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512622</v>
+        <v>512550</v>
       </c>
       <c r="R23" t="n">
-        <v>6732491</v>
+        <v>6732432</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3156,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3203,7 +3174,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121423791</v>
+        <v>121423792</v>
       </c>
       <c r="B24" t="n">
         <v>100364</v>
@@ -3243,10 +3214,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512638</v>
+        <v>512628</v>
       </c>
       <c r="R24" t="n">
-        <v>6732516</v>
+        <v>6732517</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3298,17 +3269,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Evalena Sköld, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121425051</v>
+        <v>121425292</v>
       </c>
       <c r="B25" t="n">
-        <v>100364</v>
+        <v>98098</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3317,45 +3288,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512639</v>
+        <v>512561</v>
       </c>
       <c r="R25" t="n">
-        <v>6732526</v>
+        <v>6732464</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3382,19 +3357,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>varav ca 20 med blomställning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3410,22 +3380,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Beke Regelin, Irina Röjås</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121425154</v>
+        <v>121426318</v>
       </c>
       <c r="B26" t="n">
-        <v>90731</v>
+        <v>97054</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3434,38 +3404,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>224363</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3473,10 +3432,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512529</v>
+        <v>512584</v>
       </c>
       <c r="R26" t="n">
-        <v>6732493</v>
+        <v>6732486</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3506,14 +3465,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3534,17 +3498,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121423733</v>
+        <v>121425154</v>
       </c>
       <c r="B27" t="n">
-        <v>90678</v>
+        <v>90731</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3553,41 +3517,52 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512568</v>
+        <v>512529</v>
       </c>
       <c r="R27" t="n">
-        <v>6732462</v>
+        <v>6732493</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3619,34 +3594,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121425052</v>
+        <v>121425434</v>
       </c>
       <c r="B28" t="n">
-        <v>100364</v>
+        <v>57370</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3655,45 +3636,53 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512626</v>
+        <v>512583</v>
       </c>
       <c r="R28" t="n">
-        <v>6732514</v>
+        <v>6732462</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3720,19 +3709,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:43</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3741,29 +3725,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121423792</v>
+        <v>121426321</v>
       </c>
       <c r="B29" t="n">
-        <v>100364</v>
+        <v>56558</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3772,41 +3755,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512628</v>
+        <v>512598</v>
       </c>
       <c r="R29" t="n">
-        <v>6732517</v>
+        <v>6732619</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3833,9 +3824,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3850,22 +3851,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Evalena Sköld, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121423734</v>
+        <v>121423791</v>
       </c>
       <c r="B30" t="n">
-        <v>90678</v>
+        <v>100364</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3878,21 +3879,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3902,10 +3903,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512545</v>
+        <v>512638</v>
       </c>
       <c r="R30" t="n">
-        <v>6732494</v>
+        <v>6732516</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3964,10 +3965,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121425562</v>
+        <v>121423766</v>
       </c>
       <c r="B31" t="n">
-        <v>90713</v>
+        <v>90926</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3976,52 +3977,44 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1618</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512478</v>
+        <v>512622</v>
       </c>
       <c r="R31" t="n">
-        <v>6732505</v>
+        <v>6732491</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4066,22 +4059,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121423754</v>
+        <v>121423787</v>
       </c>
       <c r="B32" t="n">
-        <v>90999</v>
+        <v>5172</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4090,25 +4083,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4118,10 +4111,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512475</v>
+        <v>512531</v>
       </c>
       <c r="R32" t="n">
-        <v>6732663</v>
+        <v>6732485</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4180,10 +4173,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121423772</v>
+        <v>121425051</v>
       </c>
       <c r="B33" t="n">
-        <v>90731</v>
+        <v>100364</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4192,41 +4185,45 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512535</v>
+        <v>512639</v>
       </c>
       <c r="R33" t="n">
-        <v>6732497</v>
+        <v>6732526</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4253,39 +4250,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121423787</v>
+        <v>121425052</v>
       </c>
       <c r="B34" t="n">
-        <v>5172</v>
+        <v>100364</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4298,37 +4306,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512531</v>
+        <v>512626</v>
       </c>
       <c r="R34" t="n">
-        <v>6732485</v>
+        <v>6732514</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4355,39 +4367,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121425292</v>
+        <v>121423754</v>
       </c>
       <c r="B35" t="n">
-        <v>98098</v>
+        <v>90999</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4396,46 +4419,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512561</v>
+        <v>512475</v>
       </c>
       <c r="R35" t="n">
-        <v>6732464</v>
+        <v>6732663</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4470,40 +4485,34 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>varav ca 20 med blomställning</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121423764</v>
+        <v>121423785</v>
       </c>
       <c r="B36" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4512,47 +4521,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>512489</v>
+        <v>512534</v>
       </c>
       <c r="R36" t="n">
-        <v>6732468</v>
+        <v>6732503</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4611,10 +4611,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121425050</v>
+        <v>121425562</v>
       </c>
       <c r="B37" t="n">
-        <v>100364</v>
+        <v>90713</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4623,45 +4623,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>512609</v>
+        <v>512478</v>
       </c>
       <c r="R37" t="n">
-        <v>6732541</v>
+        <v>6732505</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4688,19 +4695,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4716,19 +4713,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121423741</v>
+        <v>121423740</v>
       </c>
       <c r="B38" t="n">
         <v>90713</v>
@@ -4768,10 +4765,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>512543</v>
+        <v>512413</v>
       </c>
       <c r="R38" t="n">
-        <v>6732433</v>
+        <v>6732688</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4823,7 +4820,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås, Evalena Sköld, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4925,17 +4922,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås, Evalena Sköld, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121423755</v>
+        <v>121423741</v>
       </c>
       <c r="B40" t="n">
-        <v>90999</v>
+        <v>90713</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4948,21 +4945,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4972,10 +4969,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512555</v>
+        <v>512543</v>
       </c>
       <c r="R40" t="n">
-        <v>6732434</v>
+        <v>6732433</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5034,10 +5031,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121425434</v>
+        <v>121423769</v>
       </c>
       <c r="B41" t="n">
-        <v>57370</v>
+        <v>90727</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5050,49 +5047,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512583</v>
+        <v>512493</v>
       </c>
       <c r="R41" t="n">
-        <v>6732462</v>
+        <v>6732572</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5126,7 +5111,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gammla hack</t>
+          <t>På syllstock av gammal husruin</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5141,22 +5126,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121423740</v>
+        <v>121425050</v>
       </c>
       <c r="B42" t="n">
-        <v>90713</v>
+        <v>100364</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5165,41 +5150,45 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512413</v>
+        <v>512609</v>
       </c>
       <c r="R42" t="n">
-        <v>6732688</v>
+        <v>6732541</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5226,29 +5215,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås, Evalena Sköld, Philipp Weiss</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -2553,10 +2553,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121423734</v>
+        <v>121423755</v>
       </c>
       <c r="B18" t="n">
-        <v>90678</v>
+        <v>90999</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2565,25 +2565,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512545</v>
+        <v>512555</v>
       </c>
       <c r="R18" t="n">
-        <v>6732494</v>
+        <v>6732434</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2655,10 +2655,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121423772</v>
+        <v>121423734</v>
       </c>
       <c r="B19" t="n">
-        <v>90731</v>
+        <v>90678</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2667,25 +2667,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512535</v>
+        <v>512545</v>
       </c>
       <c r="R19" t="n">
-        <v>6732497</v>
+        <v>6732494</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2757,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121423755</v>
+        <v>121423772</v>
       </c>
       <c r="B20" t="n">
-        <v>90999</v>
+        <v>90731</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2773,21 +2773,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512555</v>
+        <v>512535</v>
       </c>
       <c r="R20" t="n">
-        <v>6732434</v>
+        <v>6732497</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121425052</v>
+        <v>121423754</v>
       </c>
       <c r="B34" t="n">
-        <v>100364</v>
+        <v>90999</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4302,45 +4302,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512626</v>
+        <v>512475</v>
       </c>
       <c r="R34" t="n">
-        <v>6732514</v>
+        <v>6732663</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4367,50 +4363,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121423754</v>
+        <v>121423785</v>
       </c>
       <c r="B35" t="n">
-        <v>90999</v>
+        <v>78607</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4423,21 +4408,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4447,10 +4432,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512475</v>
+        <v>512534</v>
       </c>
       <c r="R35" t="n">
-        <v>6732663</v>
+        <v>6732503</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4509,10 +4494,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121423785</v>
+        <v>121425052</v>
       </c>
       <c r="B36" t="n">
-        <v>78607</v>
+        <v>100364</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4521,41 +4506,45 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>512534</v>
+        <v>512626</v>
       </c>
       <c r="R36" t="n">
-        <v>6732503</v>
+        <v>6732514</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4582,29 +4571,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121178299</v>
+        <v>121179502</v>
       </c>
       <c r="B2" t="n">
-        <v>90713</v>
+        <v>97052</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512460</v>
+        <v>512532</v>
       </c>
       <c r="R2" t="n">
-        <v>6732491</v>
+        <v>6732598</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -761,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,12 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>uppskattat antal dm²</t>
+          <t>10x3 m, uppskattat område</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121179502</v>
+        <v>121178299</v>
       </c>
       <c r="B3" t="n">
-        <v>97052</v>
+        <v>90713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,39 +817,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512532</v>
+        <v>512460</v>
       </c>
       <c r="R3" t="n">
-        <v>6732598</v>
+        <v>6732491</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>10x3 m, uppskattat område</t>
+          <t>uppskattat antal dm²</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2553,10 +2553,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121423755</v>
+        <v>121423734</v>
       </c>
       <c r="B18" t="n">
-        <v>90999</v>
+        <v>90678</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2565,25 +2565,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512555</v>
+        <v>512545</v>
       </c>
       <c r="R18" t="n">
-        <v>6732434</v>
+        <v>6732494</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2655,10 +2655,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121423734</v>
+        <v>121423772</v>
       </c>
       <c r="B19" t="n">
-        <v>90678</v>
+        <v>90731</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2667,25 +2667,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512545</v>
+        <v>512535</v>
       </c>
       <c r="R19" t="n">
-        <v>6732494</v>
+        <v>6732497</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2757,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121423772</v>
+        <v>121423755</v>
       </c>
       <c r="B20" t="n">
-        <v>90731</v>
+        <v>90999</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2773,21 +2773,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512535</v>
+        <v>512555</v>
       </c>
       <c r="R20" t="n">
-        <v>6732497</v>
+        <v>6732434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121423790</v>
+        <v>121423742</v>
       </c>
       <c r="B21" t="n">
-        <v>100364</v>
+        <v>90713</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2871,25 +2871,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512628</v>
+        <v>512550</v>
       </c>
       <c r="R21" t="n">
-        <v>6732540</v>
+        <v>6732432</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2961,10 +2961,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121423764</v>
+        <v>121423790</v>
       </c>
       <c r="B22" t="n">
-        <v>98098</v>
+        <v>100364</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2973,47 +2973,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512489</v>
+        <v>512628</v>
       </c>
       <c r="R22" t="n">
-        <v>6732468</v>
+        <v>6732540</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3072,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121423742</v>
+        <v>121423764</v>
       </c>
       <c r="B23" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3084,38 +3075,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512550</v>
+        <v>512489</v>
       </c>
       <c r="R23" t="n">
-        <v>6732432</v>
+        <v>6732468</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121179502</v>
       </c>
       <c r="B2" t="n">
-        <v>97052</v>
+        <v>97058</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>121178299</v>
       </c>
       <c r="B3" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388881</v>
+        <v>121400201</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>91005</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,35 +946,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -982,13 +981,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512593</v>
+        <v>512488</v>
       </c>
       <c r="R4" t="n">
-        <v>6732493</v>
+        <v>6732674</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,27 +1011,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Den lät som kungsfåglar låter på hösten.</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,6 +1035,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1059,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388880</v>
+        <v>121388879</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57508</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,25 +1066,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1155,6 +1150,11 @@
           <t>14:22</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Den lät som talltitor låter på hösten</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121399873</v>
+        <v>121401275</v>
       </c>
       <c r="B6" t="n">
-        <v>56566</v>
+        <v>56567</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512569</v>
+        <v>512405</v>
       </c>
       <c r="R6" t="n">
-        <v>6732458</v>
+        <v>6732680</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1272,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,10 +1304,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121400201</v>
+        <v>121388881</v>
       </c>
       <c r="B7" t="n">
-        <v>90999</v>
+        <v>57724</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,34 +1316,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1346,13 +1352,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512488</v>
+        <v>512593</v>
       </c>
       <c r="R7" t="n">
-        <v>6732674</v>
+        <v>6732493</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,22 +1382,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Den lät som kungsfåglar låter på hösten.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,7 +1411,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1419,10 +1429,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121401275</v>
+        <v>121399873</v>
       </c>
       <c r="B8" t="n">
-        <v>56566</v>
+        <v>56567</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1467,13 +1477,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512405</v>
+        <v>512569</v>
       </c>
       <c r="R8" t="n">
-        <v>6732680</v>
+        <v>6732458</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1502,7 +1512,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1512,12 +1522,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1547,7 +1552,7 @@
         <v>121400189</v>
       </c>
       <c r="B9" t="n">
-        <v>90999</v>
+        <v>91005</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1669,10 +1674,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121399884</v>
+        <v>121388880</v>
       </c>
       <c r="B10" t="n">
-        <v>97052</v>
+        <v>57724</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1685,27 +1690,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1713,10 +1722,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512569</v>
+        <v>512611</v>
       </c>
       <c r="R10" t="n">
-        <v>6732458</v>
+        <v>6732496</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1743,22 +1752,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1767,7 +1776,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1786,10 +1794,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388879</v>
+        <v>121399884</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>97058</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1798,35 +1806,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1834,10 +1838,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512611</v>
+        <v>512569</v>
       </c>
       <c r="R11" t="n">
-        <v>6732496</v>
+        <v>6732458</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1864,27 +1868,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Den lät som talltitor låter på hösten</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,6 +1892,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>121401513</v>
       </c>
       <c r="B12" t="n">
-        <v>90678</v>
+        <v>90684</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2035,10 +2035,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121423765</v>
+        <v>121425434</v>
       </c>
       <c r="B13" t="n">
-        <v>56558</v>
+        <v>57371</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2051,16 +2051,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2068,28 +2068,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512463</v>
+        <v>512583</v>
       </c>
       <c r="R13" t="n">
-        <v>6732461</v>
+        <v>6732462</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2119,6 +2123,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2133,22 +2142,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121423768</v>
+        <v>121423772</v>
       </c>
       <c r="B14" t="n">
-        <v>91396</v>
+        <v>90737</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2157,25 +2166,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2185,10 +2194,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512478</v>
+        <v>512535</v>
       </c>
       <c r="R14" t="n">
-        <v>6732507</v>
+        <v>6732497</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2247,10 +2256,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121425291</v>
+        <v>121425051</v>
       </c>
       <c r="B15" t="n">
-        <v>97052</v>
+        <v>100370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2263,37 +2272,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512552</v>
+        <v>512639</v>
       </c>
       <c r="R15" t="n">
-        <v>6732510</v>
+        <v>6732526</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2320,39 +2333,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121423753</v>
+        <v>121423740</v>
       </c>
       <c r="B16" t="n">
-        <v>91153</v>
+        <v>90719</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2361,25 +2385,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2389,10 +2413,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512549</v>
+        <v>512413</v>
       </c>
       <c r="R16" t="n">
-        <v>6732434</v>
+        <v>6732688</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2451,10 +2475,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121423733</v>
+        <v>121425154</v>
       </c>
       <c r="B17" t="n">
-        <v>90678</v>
+        <v>90737</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2463,41 +2487,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512568</v>
+        <v>512529</v>
       </c>
       <c r="R17" t="n">
-        <v>6732462</v>
+        <v>6732493</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2529,34 +2564,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121423734</v>
+        <v>121423766</v>
       </c>
       <c r="B18" t="n">
-        <v>90678</v>
+        <v>90932</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2565,38 +2606,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1618</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512545</v>
+        <v>512622</v>
       </c>
       <c r="R18" t="n">
-        <v>6732494</v>
+        <v>6732491</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,6 +2681,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2655,10 +2700,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121423772</v>
+        <v>121423792</v>
       </c>
       <c r="B19" t="n">
-        <v>90731</v>
+        <v>100370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2667,25 +2712,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2695,10 +2740,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512535</v>
+        <v>512628</v>
       </c>
       <c r="R19" t="n">
-        <v>6732497</v>
+        <v>6732517</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2757,10 +2802,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121423755</v>
+        <v>121423734</v>
       </c>
       <c r="B20" t="n">
-        <v>90999</v>
+        <v>90684</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2769,25 +2814,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2797,10 +2842,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512555</v>
+        <v>512545</v>
       </c>
       <c r="R20" t="n">
-        <v>6732434</v>
+        <v>6732494</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2859,10 +2904,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121423742</v>
+        <v>121426321</v>
       </c>
       <c r="B21" t="n">
-        <v>90713</v>
+        <v>56559</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2875,37 +2920,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512550</v>
+        <v>512598</v>
       </c>
       <c r="R21" t="n">
-        <v>6732432</v>
+        <v>6732619</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2932,9 +2985,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2949,22 +3012,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121423790</v>
+        <v>121423754</v>
       </c>
       <c r="B22" t="n">
-        <v>100364</v>
+        <v>91005</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2973,25 +3036,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3001,10 +3064,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512628</v>
+        <v>512475</v>
       </c>
       <c r="R22" t="n">
-        <v>6732540</v>
+        <v>6732663</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3063,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121423764</v>
+        <v>121423765</v>
       </c>
       <c r="B23" t="n">
-        <v>98098</v>
+        <v>56559</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3075,47 +3138,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512489</v>
+        <v>512463</v>
       </c>
       <c r="R23" t="n">
-        <v>6732468</v>
+        <v>6732461</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3174,10 +3236,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121423792</v>
+        <v>121426318</v>
       </c>
       <c r="B24" t="n">
-        <v>100364</v>
+        <v>97060</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3190,37 +3252,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>224363</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512628</v>
+        <v>512584</v>
       </c>
       <c r="R24" t="n">
-        <v>6732517</v>
+        <v>6732486</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3247,29 +3309,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3279,7 +3352,7 @@
         <v>121425292</v>
       </c>
       <c r="B25" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3392,10 +3465,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121426318</v>
+        <v>121423790</v>
       </c>
       <c r="B26" t="n">
-        <v>97054</v>
+        <v>100370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3408,37 +3481,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>224363</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512584</v>
+        <v>512628</v>
       </c>
       <c r="R26" t="n">
-        <v>6732486</v>
+        <v>6732540</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3465,50 +3538,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121425154</v>
+        <v>121423753</v>
       </c>
       <c r="B27" t="n">
-        <v>90731</v>
+        <v>91159</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3517,52 +3579,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512529</v>
+        <v>512549</v>
       </c>
       <c r="R27" t="n">
-        <v>6732493</v>
+        <v>6732434</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3594,40 +3645,34 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121425434</v>
+        <v>121425291</v>
       </c>
       <c r="B28" t="n">
-        <v>57370</v>
+        <v>97058</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3636,53 +3681,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512583</v>
+        <v>512552</v>
       </c>
       <c r="R28" t="n">
-        <v>6732462</v>
+        <v>6732510</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3712,11 +3745,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3731,22 +3759,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121426321</v>
+        <v>121423791</v>
       </c>
       <c r="B29" t="n">
-        <v>56558</v>
+        <v>100370</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3755,49 +3783,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512598</v>
+        <v>512638</v>
       </c>
       <c r="R29" t="n">
-        <v>6732619</v>
+        <v>6732516</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3824,19 +3844,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3851,22 +3861,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121423791</v>
+        <v>121423741</v>
       </c>
       <c r="B30" t="n">
-        <v>100364</v>
+        <v>90719</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,25 +3885,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3903,10 +3913,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512638</v>
+        <v>512543</v>
       </c>
       <c r="R30" t="n">
-        <v>6732516</v>
+        <v>6732433</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3965,10 +3975,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121423766</v>
+        <v>121423768</v>
       </c>
       <c r="B31" t="n">
-        <v>90926</v>
+        <v>91402</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3977,41 +3987,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1618</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512622</v>
+        <v>512478</v>
       </c>
       <c r="R31" t="n">
-        <v>6732491</v>
+        <v>6732507</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4052,7 +4059,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4071,10 +4077,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121423787</v>
+        <v>121425050</v>
       </c>
       <c r="B32" t="n">
-        <v>5172</v>
+        <v>100370</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4087,37 +4093,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512531</v>
+        <v>512609</v>
       </c>
       <c r="R32" t="n">
-        <v>6732485</v>
+        <v>6732541</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4144,39 +4154,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121425051</v>
+        <v>121423755</v>
       </c>
       <c r="B33" t="n">
-        <v>100364</v>
+        <v>91005</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4185,45 +4206,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512639</v>
+        <v>512555</v>
       </c>
       <c r="R33" t="n">
-        <v>6732526</v>
+        <v>6732434</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4250,50 +4267,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121423754</v>
+        <v>121423785</v>
       </c>
       <c r="B34" t="n">
-        <v>90999</v>
+        <v>78608</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4306,21 +4312,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4330,10 +4336,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512475</v>
+        <v>512534</v>
       </c>
       <c r="R34" t="n">
-        <v>6732663</v>
+        <v>6732503</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4392,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121423785</v>
+        <v>121423787</v>
       </c>
       <c r="B35" t="n">
-        <v>78607</v>
+        <v>5172</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4404,25 +4410,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4432,10 +4438,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512534</v>
+        <v>512531</v>
       </c>
       <c r="R35" t="n">
-        <v>6732503</v>
+        <v>6732485</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4494,10 +4500,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121425052</v>
+        <v>121423769</v>
       </c>
       <c r="B36" t="n">
-        <v>100364</v>
+        <v>90733</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4506,45 +4512,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>512626</v>
+        <v>512493</v>
       </c>
       <c r="R36" t="n">
-        <v>6732514</v>
+        <v>6732572</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4571,19 +4573,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:43</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På syllstock av gammal husruin</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4592,29 +4589,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121425562</v>
+        <v>121423742</v>
       </c>
       <c r="B37" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4644,31 +4640,20 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>512478</v>
+        <v>512550</v>
       </c>
       <c r="R37" t="n">
-        <v>6732505</v>
+        <v>6732432</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4706,29 +4691,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121423740</v>
+        <v>121423744</v>
       </c>
       <c r="B38" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4765,10 +4749,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>512413</v>
+        <v>512454</v>
       </c>
       <c r="R38" t="n">
-        <v>6732688</v>
+        <v>6732500</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4827,10 +4811,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121423744</v>
+        <v>121425562</v>
       </c>
       <c r="B39" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4860,20 +4844,31 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>512454</v>
+        <v>512478</v>
       </c>
       <c r="R39" t="n">
-        <v>6732500</v>
+        <v>6732505</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4911,28 +4906,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121423741</v>
+        <v>121423733</v>
       </c>
       <c r="B40" t="n">
-        <v>90713</v>
+        <v>90684</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4941,25 +4937,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4969,10 +4965,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512543</v>
+        <v>512568</v>
       </c>
       <c r="R40" t="n">
-        <v>6732433</v>
+        <v>6732462</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5031,10 +5027,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121423769</v>
+        <v>121425052</v>
       </c>
       <c r="B41" t="n">
-        <v>90727</v>
+        <v>100370</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5043,41 +5039,45 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512493</v>
+        <v>512626</v>
       </c>
       <c r="R41" t="n">
-        <v>6732572</v>
+        <v>6732514</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5104,14 +5104,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På syllstock av gammal husruin</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,28 +5125,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121425050</v>
+        <v>121423764</v>
       </c>
       <c r="B42" t="n">
-        <v>100364</v>
+        <v>98104</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5150,45 +5156,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512609</v>
+        <v>512489</v>
       </c>
       <c r="R42" t="n">
-        <v>6732541</v>
+        <v>6732468</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5215,40 +5226,29 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5258,7 +5258,7 @@
         <v>121426854</v>
       </c>
       <c r="B43" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -4077,10 +4077,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121425050</v>
+        <v>121423755</v>
       </c>
       <c r="B32" t="n">
-        <v>100370</v>
+        <v>91005</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4089,45 +4089,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512609</v>
+        <v>512555</v>
       </c>
       <c r="R32" t="n">
-        <v>6732541</v>
+        <v>6732434</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4154,50 +4150,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121423755</v>
+        <v>121425050</v>
       </c>
       <c r="B33" t="n">
-        <v>91005</v>
+        <v>100370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4206,41 +4191,45 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512555</v>
+        <v>512609</v>
       </c>
       <c r="R33" t="n">
-        <v>6732434</v>
+        <v>6732541</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4267,29 +4256,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121179502</v>
       </c>
       <c r="B2" t="n">
-        <v>97058</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>121178299</v>
       </c>
       <c r="B3" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121400201</v>
+        <v>121388879</v>
       </c>
       <c r="B4" t="n">
-        <v>91005</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,30 +950,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -981,13 +982,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512488</v>
+        <v>512611</v>
       </c>
       <c r="R4" t="n">
-        <v>6732674</v>
+        <v>6732496</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,22 +1012,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Den lät som talltitor låter på hösten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1041,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1054,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388879</v>
+        <v>121401275</v>
       </c>
       <c r="B5" t="n">
-        <v>57508</v>
+        <v>56568</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,25 +1071,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1092,7 +1097,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1102,13 +1107,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512611</v>
+        <v>512405</v>
       </c>
       <c r="R5" t="n">
-        <v>6732496</v>
+        <v>6732680</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,27 +1137,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Den lät som talltitor låter på hösten</t>
+          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,10 +1184,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121401275</v>
+        <v>121399884</v>
       </c>
       <c r="B6" t="n">
-        <v>56567</v>
+        <v>97059</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,31 +1200,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1227,13 +1228,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512405</v>
+        <v>512569</v>
       </c>
       <c r="R6" t="n">
-        <v>6732680</v>
+        <v>6732458</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1263,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1273,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,6 +1282,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1304,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388881</v>
+        <v>121388880</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>57725</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512593</v>
+        <v>512611</v>
       </c>
       <c r="R7" t="n">
-        <v>6732493</v>
+        <v>6732496</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1387,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1397,12 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Den lät som kungsfåglar låter på hösten.</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121399873</v>
+        <v>121400201</v>
       </c>
       <c r="B8" t="n">
-        <v>56567</v>
+        <v>91006</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1441,35 +1433,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1477,13 +1468,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512569</v>
+        <v>512488</v>
       </c>
       <c r="R8" t="n">
-        <v>6732458</v>
+        <v>6732674</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1507,22 +1498,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,6 +1522,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1552,7 +1544,7 @@
         <v>121400189</v>
       </c>
       <c r="B9" t="n">
-        <v>91005</v>
+        <v>91006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1674,10 +1666,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388880</v>
+        <v>121399873</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>56568</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,21 +1682,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1712,7 +1704,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1722,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512611</v>
+        <v>512569</v>
       </c>
       <c r="R10" t="n">
-        <v>6732496</v>
+        <v>6732458</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1752,22 +1744,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1794,10 +1786,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121399884</v>
+        <v>121388881</v>
       </c>
       <c r="B11" t="n">
-        <v>97058</v>
+        <v>57725</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1810,27 +1802,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1838,10 +1834,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512569</v>
+        <v>512593</v>
       </c>
       <c r="R11" t="n">
-        <v>6732458</v>
+        <v>6732493</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1868,22 +1864,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Den lät som kungsfåglar låter på hösten.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1892,7 +1893,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>121401513</v>
       </c>
       <c r="B12" t="n">
-        <v>90684</v>
+        <v>90685</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2035,10 +2035,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121425434</v>
+        <v>121425562</v>
       </c>
       <c r="B13" t="n">
-        <v>57371</v>
+        <v>90720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2051,35 +2051,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2087,10 +2086,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512583</v>
+        <v>512478</v>
       </c>
       <c r="R13" t="n">
-        <v>6732462</v>
+        <v>6732505</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2125,17 +2124,13 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gammla hack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2154,10 +2149,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121423772</v>
+        <v>121423755</v>
       </c>
       <c r="B14" t="n">
-        <v>90737</v>
+        <v>91006</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2170,21 +2165,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2194,10 +2189,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512535</v>
+        <v>512555</v>
       </c>
       <c r="R14" t="n">
-        <v>6732497</v>
+        <v>6732434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2256,10 +2251,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121425051</v>
+        <v>121423785</v>
       </c>
       <c r="B15" t="n">
-        <v>100370</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2268,45 +2263,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512639</v>
+        <v>512534</v>
       </c>
       <c r="R15" t="n">
-        <v>6732526</v>
+        <v>6732503</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2333,50 +2324,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121423740</v>
+        <v>121423765</v>
       </c>
       <c r="B16" t="n">
-        <v>90719</v>
+        <v>56560</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2389,34 +2369,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512413</v>
+        <v>512463</v>
       </c>
       <c r="R16" t="n">
-        <v>6732688</v>
+        <v>6732461</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2475,10 +2463,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121425154</v>
+        <v>121423734</v>
       </c>
       <c r="B17" t="n">
-        <v>90737</v>
+        <v>90685</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2487,52 +2475,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512529</v>
+        <v>512545</v>
       </c>
       <c r="R17" t="n">
-        <v>6732493</v>
+        <v>6732494</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2564,40 +2541,34 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121423766</v>
+        <v>121425052</v>
       </c>
       <c r="B18" t="n">
-        <v>90932</v>
+        <v>100371</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2606,44 +2577,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1618</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512622</v>
+        <v>512626</v>
       </c>
       <c r="R18" t="n">
-        <v>6732491</v>
+        <v>6732514</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2670,9 +2642,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2688,22 +2670,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121423792</v>
+        <v>121425292</v>
       </c>
       <c r="B19" t="n">
-        <v>100370</v>
+        <v>98105</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,38 +2694,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512628</v>
+        <v>512561</v>
       </c>
       <c r="R19" t="n">
-        <v>6732517</v>
+        <v>6732464</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2778,34 +2768,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>varav ca 20 med blomställning</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin, Irina Röjås</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121423734</v>
+        <v>121423790</v>
       </c>
       <c r="B20" t="n">
-        <v>90684</v>
+        <v>100371</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2818,21 +2814,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2842,10 +2838,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512545</v>
+        <v>512628</v>
       </c>
       <c r="R20" t="n">
-        <v>6732494</v>
+        <v>6732540</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2904,10 +2900,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121426321</v>
+        <v>121423764</v>
       </c>
       <c r="B21" t="n">
-        <v>56559</v>
+        <v>98105</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2916,49 +2912,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512598</v>
+        <v>512489</v>
       </c>
       <c r="R21" t="n">
-        <v>6732619</v>
+        <v>6732468</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2985,19 +2982,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3012,22 +2999,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121423754</v>
+        <v>121423741</v>
       </c>
       <c r="B22" t="n">
-        <v>91005</v>
+        <v>90720</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3040,21 +3027,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3064,10 +3051,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512475</v>
+        <v>512543</v>
       </c>
       <c r="R22" t="n">
-        <v>6732663</v>
+        <v>6732433</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3126,10 +3113,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121423765</v>
+        <v>121423744</v>
       </c>
       <c r="B23" t="n">
-        <v>56559</v>
+        <v>90720</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3142,42 +3129,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512463</v>
+        <v>512454</v>
       </c>
       <c r="R23" t="n">
-        <v>6732461</v>
+        <v>6732500</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3236,10 +3215,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121426318</v>
+        <v>121423754</v>
       </c>
       <c r="B24" t="n">
-        <v>97060</v>
+        <v>91006</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3248,41 +3227,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>224363</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512584</v>
+        <v>512475</v>
       </c>
       <c r="R24" t="n">
-        <v>6732486</v>
+        <v>6732663</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3309,50 +3288,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121425292</v>
+        <v>121423792</v>
       </c>
       <c r="B25" t="n">
-        <v>98104</v>
+        <v>100371</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3361,46 +3329,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512561</v>
+        <v>512628</v>
       </c>
       <c r="R25" t="n">
-        <v>6732464</v>
+        <v>6732517</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3435,40 +3395,34 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>varav ca 20 med blomställning</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121423790</v>
+        <v>121423787</v>
       </c>
       <c r="B26" t="n">
-        <v>100370</v>
+        <v>5172</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3481,21 +3435,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3505,10 +3459,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512628</v>
+        <v>512531</v>
       </c>
       <c r="R26" t="n">
-        <v>6732540</v>
+        <v>6732485</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3567,10 +3521,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121423753</v>
+        <v>121425291</v>
       </c>
       <c r="B27" t="n">
-        <v>91159</v>
+        <v>97059</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3579,25 +3533,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3607,10 +3561,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512549</v>
+        <v>512552</v>
       </c>
       <c r="R27" t="n">
-        <v>6732434</v>
+        <v>6732510</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3657,22 +3611,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121425291</v>
+        <v>121425050</v>
       </c>
       <c r="B28" t="n">
-        <v>97058</v>
+        <v>100371</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3685,37 +3639,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512552</v>
+        <v>512609</v>
       </c>
       <c r="R28" t="n">
-        <v>6732510</v>
+        <v>6732541</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3742,39 +3700,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121423791</v>
+        <v>121423769</v>
       </c>
       <c r="B29" t="n">
-        <v>100370</v>
+        <v>90734</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3783,25 +3752,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3811,10 +3780,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512638</v>
+        <v>512493</v>
       </c>
       <c r="R29" t="n">
-        <v>6732516</v>
+        <v>6732572</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3847,6 +3816,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På syllstock av gammal husruin</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3873,10 +3847,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121423741</v>
+        <v>121425154</v>
       </c>
       <c r="B30" t="n">
-        <v>90719</v>
+        <v>90738</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3889,37 +3863,48 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512543</v>
+        <v>512529</v>
       </c>
       <c r="R30" t="n">
-        <v>6732433</v>
+        <v>6732493</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3951,34 +3936,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121423768</v>
+        <v>121423740</v>
       </c>
       <c r="B31" t="n">
-        <v>91402</v>
+        <v>90720</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3987,25 +3978,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4015,10 +4006,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512478</v>
+        <v>512413</v>
       </c>
       <c r="R31" t="n">
-        <v>6732507</v>
+        <v>6732688</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4077,10 +4068,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121423755</v>
+        <v>121423753</v>
       </c>
       <c r="B32" t="n">
-        <v>91005</v>
+        <v>91160</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4089,25 +4080,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4117,7 +4108,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512555</v>
+        <v>512549</v>
       </c>
       <c r="R32" t="n">
         <v>6732434</v>
@@ -4179,10 +4170,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121425050</v>
+        <v>121423768</v>
       </c>
       <c r="B33" t="n">
-        <v>100370</v>
+        <v>91403</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4195,41 +4186,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512609</v>
+        <v>512478</v>
       </c>
       <c r="R33" t="n">
-        <v>6732541</v>
+        <v>6732507</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4256,50 +4243,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121423785</v>
+        <v>121423742</v>
       </c>
       <c r="B34" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4312,21 +4288,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4336,10 +4312,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512534</v>
+        <v>512550</v>
       </c>
       <c r="R34" t="n">
-        <v>6732503</v>
+        <v>6732432</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4398,10 +4374,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121423787</v>
+        <v>121425434</v>
       </c>
       <c r="B35" t="n">
-        <v>5172</v>
+        <v>57372</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4410,41 +4386,53 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512531</v>
+        <v>512583</v>
       </c>
       <c r="R35" t="n">
-        <v>6732485</v>
+        <v>6732462</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4474,6 +4462,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4488,22 +4481,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121423769</v>
+        <v>121426318</v>
       </c>
       <c r="B36" t="n">
-        <v>90733</v>
+        <v>97061</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4512,41 +4505,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>224363</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>512493</v>
+        <v>512584</v>
       </c>
       <c r="R36" t="n">
-        <v>6732572</v>
+        <v>6732486</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4573,14 +4566,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På syllstock av gammal husruin</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4589,28 +4587,29 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121423742</v>
+        <v>121423733</v>
       </c>
       <c r="B37" t="n">
-        <v>90719</v>
+        <v>90685</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4619,25 +4618,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4647,10 +4646,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>512550</v>
+        <v>512568</v>
       </c>
       <c r="R37" t="n">
-        <v>6732432</v>
+        <v>6732462</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4709,10 +4708,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121423744</v>
+        <v>121425051</v>
       </c>
       <c r="B38" t="n">
-        <v>90719</v>
+        <v>100371</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4721,41 +4720,45 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>512454</v>
+        <v>512639</v>
       </c>
       <c r="R38" t="n">
-        <v>6732500</v>
+        <v>6732526</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4782,39 +4785,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121425562</v>
+        <v>121426321</v>
       </c>
       <c r="B39" t="n">
-        <v>90719</v>
+        <v>56560</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4827,48 +4841,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>512478</v>
+        <v>512598</v>
       </c>
       <c r="R39" t="n">
-        <v>6732505</v>
+        <v>6732619</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4895,40 +4906,49 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121423733</v>
+        <v>121423772</v>
       </c>
       <c r="B40" t="n">
-        <v>90684</v>
+        <v>90738</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4937,25 +4957,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4965,10 +4985,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512568</v>
+        <v>512535</v>
       </c>
       <c r="R40" t="n">
-        <v>6732462</v>
+        <v>6732497</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5027,10 +5047,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121425052</v>
+        <v>121423766</v>
       </c>
       <c r="B41" t="n">
-        <v>100370</v>
+        <v>90933</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5039,45 +5059,44 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>1618</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512626</v>
+        <v>512622</v>
       </c>
       <c r="R41" t="n">
-        <v>6732514</v>
+        <v>6732491</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5104,19 +5123,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5132,22 +5141,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121423764</v>
+        <v>121423791</v>
       </c>
       <c r="B42" t="n">
-        <v>98104</v>
+        <v>100371</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5156,47 +5165,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512489</v>
+        <v>512638</v>
       </c>
       <c r="R42" t="n">
-        <v>6732468</v>
+        <v>6732516</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5258,7 +5258,7 @@
         <v>121426854</v>
       </c>
       <c r="B43" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121179502</v>
+        <v>121178299</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512532</v>
+        <v>512460</v>
       </c>
       <c r="R2" t="n">
-        <v>6732598</v>
+        <v>6732491</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -762,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +771,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>10x3 m, uppskattat område</t>
+          <t>uppskattat antal dm²</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121178299</v>
+        <v>121179502</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>97059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,38 +816,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512460</v>
+        <v>512532</v>
       </c>
       <c r="R3" t="n">
-        <v>6732491</v>
+        <v>6732598</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>uppskattat antal dm²</t>
+          <t>10x3 m, uppskattat område</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388879</v>
+        <v>121400189</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>91006</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,31 +950,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -982,13 +981,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512611</v>
+        <v>512462</v>
       </c>
       <c r="R4" t="n">
-        <v>6732496</v>
+        <v>6732670</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,27 +1011,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Den lät som talltitor låter på hösten</t>
+          <t>stort granvindfälle</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,6 +1040,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121399884</v>
+        <v>121388879</v>
       </c>
       <c r="B6" t="n">
-        <v>97059</v>
+        <v>57509</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1196,31 +1196,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1228,10 +1232,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512569</v>
+        <v>512611</v>
       </c>
       <c r="R6" t="n">
-        <v>6732458</v>
+        <v>6732496</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1258,22 +1262,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Den lät som talltitor låter på hösten</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,7 +1291,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1301,10 +1309,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388880</v>
+        <v>121400201</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>91006</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1313,35 +1321,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1349,13 +1356,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512611</v>
+        <v>512488</v>
       </c>
       <c r="R7" t="n">
-        <v>6732496</v>
+        <v>6732674</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1379,22 +1386,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,6 +1410,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1421,10 +1429,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121400201</v>
+        <v>121388881</v>
       </c>
       <c r="B8" t="n">
-        <v>91006</v>
+        <v>57725</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,34 +1441,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1468,13 +1477,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512488</v>
+        <v>512593</v>
       </c>
       <c r="R8" t="n">
-        <v>6732674</v>
+        <v>6732493</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,22 +1507,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Den lät som kungsfåglar låter på hösten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,7 +1536,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1541,10 +1554,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121400189</v>
+        <v>121399884</v>
       </c>
       <c r="B9" t="n">
-        <v>91006</v>
+        <v>97059</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1553,34 +1566,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1588,13 +1598,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512462</v>
+        <v>512569</v>
       </c>
       <c r="R9" t="n">
-        <v>6732670</v>
+        <v>6732458</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1623,7 +1633,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1633,12 +1643,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>stort granvindfälle</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1786,7 +1791,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388881</v>
+        <v>121388880</v>
       </c>
       <c r="B11" t="n">
         <v>57725</v>
@@ -1834,10 +1839,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512593</v>
+        <v>512611</v>
       </c>
       <c r="R11" t="n">
-        <v>6732493</v>
+        <v>6732496</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1869,7 +1874,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1879,12 +1884,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Den lät som kungsfåglar låter på hösten.</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2035,10 +2035,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121425562</v>
+        <v>121423792</v>
       </c>
       <c r="B13" t="n">
-        <v>90720</v>
+        <v>100371</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2047,52 +2047,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512478</v>
+        <v>512628</v>
       </c>
       <c r="R13" t="n">
-        <v>6732505</v>
+        <v>6732517</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2130,29 +2119,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121423755</v>
+        <v>121423764</v>
       </c>
       <c r="B14" t="n">
-        <v>91006</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2161,38 +2149,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512555</v>
+        <v>512489</v>
       </c>
       <c r="R14" t="n">
-        <v>6732434</v>
+        <v>6732468</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2251,10 +2248,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121423785</v>
+        <v>121425052</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>100371</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2263,41 +2260,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512534</v>
+        <v>512626</v>
       </c>
       <c r="R15" t="n">
-        <v>6732503</v>
+        <v>6732514</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2324,39 +2325,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121423765</v>
+        <v>121423733</v>
       </c>
       <c r="B16" t="n">
-        <v>56560</v>
+        <v>90685</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2365,46 +2377,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512463</v>
+        <v>512568</v>
       </c>
       <c r="R16" t="n">
-        <v>6732461</v>
+        <v>6732462</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2463,10 +2467,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121423734</v>
+        <v>121425291</v>
       </c>
       <c r="B17" t="n">
-        <v>90685</v>
+        <v>97059</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2479,21 +2483,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2503,10 +2507,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512545</v>
+        <v>512552</v>
       </c>
       <c r="R17" t="n">
-        <v>6732494</v>
+        <v>6732510</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2553,22 +2557,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121425052</v>
+        <v>121423742</v>
       </c>
       <c r="B18" t="n">
-        <v>100371</v>
+        <v>90720</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2577,45 +2581,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512626</v>
+        <v>512550</v>
       </c>
       <c r="R18" t="n">
-        <v>6732514</v>
+        <v>6732432</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2642,50 +2642,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121425292</v>
+        <v>121423772</v>
       </c>
       <c r="B19" t="n">
-        <v>98105</v>
+        <v>90738</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2694,46 +2683,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512561</v>
+        <v>512535</v>
       </c>
       <c r="R19" t="n">
-        <v>6732464</v>
+        <v>6732497</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2768,37 +2749,31 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>varav ca 20 med blomställning</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121423790</v>
+        <v>121425051</v>
       </c>
       <c r="B20" t="n">
         <v>100371</v>
@@ -2832,19 +2807,23 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512628</v>
+        <v>512639</v>
       </c>
       <c r="R20" t="n">
-        <v>6732540</v>
+        <v>6732526</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2871,39 +2850,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121423764</v>
+        <v>121423744</v>
       </c>
       <c r="B21" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2912,47 +2902,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512489</v>
+        <v>512454</v>
       </c>
       <c r="R21" t="n">
-        <v>6732468</v>
+        <v>6732500</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3011,10 +2992,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121423741</v>
+        <v>121423791</v>
       </c>
       <c r="B22" t="n">
-        <v>90720</v>
+        <v>100371</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3023,25 +3004,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3051,10 +3032,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512543</v>
+        <v>512638</v>
       </c>
       <c r="R22" t="n">
-        <v>6732433</v>
+        <v>6732516</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3113,7 +3094,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121423744</v>
+        <v>121423741</v>
       </c>
       <c r="B23" t="n">
         <v>90720</v>
@@ -3153,10 +3134,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512454</v>
+        <v>512543</v>
       </c>
       <c r="R23" t="n">
-        <v>6732500</v>
+        <v>6732433</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3215,10 +3196,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121423754</v>
+        <v>121423790</v>
       </c>
       <c r="B24" t="n">
-        <v>91006</v>
+        <v>100371</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3227,25 +3208,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3255,10 +3236,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512475</v>
+        <v>512628</v>
       </c>
       <c r="R24" t="n">
-        <v>6732663</v>
+        <v>6732540</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3317,10 +3298,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121423792</v>
+        <v>121423755</v>
       </c>
       <c r="B25" t="n">
-        <v>100371</v>
+        <v>91006</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3329,25 +3310,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3357,10 +3338,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512628</v>
+        <v>512555</v>
       </c>
       <c r="R25" t="n">
-        <v>6732517</v>
+        <v>6732434</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3419,10 +3400,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121423787</v>
+        <v>121423765</v>
       </c>
       <c r="B26" t="n">
-        <v>5172</v>
+        <v>56560</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3431,38 +3412,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512531</v>
+        <v>512463</v>
       </c>
       <c r="R26" t="n">
-        <v>6732485</v>
+        <v>6732461</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3521,10 +3510,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121425291</v>
+        <v>121423754</v>
       </c>
       <c r="B27" t="n">
-        <v>97059</v>
+        <v>91006</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3533,25 +3522,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3561,10 +3550,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512552</v>
+        <v>512475</v>
       </c>
       <c r="R27" t="n">
-        <v>6732510</v>
+        <v>6732663</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3611,22 +3600,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121425050</v>
+        <v>121425292</v>
       </c>
       <c r="B28" t="n">
-        <v>100371</v>
+        <v>98105</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3635,45 +3624,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512609</v>
+        <v>512561</v>
       </c>
       <c r="R28" t="n">
-        <v>6732541</v>
+        <v>6732464</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3700,19 +3693,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:50</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>varav ca 20 med blomställning</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3728,22 +3716,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Beke Regelin, Irina Röjås</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121423769</v>
+        <v>121426321</v>
       </c>
       <c r="B29" t="n">
-        <v>90734</v>
+        <v>56560</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3756,37 +3744,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512493</v>
+        <v>512598</v>
       </c>
       <c r="R29" t="n">
-        <v>6732572</v>
+        <v>6732619</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3813,14 +3809,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På syllstock av gammal husruin</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3835,22 +3836,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121425154</v>
+        <v>121423740</v>
       </c>
       <c r="B30" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3863,48 +3864,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512529</v>
+        <v>512413</v>
       </c>
       <c r="R30" t="n">
-        <v>6732493</v>
+        <v>6732688</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3936,40 +3926,34 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121423740</v>
+        <v>121425154</v>
       </c>
       <c r="B31" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3982,37 +3966,48 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512413</v>
+        <v>512529</v>
       </c>
       <c r="R31" t="n">
-        <v>6732688</v>
+        <v>6732493</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4044,24 +4039,30 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4170,10 +4171,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121423768</v>
+        <v>121423766</v>
       </c>
       <c r="B33" t="n">
-        <v>91403</v>
+        <v>90933</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4182,38 +4183,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>1618</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512478</v>
+        <v>512622</v>
       </c>
       <c r="R33" t="n">
-        <v>6732507</v>
+        <v>6732491</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4254,6 +4258,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4272,10 +4277,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121423742</v>
+        <v>121426318</v>
       </c>
       <c r="B34" t="n">
-        <v>90720</v>
+        <v>97061</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4284,41 +4289,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>224363</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512550</v>
+        <v>512584</v>
       </c>
       <c r="R34" t="n">
-        <v>6732432</v>
+        <v>6732486</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4345,29 +4350,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4493,10 +4509,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121426318</v>
+        <v>121423785</v>
       </c>
       <c r="B36" t="n">
-        <v>97061</v>
+        <v>78609</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4505,41 +4521,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>224363</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>512584</v>
+        <v>512534</v>
       </c>
       <c r="R36" t="n">
-        <v>6732486</v>
+        <v>6732503</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4566,50 +4582,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121423733</v>
+        <v>121425562</v>
       </c>
       <c r="B37" t="n">
-        <v>90685</v>
+        <v>90720</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4618,41 +4623,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>512568</v>
+        <v>512478</v>
       </c>
       <c r="R37" t="n">
-        <v>6732462</v>
+        <v>6732505</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4690,28 +4706,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121425051</v>
+        <v>121423768</v>
       </c>
       <c r="B38" t="n">
-        <v>100371</v>
+        <v>91403</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4724,41 +4741,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>512639</v>
+        <v>512478</v>
       </c>
       <c r="R38" t="n">
-        <v>6732526</v>
+        <v>6732507</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4785,50 +4798,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121426321</v>
+        <v>121423787</v>
       </c>
       <c r="B39" t="n">
-        <v>56560</v>
+        <v>5172</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4837,49 +4839,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>512598</v>
+        <v>512531</v>
       </c>
       <c r="R39" t="n">
-        <v>6732619</v>
+        <v>6732485</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4906,19 +4900,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4933,22 +4917,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121423772</v>
+        <v>121423734</v>
       </c>
       <c r="B40" t="n">
-        <v>90738</v>
+        <v>90685</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4957,25 +4941,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4985,10 +4969,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512535</v>
+        <v>512545</v>
       </c>
       <c r="R40" t="n">
-        <v>6732497</v>
+        <v>6732494</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5047,10 +5031,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121423766</v>
+        <v>121423769</v>
       </c>
       <c r="B41" t="n">
-        <v>90933</v>
+        <v>90734</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5059,41 +5043,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1618</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512622</v>
+        <v>512493</v>
       </c>
       <c r="R41" t="n">
-        <v>6732491</v>
+        <v>6732572</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5128,13 +5109,17 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På syllstock av gammal husruin</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5153,7 +5138,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121423791</v>
+        <v>121425050</v>
       </c>
       <c r="B42" t="n">
         <v>100371</v>
@@ -5187,19 +5172,23 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512638</v>
+        <v>512609</v>
       </c>
       <c r="R42" t="n">
-        <v>6732516</v>
+        <v>6732541</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5226,29 +5215,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121400189</v>
+        <v>121401275</v>
       </c>
       <c r="B4" t="n">
-        <v>91006</v>
+        <v>56568</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,34 +946,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -981,13 +982,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512462</v>
+        <v>512405</v>
       </c>
       <c r="R4" t="n">
-        <v>6732670</v>
+        <v>6732680</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,12 +1027,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>stort granvindfälle</t>
+          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1041,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1059,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121401275</v>
+        <v>121399884</v>
       </c>
       <c r="B5" t="n">
-        <v>56568</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,31 +1075,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1107,13 +1103,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512405</v>
+        <v>512569</v>
       </c>
       <c r="R5" t="n">
-        <v>6732680</v>
+        <v>6732458</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,12 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,6 +1157,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1184,10 +1176,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388879</v>
+        <v>121400189</v>
       </c>
       <c r="B6" t="n">
-        <v>57509</v>
+        <v>91006</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1200,31 +1192,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1232,13 +1223,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512611</v>
+        <v>512462</v>
       </c>
       <c r="R6" t="n">
-        <v>6732496</v>
+        <v>6732670</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,27 +1253,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Den lät som talltitor låter på hösten</t>
+          <t>stort granvindfälle</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,6 +1282,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1309,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121400201</v>
+        <v>121388881</v>
       </c>
       <c r="B7" t="n">
-        <v>91006</v>
+        <v>57725</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,34 +1313,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1356,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512488</v>
+        <v>512593</v>
       </c>
       <c r="R7" t="n">
-        <v>6732674</v>
+        <v>6732493</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,22 +1379,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Den lät som kungsfåglar låter på hösten.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,7 +1408,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1429,10 +1426,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388881</v>
+        <v>121399873</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>56568</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1445,21 +1442,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1467,7 +1464,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1477,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512593</v>
+        <v>512569</v>
       </c>
       <c r="R8" t="n">
-        <v>6732493</v>
+        <v>6732458</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1507,27 +1504,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Den lät som kungsfåglar låter på hösten.</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,10 +1546,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121399884</v>
+        <v>121400201</v>
       </c>
       <c r="B9" t="n">
-        <v>97059</v>
+        <v>91006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1566,31 +1558,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1598,13 +1593,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512569</v>
+        <v>512488</v>
       </c>
       <c r="R9" t="n">
-        <v>6732458</v>
+        <v>6732674</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1628,22 +1623,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1671,10 +1666,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121399873</v>
+        <v>121388879</v>
       </c>
       <c r="B10" t="n">
-        <v>56568</v>
+        <v>57509</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1683,25 +1678,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1709,7 +1704,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512569</v>
+        <v>512611</v>
       </c>
       <c r="R10" t="n">
-        <v>6732458</v>
+        <v>6732496</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1749,22 +1744,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Den lät som talltitor låter på hösten</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2035,10 +2035,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121423792</v>
+        <v>121423741</v>
       </c>
       <c r="B13" t="n">
-        <v>100371</v>
+        <v>90720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2047,25 +2047,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512628</v>
+        <v>512543</v>
       </c>
       <c r="R13" t="n">
-        <v>6732517</v>
+        <v>6732433</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2137,10 +2137,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121423764</v>
+        <v>121426318</v>
       </c>
       <c r="B14" t="n">
-        <v>98105</v>
+        <v>97061</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2149,50 +2149,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>224363</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512489</v>
+        <v>512584</v>
       </c>
       <c r="R14" t="n">
-        <v>6732468</v>
+        <v>6732486</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,39 +2210,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121425052</v>
+        <v>121423740</v>
       </c>
       <c r="B15" t="n">
-        <v>100371</v>
+        <v>90720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2260,45 +2262,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512626</v>
+        <v>512413</v>
       </c>
       <c r="R15" t="n">
-        <v>6732514</v>
+        <v>6732688</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2325,50 +2323,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121423733</v>
+        <v>121423753</v>
       </c>
       <c r="B16" t="n">
-        <v>90685</v>
+        <v>91160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2377,25 +2364,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2405,10 +2392,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512568</v>
+        <v>512549</v>
       </c>
       <c r="R16" t="n">
-        <v>6732462</v>
+        <v>6732434</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2467,10 +2454,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121425291</v>
+        <v>121423769</v>
       </c>
       <c r="B17" t="n">
-        <v>97059</v>
+        <v>90734</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2479,25 +2466,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2507,10 +2494,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512552</v>
+        <v>512493</v>
       </c>
       <c r="R17" t="n">
-        <v>6732510</v>
+        <v>6732572</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2545,6 +2532,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På syllstock av gammal husruin</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2557,22 +2549,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121423742</v>
+        <v>121425154</v>
       </c>
       <c r="B18" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2585,37 +2577,48 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512550</v>
+        <v>512529</v>
       </c>
       <c r="R18" t="n">
-        <v>6732432</v>
+        <v>6732493</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2647,34 +2650,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121423772</v>
+        <v>121425052</v>
       </c>
       <c r="B19" t="n">
-        <v>90738</v>
+        <v>100371</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2683,41 +2692,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512535</v>
+        <v>512626</v>
       </c>
       <c r="R19" t="n">
-        <v>6732497</v>
+        <v>6732514</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2744,39 +2757,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121425051</v>
+        <v>121423772</v>
       </c>
       <c r="B20" t="n">
-        <v>100371</v>
+        <v>90738</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2785,45 +2809,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512639</v>
+        <v>512535</v>
       </c>
       <c r="R20" t="n">
-        <v>6732526</v>
+        <v>6732497</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2850,47 +2870,36 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121423744</v>
+        <v>121425562</v>
       </c>
       <c r="B21" t="n">
         <v>90720</v>
@@ -2923,20 +2932,31 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512454</v>
+        <v>512478</v>
       </c>
       <c r="R21" t="n">
-        <v>6732500</v>
+        <v>6732505</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2974,28 +2994,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121423791</v>
+        <v>121423755</v>
       </c>
       <c r="B22" t="n">
-        <v>100371</v>
+        <v>91006</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3004,25 +3025,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3032,10 +3053,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512638</v>
+        <v>512555</v>
       </c>
       <c r="R22" t="n">
-        <v>6732516</v>
+        <v>6732434</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3094,10 +3115,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121423741</v>
+        <v>121423754</v>
       </c>
       <c r="B23" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3110,21 +3131,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3134,10 +3155,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512543</v>
+        <v>512475</v>
       </c>
       <c r="R23" t="n">
-        <v>6732433</v>
+        <v>6732663</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3196,10 +3217,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121423790</v>
+        <v>121423766</v>
       </c>
       <c r="B24" t="n">
-        <v>100371</v>
+        <v>90933</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3208,38 +3229,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1618</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512628</v>
+        <v>512622</v>
       </c>
       <c r="R24" t="n">
-        <v>6732540</v>
+        <v>6732491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3280,6 +3304,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3298,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121423755</v>
+        <v>121423787</v>
       </c>
       <c r="B25" t="n">
-        <v>91006</v>
+        <v>5172</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3310,25 +3335,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3338,10 +3363,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512555</v>
+        <v>512531</v>
       </c>
       <c r="R25" t="n">
-        <v>6732434</v>
+        <v>6732485</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3400,10 +3425,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121423765</v>
+        <v>121425292</v>
       </c>
       <c r="B26" t="n">
-        <v>56560</v>
+        <v>98105</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3412,35 +3437,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3448,10 +3473,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512463</v>
+        <v>512561</v>
       </c>
       <c r="R26" t="n">
-        <v>6732461</v>
+        <v>6732464</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3486,34 +3511,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>varav ca 20 med blomställning</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin, Irina Röjås</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121423754</v>
+        <v>121423734</v>
       </c>
       <c r="B27" t="n">
-        <v>91006</v>
+        <v>90685</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3522,25 +3553,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3550,10 +3581,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512475</v>
+        <v>512545</v>
       </c>
       <c r="R27" t="n">
-        <v>6732663</v>
+        <v>6732494</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3612,10 +3643,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121425292</v>
+        <v>121423792</v>
       </c>
       <c r="B28" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3624,46 +3655,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512561</v>
+        <v>512628</v>
       </c>
       <c r="R28" t="n">
-        <v>6732464</v>
+        <v>6732517</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3698,40 +3721,34 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>varav ca 20 med blomställning</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121426321</v>
+        <v>121425434</v>
       </c>
       <c r="B29" t="n">
-        <v>56560</v>
+        <v>57372</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3744,16 +3761,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3761,28 +3778,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512598</v>
+        <v>512583</v>
       </c>
       <c r="R29" t="n">
-        <v>6732619</v>
+        <v>6732462</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3809,19 +3830,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:02</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,22 +3852,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121423740</v>
+        <v>121425291</v>
       </c>
       <c r="B30" t="n">
-        <v>90720</v>
+        <v>97059</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3860,25 +3876,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3888,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512413</v>
+        <v>512552</v>
       </c>
       <c r="R30" t="n">
-        <v>6732688</v>
+        <v>6732510</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3938,22 +3954,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121425154</v>
+        <v>121423765</v>
       </c>
       <c r="B31" t="n">
-        <v>90738</v>
+        <v>56560</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,48 +3982,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512529</v>
+        <v>512463</v>
       </c>
       <c r="R31" t="n">
-        <v>6732493</v>
+        <v>6732461</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4039,40 +4052,34 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121423753</v>
+        <v>121423791</v>
       </c>
       <c r="B32" t="n">
-        <v>91160</v>
+        <v>100371</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4081,25 +4088,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4109,10 +4116,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512549</v>
+        <v>512638</v>
       </c>
       <c r="R32" t="n">
-        <v>6732434</v>
+        <v>6732516</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4171,10 +4178,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121423766</v>
+        <v>121423733</v>
       </c>
       <c r="B33" t="n">
-        <v>90933</v>
+        <v>90685</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4183,41 +4190,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1618</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512622</v>
+        <v>512568</v>
       </c>
       <c r="R33" t="n">
-        <v>6732491</v>
+        <v>6732462</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4258,7 +4262,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4277,10 +4280,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121426318</v>
+        <v>121425050</v>
       </c>
       <c r="B34" t="n">
-        <v>97061</v>
+        <v>100371</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4293,19 +4296,23 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>224363</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -4317,10 +4324,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512584</v>
+        <v>512609</v>
       </c>
       <c r="R34" t="n">
-        <v>6732486</v>
+        <v>6732541</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4352,7 +4359,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4362,7 +4369,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4390,10 +4397,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121425434</v>
+        <v>121423742</v>
       </c>
       <c r="B35" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4406,49 +4413,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512583</v>
+        <v>512550</v>
       </c>
       <c r="R35" t="n">
-        <v>6732462</v>
+        <v>6732432</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4478,11 +4473,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4497,22 +4487,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121423785</v>
+        <v>121423744</v>
       </c>
       <c r="B36" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4525,21 +4515,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4549,10 +4539,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>512534</v>
+        <v>512454</v>
       </c>
       <c r="R36" t="n">
-        <v>6732503</v>
+        <v>6732500</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4611,10 +4601,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121425562</v>
+        <v>121423768</v>
       </c>
       <c r="B37" t="n">
-        <v>90720</v>
+        <v>91403</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4623,52 +4613,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
         <v>512478</v>
       </c>
       <c r="R37" t="n">
-        <v>6732505</v>
+        <v>6732507</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4706,29 +4685,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121423768</v>
+        <v>121423790</v>
       </c>
       <c r="B38" t="n">
-        <v>91403</v>
+        <v>100371</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4741,21 +4719,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3298</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4765,10 +4743,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>512478</v>
+        <v>512628</v>
       </c>
       <c r="R38" t="n">
-        <v>6732507</v>
+        <v>6732540</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4827,10 +4805,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121423787</v>
+        <v>121425051</v>
       </c>
       <c r="B39" t="n">
-        <v>5172</v>
+        <v>100371</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4843,37 +4821,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>512531</v>
+        <v>512639</v>
       </c>
       <c r="R39" t="n">
-        <v>6732485</v>
+        <v>6732526</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4900,39 +4882,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121423734</v>
+        <v>121426321</v>
       </c>
       <c r="B40" t="n">
-        <v>90685</v>
+        <v>56560</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4941,41 +4934,49 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512545</v>
+        <v>512598</v>
       </c>
       <c r="R40" t="n">
-        <v>6732494</v>
+        <v>6732619</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5002,9 +5003,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5019,22 +5030,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121423769</v>
+        <v>121423785</v>
       </c>
       <c r="B41" t="n">
-        <v>90734</v>
+        <v>78609</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5047,21 +5058,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5071,10 +5082,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512493</v>
+        <v>512534</v>
       </c>
       <c r="R41" t="n">
-        <v>6732572</v>
+        <v>6732503</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5107,11 +5118,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På syllstock av gammal husruin</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5138,10 +5144,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121425050</v>
+        <v>121423764</v>
       </c>
       <c r="B42" t="n">
-        <v>100371</v>
+        <v>98105</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5150,45 +5156,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512609</v>
+        <v>512489</v>
       </c>
       <c r="R42" t="n">
-        <v>6732541</v>
+        <v>6732468</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5215,40 +5226,29 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121178299</v>
+        <v>121179502</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512460</v>
+        <v>512532</v>
       </c>
       <c r="R2" t="n">
-        <v>6732491</v>
+        <v>6732598</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -761,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,12 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>uppskattat antal dm²</t>
+          <t>10x3 m, uppskattat område</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121179502</v>
+        <v>121178299</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,39 +817,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512532</v>
+        <v>512460</v>
       </c>
       <c r="R3" t="n">
-        <v>6732598</v>
+        <v>6732491</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>10x3 m, uppskattat område</t>
+          <t>uppskattat antal dm²</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121401275</v>
+        <v>121399884</v>
       </c>
       <c r="B4" t="n">
-        <v>56568</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,31 +950,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -982,13 +978,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512405</v>
+        <v>512569</v>
       </c>
       <c r="R4" t="n">
-        <v>6732680</v>
+        <v>6732458</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,12 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,6 +1032,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1059,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121399884</v>
+        <v>121400189</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
+        <v>91006</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,31 +1063,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1103,13 +1098,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512569</v>
+        <v>512462</v>
       </c>
       <c r="R5" t="n">
-        <v>6732458</v>
+        <v>6732670</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1133,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,7 +1143,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>stort granvindfälle</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,7 +1176,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121400189</v>
+        <v>121400201</v>
       </c>
       <c r="B6" t="n">
         <v>91006</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512462</v>
+        <v>512488</v>
       </c>
       <c r="R6" t="n">
-        <v>6732670</v>
+        <v>6732674</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,27 +1253,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>stort granvindfälle</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1546,10 +1541,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121400201</v>
+        <v>121401275</v>
       </c>
       <c r="B9" t="n">
-        <v>91006</v>
+        <v>56568</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1558,34 +1553,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1593,13 +1589,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512488</v>
+        <v>512405</v>
       </c>
       <c r="R9" t="n">
-        <v>6732674</v>
+        <v>6732680</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1623,22 +1619,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,7 +1648,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1666,10 +1666,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388879</v>
+        <v>121388880</v>
       </c>
       <c r="B10" t="n">
-        <v>57509</v>
+        <v>57725</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1678,25 +1678,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1762,11 +1762,6 @@
           <t>14:22</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Den lät som talltitor låter på hösten</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1791,10 +1786,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388880</v>
+        <v>121388879</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57509</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1803,25 +1798,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1885,6 +1880,11 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Den lät som talltitor låter på hösten</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2035,7 +2035,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121423741</v>
+        <v>121423740</v>
       </c>
       <c r="B13" t="n">
         <v>90720</v>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512543</v>
+        <v>512413</v>
       </c>
       <c r="R13" t="n">
-        <v>6732433</v>
+        <v>6732688</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2137,10 +2137,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121426318</v>
+        <v>121423744</v>
       </c>
       <c r="B14" t="n">
-        <v>97061</v>
+        <v>90720</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2149,41 +2149,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224363</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512584</v>
+        <v>512454</v>
       </c>
       <c r="R14" t="n">
-        <v>6732486</v>
+        <v>6732500</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,50 +2210,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121423740</v>
+        <v>121423755</v>
       </c>
       <c r="B15" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2266,21 +2255,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2290,10 +2279,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512413</v>
+        <v>512555</v>
       </c>
       <c r="R15" t="n">
-        <v>6732688</v>
+        <v>6732434</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2345,17 +2334,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås, Evalena Sköld, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121423753</v>
+        <v>121426321</v>
       </c>
       <c r="B16" t="n">
-        <v>91160</v>
+        <v>56560</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2364,41 +2353,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512549</v>
+        <v>512598</v>
       </c>
       <c r="R16" t="n">
-        <v>6732434</v>
+        <v>6732619</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2425,9 +2422,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2442,22 +2449,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121423769</v>
+        <v>121423787</v>
       </c>
       <c r="B17" t="n">
-        <v>90734</v>
+        <v>5172</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2466,25 +2473,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2494,10 +2501,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512493</v>
+        <v>512531</v>
       </c>
       <c r="R17" t="n">
-        <v>6732572</v>
+        <v>6732485</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2530,11 +2537,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På syllstock av gammal husruin</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,10 +2563,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121425154</v>
+        <v>121423791</v>
       </c>
       <c r="B18" t="n">
-        <v>90738</v>
+        <v>100371</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2573,52 +2575,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512529</v>
+        <v>512638</v>
       </c>
       <c r="R18" t="n">
-        <v>6732493</v>
+        <v>6732516</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2650,40 +2641,34 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121425052</v>
+        <v>121423764</v>
       </c>
       <c r="B19" t="n">
-        <v>100371</v>
+        <v>98105</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2692,45 +2677,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512626</v>
+        <v>512489</v>
       </c>
       <c r="R19" t="n">
-        <v>6732514</v>
+        <v>6732468</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2757,50 +2747,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121423772</v>
+        <v>121425052</v>
       </c>
       <c r="B20" t="n">
-        <v>90738</v>
+        <v>100371</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2809,41 +2788,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512535</v>
+        <v>512626</v>
       </c>
       <c r="R20" t="n">
-        <v>6732497</v>
+        <v>6732514</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2870,39 +2853,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121425562</v>
+        <v>121423734</v>
       </c>
       <c r="B21" t="n">
-        <v>90720</v>
+        <v>90685</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2911,52 +2905,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512478</v>
+        <v>512545</v>
       </c>
       <c r="R21" t="n">
-        <v>6732505</v>
+        <v>6732494</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2994,29 +2977,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121423755</v>
+        <v>121423741</v>
       </c>
       <c r="B22" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3029,21 +3011,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3053,10 +3035,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512555</v>
+        <v>512543</v>
       </c>
       <c r="R22" t="n">
-        <v>6732434</v>
+        <v>6732433</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3115,10 +3097,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121423754</v>
+        <v>121423742</v>
       </c>
       <c r="B23" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3131,21 +3113,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3155,10 +3137,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512475</v>
+        <v>512550</v>
       </c>
       <c r="R23" t="n">
-        <v>6732663</v>
+        <v>6732432</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3323,10 +3305,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121423787</v>
+        <v>121425292</v>
       </c>
       <c r="B25" t="n">
-        <v>5172</v>
+        <v>98105</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3335,38 +3317,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512531</v>
+        <v>512561</v>
       </c>
       <c r="R25" t="n">
-        <v>6732485</v>
+        <v>6732464</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3401,34 +3391,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>varav ca 20 med blomställning</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin, Irina Röjås</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121425292</v>
+        <v>121423792</v>
       </c>
       <c r="B26" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3437,46 +3433,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512561</v>
+        <v>512628</v>
       </c>
       <c r="R26" t="n">
-        <v>6732464</v>
+        <v>6732517</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3511,40 +3499,34 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>varav ca 20 med blomställning</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121423734</v>
+        <v>121423772</v>
       </c>
       <c r="B27" t="n">
-        <v>90685</v>
+        <v>90738</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3553,25 +3535,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3581,10 +3563,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512545</v>
+        <v>512535</v>
       </c>
       <c r="R27" t="n">
-        <v>6732494</v>
+        <v>6732497</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3643,10 +3625,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121423792</v>
+        <v>121426318</v>
       </c>
       <c r="B28" t="n">
-        <v>100371</v>
+        <v>97061</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3659,37 +3641,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>224363</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512628</v>
+        <v>512584</v>
       </c>
       <c r="R28" t="n">
-        <v>6732517</v>
+        <v>6732486</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3716,39 +3698,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121425434</v>
+        <v>121425562</v>
       </c>
       <c r="B29" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3761,35 +3754,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3797,10 +3789,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512583</v>
+        <v>512478</v>
       </c>
       <c r="R29" t="n">
-        <v>6732462</v>
+        <v>6732505</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3835,17 +3827,13 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gammla hack</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3864,10 +3852,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121425291</v>
+        <v>121423754</v>
       </c>
       <c r="B30" t="n">
-        <v>97059</v>
+        <v>91006</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3876,25 +3864,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3904,10 +3892,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512552</v>
+        <v>512475</v>
       </c>
       <c r="R30" t="n">
-        <v>6732510</v>
+        <v>6732663</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3954,22 +3942,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121423765</v>
+        <v>121423769</v>
       </c>
       <c r="B31" t="n">
-        <v>56560</v>
+        <v>90734</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3982,42 +3970,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512463</v>
+        <v>512493</v>
       </c>
       <c r="R31" t="n">
-        <v>6732461</v>
+        <v>6732572</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4050,6 +4030,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På syllstock av gammal husruin</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4076,10 +4061,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121423791</v>
+        <v>121423785</v>
       </c>
       <c r="B32" t="n">
-        <v>100371</v>
+        <v>78609</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4088,25 +4073,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4116,10 +4101,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512638</v>
+        <v>512534</v>
       </c>
       <c r="R32" t="n">
-        <v>6732516</v>
+        <v>6732503</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4171,17 +4156,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Philipp Weiss, Irina Röjås, Evalena Sköld, Beke Regelin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121423733</v>
+        <v>121425051</v>
       </c>
       <c r="B33" t="n">
-        <v>90685</v>
+        <v>100371</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4194,37 +4179,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512568</v>
+        <v>512639</v>
       </c>
       <c r="R33" t="n">
-        <v>6732462</v>
+        <v>6732526</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4251,39 +4240,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121425050</v>
+        <v>121425434</v>
       </c>
       <c r="B34" t="n">
-        <v>100371</v>
+        <v>57372</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4292,45 +4292,53 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512609</v>
+        <v>512583</v>
       </c>
       <c r="R34" t="n">
-        <v>6732541</v>
+        <v>6732462</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4357,19 +4365,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:50</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,29 +4381,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121423742</v>
+        <v>121423790</v>
       </c>
       <c r="B35" t="n">
-        <v>90720</v>
+        <v>100371</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4409,25 +4411,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4437,10 +4439,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512550</v>
+        <v>512628</v>
       </c>
       <c r="R35" t="n">
-        <v>6732432</v>
+        <v>6732540</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4499,10 +4501,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121423744</v>
+        <v>121423753</v>
       </c>
       <c r="B36" t="n">
-        <v>90720</v>
+        <v>91160</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4511,25 +4513,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4539,10 +4541,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>512454</v>
+        <v>512549</v>
       </c>
       <c r="R36" t="n">
-        <v>6732500</v>
+        <v>6732434</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4601,10 +4603,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121423768</v>
+        <v>121425291</v>
       </c>
       <c r="B37" t="n">
-        <v>91403</v>
+        <v>97059</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4617,21 +4619,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4641,10 +4643,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>512478</v>
+        <v>512552</v>
       </c>
       <c r="R37" t="n">
-        <v>6732507</v>
+        <v>6732510</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4691,22 +4693,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121423790</v>
+        <v>121423733</v>
       </c>
       <c r="B38" t="n">
-        <v>100371</v>
+        <v>90685</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4719,21 +4721,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4743,10 +4745,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>512628</v>
+        <v>512568</v>
       </c>
       <c r="R38" t="n">
-        <v>6732540</v>
+        <v>6732462</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4805,7 +4807,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121425051</v>
+        <v>121425050</v>
       </c>
       <c r="B39" t="n">
         <v>100371</v>
@@ -4849,10 +4851,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>512639</v>
+        <v>512609</v>
       </c>
       <c r="R39" t="n">
-        <v>6732526</v>
+        <v>6732541</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4884,7 +4886,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4894,7 +4896,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4922,10 +4924,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121426321</v>
+        <v>121425154</v>
       </c>
       <c r="B40" t="n">
-        <v>56560</v>
+        <v>90738</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4938,31 +4940,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4970,13 +4975,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512598</v>
+        <v>512529</v>
       </c>
       <c r="R40" t="n">
-        <v>6732619</v>
+        <v>6732493</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5003,19 +5008,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:02</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5024,6 +5024,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5042,10 +5043,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121423785</v>
+        <v>121423765</v>
       </c>
       <c r="B41" t="n">
-        <v>78609</v>
+        <v>56560</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5058,34 +5059,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512534</v>
+        <v>512463</v>
       </c>
       <c r="R41" t="n">
-        <v>6732503</v>
+        <v>6732461</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5144,10 +5153,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121423764</v>
+        <v>121423768</v>
       </c>
       <c r="B42" t="n">
-        <v>98105</v>
+        <v>91403</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5156,47 +5165,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512489</v>
+        <v>512478</v>
       </c>
       <c r="R42" t="n">
-        <v>6732468</v>
+        <v>6732507</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Beke Regelin, Irina Röjås</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121179502</v>
+        <v>121178299</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>90728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512532</v>
+        <v>512460</v>
       </c>
       <c r="R2" t="n">
-        <v>6732598</v>
+        <v>6732491</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -762,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +771,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>10x3 m, uppskattat område</t>
+          <t>uppskattat antal dm²</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121178299</v>
+        <v>121179502</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,38 +816,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512460</v>
+        <v>512532</v>
       </c>
       <c r="R3" t="n">
-        <v>6732491</v>
+        <v>6732598</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>uppskattat antal dm²</t>
+          <t>10x3 m, uppskattat område</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121399884</v>
+        <v>121388881</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>57726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,27 +950,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -978,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512569</v>
+        <v>512593</v>
       </c>
       <c r="R4" t="n">
-        <v>6732458</v>
+        <v>6732493</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1008,22 +1012,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Den lät som kungsfåglar låter på hösten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1041,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1051,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121400189</v>
+        <v>121399873</v>
       </c>
       <c r="B5" t="n">
-        <v>91006</v>
+        <v>56569</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,34 +1071,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1098,13 +1107,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512462</v>
+        <v>512569</v>
       </c>
       <c r="R5" t="n">
-        <v>6732670</v>
+        <v>6732458</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1143,12 +1152,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>stort granvindfälle</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,7 +1161,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1176,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121400201</v>
+        <v>121400189</v>
       </c>
       <c r="B6" t="n">
-        <v>91006</v>
+        <v>91014</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,7 +1214,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1223,10 +1226,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512488</v>
+        <v>512462</v>
       </c>
       <c r="R6" t="n">
-        <v>6732674</v>
+        <v>6732670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,22 +1256,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>stort granvindfälle</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1304,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388881</v>
+        <v>121401275</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>56569</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1320,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1334,7 +1342,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1344,13 +1352,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512593</v>
+        <v>512405</v>
       </c>
       <c r="R7" t="n">
-        <v>6732493</v>
+        <v>6732680</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,27 +1382,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Den lät som kungsfåglar låter på hösten.</t>
+          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,10 +1429,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121399873</v>
+        <v>121388880</v>
       </c>
       <c r="B8" t="n">
-        <v>56568</v>
+        <v>57726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,21 +1445,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1459,7 +1467,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1469,10 +1477,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512569</v>
+        <v>512611</v>
       </c>
       <c r="R8" t="n">
-        <v>6732458</v>
+        <v>6732496</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1499,22 +1507,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,10 +1549,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121401275</v>
+        <v>121400201</v>
       </c>
       <c r="B9" t="n">
-        <v>56568</v>
+        <v>91014</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1553,35 +1561,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1589,13 +1596,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512405</v>
+        <v>512488</v>
       </c>
       <c r="R9" t="n">
-        <v>6732680</v>
+        <v>6732674</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,27 +1626,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Vacker kväll och jag hittade spillningen när jag skulle "ta lunch".</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,6 +1650,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1666,10 +1669,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388880</v>
+        <v>121388879</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>57510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1678,25 +1681,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1762,6 +1765,11 @@
           <t>14:22</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Den lät som talltitor låter på hösten</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1786,10 +1794,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388879</v>
+        <v>121399884</v>
       </c>
       <c r="B11" t="n">
-        <v>57509</v>
+        <v>97067</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1798,35 +1806,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1834,10 +1838,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512611</v>
+        <v>512569</v>
       </c>
       <c r="R11" t="n">
-        <v>6732496</v>
+        <v>6732458</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1864,27 +1868,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Den lät som talltitor låter på hösten</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,6 +1892,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>121401513</v>
       </c>
       <c r="B12" t="n">
-        <v>90685</v>
+        <v>90693</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2035,10 +2035,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121423740</v>
+        <v>121423755</v>
       </c>
       <c r="B13" t="n">
-        <v>90720</v>
+        <v>91014</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2051,21 +2051,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512413</v>
+        <v>512555</v>
       </c>
       <c r="R13" t="n">
-        <v>6732688</v>
+        <v>6732434</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2137,10 +2137,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121423744</v>
+        <v>121425291</v>
       </c>
       <c r="B14" t="n">
-        <v>90720</v>
+        <v>97067</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2149,25 +2149,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512454</v>
+        <v>512552</v>
       </c>
       <c r="R14" t="n">
-        <v>6732500</v>
+        <v>6732510</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2227,22 +2227,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121423755</v>
+        <v>121425292</v>
       </c>
       <c r="B15" t="n">
-        <v>91006</v>
+        <v>98113</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,38 +2251,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512555</v>
+        <v>512561</v>
       </c>
       <c r="R15" t="n">
-        <v>6732434</v>
+        <v>6732464</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2317,34 +2325,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>varav ca 20 med blomställning</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Irina Röjås, Evalena Sköld, Philipp Weiss, Beke Regelin</t>
+          <t>Beke Regelin, Irina Röjås</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121426321</v>
+        <v>121426318</v>
       </c>
       <c r="B16" t="n">
-        <v>56560</v>
+        <v>97069</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2353,35 +2367,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>224363</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2389,13 +2395,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512598</v>
+        <v>512584</v>
       </c>
       <c r="R16" t="n">
-        <v>6732619</v>
+        <v>6732486</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2424,7 +2430,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2434,7 +2440,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,6 +2449,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2454,17 +2461,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121423787</v>
+        <v>121423740</v>
       </c>
       <c r="B17" t="n">
-        <v>5172</v>
+        <v>90728</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,25 +2480,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2501,10 +2508,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512531</v>
+        <v>512413</v>
       </c>
       <c r="R17" t="n">
-        <v>6732485</v>
+        <v>6732688</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2563,10 +2570,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121423791</v>
+        <v>121423764</v>
       </c>
       <c r="B18" t="n">
-        <v>100371</v>
+        <v>98113</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2575,38 +2582,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512638</v>
+        <v>512489</v>
       </c>
       <c r="R18" t="n">
-        <v>6732516</v>
+        <v>6732468</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2665,10 +2681,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121423764</v>
+        <v>121423744</v>
       </c>
       <c r="B19" t="n">
-        <v>98105</v>
+        <v>90728</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2677,47 +2693,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512489</v>
+        <v>512454</v>
       </c>
       <c r="R19" t="n">
-        <v>6732468</v>
+        <v>6732500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2776,10 +2783,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121425052</v>
+        <v>121423790</v>
       </c>
       <c r="B20" t="n">
-        <v>100371</v>
+        <v>100379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,23 +2817,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512626</v>
+        <v>512628</v>
       </c>
       <c r="R20" t="n">
-        <v>6732514</v>
+        <v>6732540</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2853,50 +2856,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121423734</v>
+        <v>121423733</v>
       </c>
       <c r="B21" t="n">
-        <v>90685</v>
+        <v>90693</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2933,10 +2925,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512545</v>
+        <v>512568</v>
       </c>
       <c r="R21" t="n">
-        <v>6732494</v>
+        <v>6732462</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2995,10 +2987,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121423741</v>
+        <v>121423768</v>
       </c>
       <c r="B22" t="n">
-        <v>90720</v>
+        <v>91411</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3007,25 +2999,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3035,10 +3027,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512543</v>
+        <v>512478</v>
       </c>
       <c r="R22" t="n">
-        <v>6732433</v>
+        <v>6732507</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3097,10 +3089,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121423742</v>
+        <v>121423791</v>
       </c>
       <c r="B23" t="n">
-        <v>90720</v>
+        <v>100379</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3109,25 +3101,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3137,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512550</v>
+        <v>512638</v>
       </c>
       <c r="R23" t="n">
-        <v>6732432</v>
+        <v>6732516</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3199,10 +3191,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121423766</v>
+        <v>121423792</v>
       </c>
       <c r="B24" t="n">
-        <v>90933</v>
+        <v>100379</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3211,41 +3203,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1618</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512622</v>
+        <v>512628</v>
       </c>
       <c r="R24" t="n">
-        <v>6732491</v>
+        <v>6732517</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3286,7 +3275,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3305,10 +3293,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121425292</v>
+        <v>121423787</v>
       </c>
       <c r="B25" t="n">
-        <v>98105</v>
+        <v>5173</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3317,46 +3305,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512561</v>
+        <v>512531</v>
       </c>
       <c r="R25" t="n">
-        <v>6732464</v>
+        <v>6732485</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3391,40 +3371,34 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>varav ca 20 med blomställning</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121423792</v>
+        <v>121425154</v>
       </c>
       <c r="B26" t="n">
-        <v>100371</v>
+        <v>90746</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3433,41 +3407,52 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512628</v>
+        <v>512529</v>
       </c>
       <c r="R26" t="n">
-        <v>6732517</v>
+        <v>6732493</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3499,34 +3484,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121423772</v>
+        <v>121423753</v>
       </c>
       <c r="B27" t="n">
-        <v>90738</v>
+        <v>91168</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3535,25 +3526,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3563,10 +3554,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512535</v>
+        <v>512549</v>
       </c>
       <c r="R27" t="n">
-        <v>6732497</v>
+        <v>6732434</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3625,10 +3616,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121426318</v>
+        <v>121423766</v>
       </c>
       <c r="B28" t="n">
-        <v>97061</v>
+        <v>90941</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3637,41 +3628,44 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>224363</v>
+        <v>1618</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Postia ceriflua</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512584</v>
+        <v>512622</v>
       </c>
       <c r="R28" t="n">
-        <v>6732486</v>
+        <v>6732491</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3698,19 +3692,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,22 +3710,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121425562</v>
+        <v>121425051</v>
       </c>
       <c r="B29" t="n">
-        <v>90720</v>
+        <v>100379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3750,52 +3734,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512478</v>
+        <v>512639</v>
       </c>
       <c r="R29" t="n">
-        <v>6732505</v>
+        <v>6732526</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3822,9 +3799,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3840,22 +3827,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121423754</v>
+        <v>121425562</v>
       </c>
       <c r="B30" t="n">
-        <v>91006</v>
+        <v>90728</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3868,37 +3855,48 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512475</v>
+        <v>512478</v>
       </c>
       <c r="R30" t="n">
-        <v>6732663</v>
+        <v>6732505</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3936,28 +3934,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121423769</v>
+        <v>121423741</v>
       </c>
       <c r="B31" t="n">
-        <v>90734</v>
+        <v>90728</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3970,21 +3969,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3994,10 +3993,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512493</v>
+        <v>512543</v>
       </c>
       <c r="R31" t="n">
-        <v>6732572</v>
+        <v>6732433</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4030,11 +4029,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På syllstock av gammal husruin</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4061,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121423785</v>
+        <v>121423769</v>
       </c>
       <c r="B32" t="n">
-        <v>78609</v>
+        <v>90742</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4077,21 +4071,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4101,10 +4095,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512534</v>
+        <v>512493</v>
       </c>
       <c r="R32" t="n">
-        <v>6732503</v>
+        <v>6732572</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4139,6 +4133,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På syllstock av gammal husruin</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4156,17 +4155,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Irina Röjås, Evalena Sköld, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121425051</v>
+        <v>121423754</v>
       </c>
       <c r="B33" t="n">
-        <v>100371</v>
+        <v>91014</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4175,45 +4174,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512639</v>
+        <v>512475</v>
       </c>
       <c r="R33" t="n">
-        <v>6732526</v>
+        <v>6732663</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4240,50 +4235,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121425434</v>
+        <v>121423734</v>
       </c>
       <c r="B34" t="n">
-        <v>57372</v>
+        <v>90693</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4292,53 +4276,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512583</v>
+        <v>512545</v>
       </c>
       <c r="R34" t="n">
-        <v>6732462</v>
+        <v>6732494</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4368,11 +4340,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4387,22 +4354,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121423790</v>
+        <v>121423772</v>
       </c>
       <c r="B35" t="n">
-        <v>100371</v>
+        <v>90746</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4411,25 +4378,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4439,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512628</v>
+        <v>512535</v>
       </c>
       <c r="R35" t="n">
-        <v>6732540</v>
+        <v>6732497</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4501,10 +4468,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121423753</v>
+        <v>121426321</v>
       </c>
       <c r="B36" t="n">
-        <v>91160</v>
+        <v>56561</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4513,41 +4480,49 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>512549</v>
+        <v>512598</v>
       </c>
       <c r="R36" t="n">
-        <v>6732434</v>
+        <v>6732619</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4574,9 +4549,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4591,22 +4576,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121425291</v>
+        <v>121425052</v>
       </c>
       <c r="B37" t="n">
-        <v>97059</v>
+        <v>100379</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4619,37 +4604,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>512552</v>
+        <v>512626</v>
       </c>
       <c r="R37" t="n">
-        <v>6732510</v>
+        <v>6732514</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4676,39 +4665,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121423733</v>
+        <v>121423765</v>
       </c>
       <c r="B38" t="n">
-        <v>90685</v>
+        <v>56561</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4717,38 +4717,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>512568</v>
+        <v>512463</v>
       </c>
       <c r="R38" t="n">
-        <v>6732462</v>
+        <v>6732461</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4807,10 +4815,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121425050</v>
+        <v>121425434</v>
       </c>
       <c r="B39" t="n">
-        <v>100371</v>
+        <v>57373</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4819,45 +4827,53 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>512609</v>
+        <v>512583</v>
       </c>
       <c r="R39" t="n">
-        <v>6732541</v>
+        <v>6732462</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4884,19 +4900,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:50</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gammla hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4905,29 +4916,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121425154</v>
+        <v>121425050</v>
       </c>
       <c r="B40" t="n">
-        <v>90738</v>
+        <v>100379</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4936,38 +4946,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4975,10 +4978,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512529</v>
+        <v>512609</v>
       </c>
       <c r="R40" t="n">
-        <v>6732493</v>
+        <v>6732541</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5008,14 +5011,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>större och mindre, 3 var "stora", över 1dm² och resten mindre.</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5036,17 +5044,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121423765</v>
+        <v>121423785</v>
       </c>
       <c r="B41" t="n">
-        <v>56560</v>
+        <v>78616</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5059,42 +5067,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512463</v>
+        <v>512534</v>
       </c>
       <c r="R41" t="n">
-        <v>6732461</v>
+        <v>6732503</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5153,10 +5153,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121423768</v>
+        <v>121423742</v>
       </c>
       <c r="B42" t="n">
-        <v>91403</v>
+        <v>90728</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5165,25 +5165,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512478</v>
+        <v>512550</v>
       </c>
       <c r="R42" t="n">
-        <v>6732507</v>
+        <v>6732432</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5258,7 +5258,7 @@
         <v>121426854</v>
       </c>
       <c r="B43" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Evalena Sköld, Philipp Weiss, Beke Regelin, Irina Röjås</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5382,7 +5382,7 @@
         <v>121426852</v>
       </c>
       <c r="B44" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5382,7 +5382,7 @@
         <v>121426852</v>
       </c>
       <c r="B44" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5382,7 +5382,7 @@
         <v>121426852</v>
       </c>
       <c r="B44" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5382,7 +5382,7 @@
         <v>121426852</v>
       </c>
       <c r="B44" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5382,7 +5382,7 @@
         <v>121426852</v>
       </c>
       <c r="B44" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5498,6 +5498,135 @@
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125811035</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>512578</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6732520</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 50 Flera med blomstänglar.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5627,6 +5627,371 @@
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125813662</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98245</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>512505</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6732477</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>uppskattat antal 200 plantor på en yta ca 10x10m</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125812392</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98245</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>512543</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6732510</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125812085</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98349</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>512564</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6732513</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5503,7 +5503,7 @@
         <v>125811035</v>
       </c>
       <c r="B45" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>125813662</v>
       </c>
       <c r="B46" t="n">
-        <v>98245</v>
+        <v>98248</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>125812392</v>
       </c>
       <c r="B47" t="n">
-        <v>98245</v>
+        <v>98248</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>125812085</v>
       </c>
       <c r="B48" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5991,6 +5991,1909 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125816687</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>512426</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6732697</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>22:34</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>22:34</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125809649</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>512552</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6732505</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Några i blom</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125809802</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>512547</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6732517</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125810285</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58019</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>512560</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6732515</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Osäker på antal</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125810466</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98248</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>512560</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6732515</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125810907</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>512578</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6732520</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Några i blom och några utan blommor</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125812971</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>512539</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6732473</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125810185</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98235</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>512554</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6732516</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Svårt att säga hur många man ser ju bara dem med blomstänglar.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125809958</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98248</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>512558</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6732515</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125812932</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>512543</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6732471</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125813330</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>512524</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6732444</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125810697</v>
+      </c>
+      <c r="B60" t="n">
+        <v>105340</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>512560</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6732515</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Så liten, så skör och så vacker!</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125811364</v>
+      </c>
+      <c r="B61" t="n">
+        <v>105340</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>512579</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6732525</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, blommande, knopp och plantor utan.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125812445</v>
+      </c>
+      <c r="B62" t="n">
+        <v>105340</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>512543</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6732510</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125805740</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>512523</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6732464</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125807286</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98248</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>512607</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6732455</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6590,46 +6590,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125810907</v>
+        <v>125812971</v>
       </c>
       <c r="B54" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6637,10 +6633,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>512578</v>
+        <v>512539</v>
       </c>
       <c r="R54" t="n">
-        <v>6732520</v>
+        <v>6732473</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6672,7 +6668,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6682,12 +6678,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:33</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Några i blom och några utan blommor</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6696,7 +6687,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6715,42 +6705,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125812971</v>
+        <v>125810907</v>
       </c>
       <c r="B55" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6758,10 +6752,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>512539</v>
+        <v>512578</v>
       </c>
       <c r="R55" t="n">
-        <v>6732473</v>
+        <v>6732520</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6793,7 +6787,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6803,7 +6797,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Några i blom och några utan blommor</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6812,6 +6811,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7895,6 +7895,1739 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125967830</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>512459</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6732486</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125973632</v>
+      </c>
+      <c r="B66" t="n">
+        <v>58019</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>512495</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6732470</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Bakom trädskärmen finns ett blötare område med vattenklöver och fläcknycklar.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125972442</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>512481</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6732473</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125971458</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>512481</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6732503</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125968150</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>512450</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6732474</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Några blommade. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125976779</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>658</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>512473</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6732663</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Fjolårets ticka, men jag har inget minne av denna från höstas.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125972943</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>512495</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6732470</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>19:47</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>19:47</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>uppskattat antal.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>125970447</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>512475</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6732479</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Däremot fanns inga blomstänglar just här.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>125970625</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>512475</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6732479</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>125969726</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>512469</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6732470</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>125971792</v>
+      </c>
+      <c r="B75" t="n">
+        <v>97209</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>512451</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6732445</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Minst sex mindre grupper på en mindre yta.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>125969749</v>
+      </c>
+      <c r="B76" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>512472</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6732471</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>125974109</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Hackmora, Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>512490</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6732618</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Granen är nog kring två meter i omkrets.</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>125971336</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>512484</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6732491</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5503,7 +5503,7 @@
         <v>125811035</v>
       </c>
       <c r="B45" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>125813662</v>
       </c>
       <c r="B46" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>125812392</v>
       </c>
       <c r="B47" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>125812085</v>
       </c>
       <c r="B48" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>125809649</v>
       </c>
       <c r="B50" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>125809802</v>
       </c>
       <c r="B51" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>125810285</v>
       </c>
       <c r="B52" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>125810466</v>
       </c>
       <c r="B53" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>125810907</v>
       </c>
       <c r="B55" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>125810185</v>
       </c>
       <c r="B56" t="n">
-        <v>98235</v>
+        <v>98236</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>125809958</v>
       </c>
       <c r="B57" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>125810697</v>
       </c>
       <c r="B60" t="n">
-        <v>105340</v>
+        <v>105341</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>125811364</v>
       </c>
       <c r="B61" t="n">
-        <v>105340</v>
+        <v>105341</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>125812445</v>
       </c>
       <c r="B62" t="n">
-        <v>105340</v>
+        <v>105341</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>125807286</v>
       </c>
       <c r="B64" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>125967830</v>
       </c>
       <c r="B65" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>125973632</v>
       </c>
       <c r="B66" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>125972442</v>
       </c>
       <c r="B67" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>125971458</v>
       </c>
       <c r="B68" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>125968150</v>
       </c>
       <c r="B69" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>125976779</v>
       </c>
       <c r="B70" t="n">
-        <v>91520</v>
+        <v>91521</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>125972943</v>
       </c>
       <c r="B71" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>125970447</v>
       </c>
       <c r="B72" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>125970625</v>
       </c>
       <c r="B73" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9019,10 +9019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125969726</v>
+        <v>125971792</v>
       </c>
       <c r="B74" t="n">
-        <v>98352</v>
+        <v>97210</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9030,38 +9030,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -9070,10 +9066,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>512469</v>
+        <v>512451</v>
       </c>
       <c r="R74" t="n">
-        <v>6732470</v>
+        <v>6732445</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9105,7 +9101,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9115,12 +9111,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Minst sex mindre grupper på en mindre yta.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9148,10 +9144,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125971792</v>
+        <v>125969726</v>
       </c>
       <c r="B75" t="n">
-        <v>97209</v>
+        <v>98353</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9159,34 +9155,38 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>512451</v>
+        <v>512469</v>
       </c>
       <c r="R75" t="n">
-        <v>6732445</v>
+        <v>6732470</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst sex mindre grupper på en mindre yta.</t>
+          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9276,7 +9276,7 @@
         <v>125969749</v>
       </c>
       <c r="B76" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>125971336</v>
       </c>
       <c r="B78" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9627,6 +9627,684 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>125970965</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>512473</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6732483</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Inom en radie på fem meter 100st</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>125971419</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>512481</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6732503</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Kärrviol frånen</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>125964674</v>
+      </c>
+      <c r="B81" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>512459</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6732421</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>125968512</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>512462</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6732477</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>125969094</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>512467</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6732466</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>125974426</v>
+      </c>
+      <c r="B84" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>512516</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6732620</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>När jag stod i kanten mot en öppen yta, äng, hörde jag ett "tjäderbrak" i snåren på andra sidan ängen men jag hann bara se en skymt. Kan eventuellt varit samma hona som jag såg trekvart senare.</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5503,7 +5503,7 @@
         <v>125811035</v>
       </c>
       <c r="B45" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>125813662</v>
       </c>
       <c r="B46" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>125812392</v>
       </c>
       <c r="B47" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>125812085</v>
       </c>
       <c r="B48" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>125809649</v>
       </c>
       <c r="B50" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>125809802</v>
       </c>
       <c r="B51" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6354,10 +6354,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125810285</v>
+        <v>125810466</v>
       </c>
       <c r="B52" t="n">
-        <v>58020</v>
+        <v>98251</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6365,27 +6365,35 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6428,7 +6436,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6438,12 +6446,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Osäker på antal</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6452,6 +6455,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6470,10 +6474,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125810466</v>
+        <v>125810285</v>
       </c>
       <c r="B53" t="n">
-        <v>98249</v>
+        <v>58020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6481,35 +6485,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6552,7 +6548,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6562,7 +6558,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Osäker på antal</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6571,7 +6572,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6590,42 +6590,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125812971</v>
+        <v>125810907</v>
       </c>
       <c r="B54" t="n">
-        <v>57651</v>
+        <v>98355</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6633,10 +6637,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>512539</v>
+        <v>512578</v>
       </c>
       <c r="R54" t="n">
-        <v>6732473</v>
+        <v>6732520</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6668,7 +6672,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6678,7 +6682,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Några i blom och några utan blommor</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6687,6 +6696,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6705,46 +6715,42 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125810907</v>
+        <v>125812971</v>
       </c>
       <c r="B55" t="n">
-        <v>98353</v>
+        <v>57651</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6752,10 +6758,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>512578</v>
+        <v>512539</v>
       </c>
       <c r="R55" t="n">
-        <v>6732520</v>
+        <v>6732473</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6787,7 +6793,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6797,12 +6803,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:33</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Några i blom och några utan blommor</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6811,7 +6812,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>125810185</v>
       </c>
       <c r="B56" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>125809958</v>
       </c>
       <c r="B57" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>125810697</v>
       </c>
       <c r="B60" t="n">
-        <v>105341</v>
+        <v>105343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>125811364</v>
       </c>
       <c r="B61" t="n">
-        <v>105341</v>
+        <v>105343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>125812445</v>
       </c>
       <c r="B62" t="n">
-        <v>105341</v>
+        <v>105343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>125807286</v>
       </c>
       <c r="B64" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>125967830</v>
       </c>
       <c r="B65" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>125972442</v>
       </c>
       <c r="B67" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>125971458</v>
       </c>
       <c r="B68" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>125968150</v>
       </c>
       <c r="B69" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>125976779</v>
       </c>
       <c r="B70" t="n">
-        <v>91521</v>
+        <v>91524</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>125972943</v>
       </c>
       <c r="B71" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8761,37 +8761,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125970447</v>
+        <v>125970625</v>
       </c>
       <c r="B72" t="n">
-        <v>98332</v>
+        <v>98355</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Däremot fanns inga blomstänglar just här.</t>
+          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8890,37 +8890,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125970625</v>
+        <v>125970447</v>
       </c>
       <c r="B73" t="n">
-        <v>98353</v>
+        <v>98334</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Däremot fanns inga blomstänglar just här.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9019,10 +9019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125971792</v>
+        <v>125969726</v>
       </c>
       <c r="B74" t="n">
-        <v>97210</v>
+        <v>98355</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9030,34 +9030,38 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -9066,10 +9070,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>512451</v>
+        <v>512469</v>
       </c>
       <c r="R74" t="n">
-        <v>6732445</v>
+        <v>6732470</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9101,7 +9105,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9111,12 +9115,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst sex mindre grupper på en mindre yta.</t>
+          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9144,10 +9148,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125969726</v>
+        <v>125971792</v>
       </c>
       <c r="B75" t="n">
-        <v>98353</v>
+        <v>97212</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9155,38 +9159,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>512469</v>
+        <v>512451</v>
       </c>
       <c r="R75" t="n">
-        <v>6732470</v>
+        <v>6732445</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Minst sex mindre grupper på en mindre yta.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9276,7 +9276,7 @@
         <v>125969749</v>
       </c>
       <c r="B76" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>125971336</v>
       </c>
       <c r="B78" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>125970965</v>
       </c>
       <c r="B79" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>125971419</v>
       </c>
       <c r="B80" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>125968512</v>
       </c>
       <c r="B82" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>125969094</v>
       </c>
       <c r="B83" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5503,7 +5503,7 @@
         <v>125811035</v>
       </c>
       <c r="B45" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>125813662</v>
       </c>
       <c r="B46" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>125812392</v>
       </c>
       <c r="B47" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>125812085</v>
       </c>
       <c r="B48" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5994,42 +5994,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125816687</v>
+        <v>125809649</v>
       </c>
       <c r="B49" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6037,10 +6041,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512426</v>
+        <v>512552</v>
       </c>
       <c r="R49" t="n">
-        <v>6732697</v>
+        <v>6732505</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6072,7 +6076,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6082,7 +6086,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Några i blom</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6091,6 +6100,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6109,46 +6119,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125809649</v>
+        <v>125816687</v>
       </c>
       <c r="B50" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6156,10 +6162,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512552</v>
+        <v>512426</v>
       </c>
       <c r="R50" t="n">
-        <v>6732505</v>
+        <v>6732697</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6191,7 +6197,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6201,12 +6207,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Några i blom</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6215,7 +6216,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6237,7 +6237,7 @@
         <v>125809802</v>
       </c>
       <c r="B51" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>125810466</v>
       </c>
       <c r="B52" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>125810907</v>
       </c>
       <c r="B54" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>125810185</v>
       </c>
       <c r="B56" t="n">
-        <v>98238</v>
+        <v>98242</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>125809958</v>
       </c>
       <c r="B57" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>125810697</v>
       </c>
       <c r="B60" t="n">
-        <v>105343</v>
+        <v>105347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>125811364</v>
       </c>
       <c r="B61" t="n">
-        <v>105343</v>
+        <v>105347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>125812445</v>
       </c>
       <c r="B62" t="n">
-        <v>105343</v>
+        <v>105347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>125807286</v>
       </c>
       <c r="B64" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>125967830</v>
       </c>
       <c r="B65" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>125972442</v>
       </c>
       <c r="B67" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>125971458</v>
       </c>
       <c r="B68" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>125968150</v>
       </c>
       <c r="B69" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>125976779</v>
       </c>
       <c r="B70" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>125972943</v>
       </c>
       <c r="B71" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>125970625</v>
       </c>
       <c r="B72" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>125970447</v>
       </c>
       <c r="B73" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9019,10 +9019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125969726</v>
+        <v>125971792</v>
       </c>
       <c r="B74" t="n">
-        <v>98355</v>
+        <v>97216</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9030,38 +9030,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -9070,10 +9066,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>512469</v>
+        <v>512451</v>
       </c>
       <c r="R74" t="n">
-        <v>6732470</v>
+        <v>6732445</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9105,7 +9101,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9115,12 +9111,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Minst sex mindre grupper på en mindre yta.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9148,10 +9144,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125971792</v>
+        <v>125969726</v>
       </c>
       <c r="B75" t="n">
-        <v>97212</v>
+        <v>98359</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9159,34 +9155,38 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>512451</v>
+        <v>512469</v>
       </c>
       <c r="R75" t="n">
-        <v>6732445</v>
+        <v>6732470</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst sex mindre grupper på en mindre yta.</t>
+          <t>Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9276,7 +9276,7 @@
         <v>125969749</v>
       </c>
       <c r="B76" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>125971336</v>
       </c>
       <c r="B78" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>125970965</v>
       </c>
       <c r="B79" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>125971419</v>
       </c>
       <c r="B80" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>125968512</v>
       </c>
       <c r="B82" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>125969094</v>
       </c>
       <c r="B83" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -8761,37 +8761,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125970625</v>
+        <v>125970447</v>
       </c>
       <c r="B72" t="n">
-        <v>98359</v>
+        <v>98338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Däremot fanns inga blomstänglar just här.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8890,37 +8890,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125970447</v>
+        <v>125970625</v>
       </c>
       <c r="B73" t="n">
-        <v>98338</v>
+        <v>98359</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Däremot fanns inga blomstänglar just här.</t>
+          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5503,7 +5503,7 @@
         <v>125811035</v>
       </c>
       <c r="B45" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>125813662</v>
       </c>
       <c r="B46" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>125812392</v>
       </c>
       <c r="B47" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>125812085</v>
       </c>
       <c r="B48" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5994,46 +5994,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125809649</v>
+        <v>125816687</v>
       </c>
       <c r="B49" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6041,10 +6037,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512552</v>
+        <v>512426</v>
       </c>
       <c r="R49" t="n">
-        <v>6732505</v>
+        <v>6732697</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6076,7 +6072,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6086,12 +6082,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Några i blom</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6100,7 +6091,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6119,42 +6109,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125816687</v>
+        <v>125809649</v>
       </c>
       <c r="B50" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6162,10 +6156,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512426</v>
+        <v>512552</v>
       </c>
       <c r="R50" t="n">
-        <v>6732697</v>
+        <v>6732505</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6197,7 +6191,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6207,7 +6201,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Några i blom</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6216,6 +6215,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6237,7 +6237,7 @@
         <v>125809802</v>
       </c>
       <c r="B51" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6354,10 +6354,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125810466</v>
+        <v>125810285</v>
       </c>
       <c r="B52" t="n">
-        <v>98255</v>
+        <v>58020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6365,35 +6365,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6436,7 +6428,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6446,7 +6438,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Osäker på antal</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6455,7 +6452,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6474,10 +6470,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125810285</v>
+        <v>125810466</v>
       </c>
       <c r="B53" t="n">
-        <v>58020</v>
+        <v>98256</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6485,27 +6481,35 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6548,7 +6552,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6558,12 +6562,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Osäker på antal</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6572,6 +6571,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6590,46 +6590,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125810907</v>
+        <v>125812971</v>
       </c>
       <c r="B54" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6637,10 +6633,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>512578</v>
+        <v>512539</v>
       </c>
       <c r="R54" t="n">
-        <v>6732520</v>
+        <v>6732473</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6672,7 +6668,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6682,12 +6678,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:33</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Några i blom och några utan blommor</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6696,7 +6687,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6715,42 +6705,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125812971</v>
+        <v>125810907</v>
       </c>
       <c r="B55" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6758,10 +6752,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>512539</v>
+        <v>512578</v>
       </c>
       <c r="R55" t="n">
-        <v>6732473</v>
+        <v>6732520</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6793,7 +6787,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6803,7 +6797,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Några i blom och några utan blommor</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6812,6 +6811,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>125810185</v>
       </c>
       <c r="B56" t="n">
-        <v>98242</v>
+        <v>98243</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>125809958</v>
       </c>
       <c r="B57" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>125810697</v>
       </c>
       <c r="B60" t="n">
-        <v>105347</v>
+        <v>105348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>125811364</v>
       </c>
       <c r="B61" t="n">
-        <v>105347</v>
+        <v>105348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>125812445</v>
       </c>
       <c r="B62" t="n">
-        <v>105347</v>
+        <v>105348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>125807286</v>
       </c>
       <c r="B64" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>125967830</v>
       </c>
       <c r="B65" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>125972442</v>
       </c>
       <c r="B67" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>125971458</v>
       </c>
       <c r="B68" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>125968150</v>
       </c>
       <c r="B69" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>125972943</v>
       </c>
       <c r="B71" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>125970447</v>
       </c>
       <c r="B72" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>125970625</v>
       </c>
       <c r="B73" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>125971792</v>
       </c>
       <c r="B74" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>125969726</v>
       </c>
       <c r="B75" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>125969749</v>
       </c>
       <c r="B76" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>125971336</v>
       </c>
       <c r="B78" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>125970965</v>
       </c>
       <c r="B79" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>125971419</v>
       </c>
       <c r="B80" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>125968512</v>
       </c>
       <c r="B82" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>125969094</v>
       </c>
       <c r="B83" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5503,7 +5503,7 @@
         <v>125811035</v>
       </c>
       <c r="B45" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>125813662</v>
       </c>
       <c r="B46" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125812392</v>
+        <v>125812085</v>
       </c>
       <c r="B47" t="n">
-        <v>98256</v>
+        <v>98362</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,34 +5769,50 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>512543</v>
+        <v>512564</v>
       </c>
       <c r="R47" t="n">
-        <v>6732510</v>
+        <v>6732513</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5828,7 +5844,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5838,7 +5854,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,6 +5868,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5865,10 +5887,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125812085</v>
+        <v>125812392</v>
       </c>
       <c r="B48" t="n">
-        <v>98360</v>
+        <v>98258</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5876,50 +5898,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>512564</v>
+        <v>512543</v>
       </c>
       <c r="R48" t="n">
-        <v>6732513</v>
+        <v>6732510</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5951,7 +5957,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5961,12 +5967,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5975,7 +5976,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5994,42 +5994,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125816687</v>
+        <v>125809649</v>
       </c>
       <c r="B49" t="n">
-        <v>57651</v>
+        <v>98362</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6037,10 +6041,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512426</v>
+        <v>512552</v>
       </c>
       <c r="R49" t="n">
-        <v>6732697</v>
+        <v>6732505</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6072,7 +6076,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6082,7 +6086,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Några i blom</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6091,6 +6100,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6109,46 +6119,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125809649</v>
+        <v>125816687</v>
       </c>
       <c r="B50" t="n">
-        <v>98360</v>
+        <v>57652</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6156,10 +6162,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512552</v>
+        <v>512426</v>
       </c>
       <c r="R50" t="n">
-        <v>6732505</v>
+        <v>6732697</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6191,7 +6197,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6201,12 +6207,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Några i blom</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6215,7 +6216,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6237,7 +6237,7 @@
         <v>125809802</v>
       </c>
       <c r="B51" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>125810285</v>
       </c>
       <c r="B52" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>125810466</v>
       </c>
       <c r="B53" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6590,42 +6590,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125812971</v>
+        <v>125810907</v>
       </c>
       <c r="B54" t="n">
-        <v>57651</v>
+        <v>98362</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6633,10 +6637,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>512539</v>
+        <v>512578</v>
       </c>
       <c r="R54" t="n">
-        <v>6732473</v>
+        <v>6732520</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6668,7 +6672,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6678,7 +6682,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Några i blom och några utan blommor</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6687,6 +6696,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6705,46 +6715,42 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125810907</v>
+        <v>125812971</v>
       </c>
       <c r="B55" t="n">
-        <v>98360</v>
+        <v>57652</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6752,10 +6758,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>512578</v>
+        <v>512539</v>
       </c>
       <c r="R55" t="n">
-        <v>6732520</v>
+        <v>6732473</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6787,7 +6793,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6797,12 +6803,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:33</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Några i blom och några utan blommor</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6811,7 +6812,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>125810185</v>
       </c>
       <c r="B56" t="n">
-        <v>98243</v>
+        <v>98245</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>125809958</v>
       </c>
       <c r="B57" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>125812932</v>
       </c>
       <c r="B58" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>125813330</v>
       </c>
       <c r="B59" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>125810697</v>
       </c>
       <c r="B60" t="n">
-        <v>105348</v>
+        <v>105350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>125811364</v>
       </c>
       <c r="B61" t="n">
-        <v>105348</v>
+        <v>105350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>125812445</v>
       </c>
       <c r="B62" t="n">
-        <v>105348</v>
+        <v>105350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>125805740</v>
       </c>
       <c r="B63" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>125807286</v>
       </c>
       <c r="B64" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>125967830</v>
       </c>
       <c r="B65" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>125973632</v>
       </c>
       <c r="B66" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>125972442</v>
       </c>
       <c r="B67" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>125971458</v>
       </c>
       <c r="B68" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>125968150</v>
       </c>
       <c r="B69" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>125976779</v>
       </c>
       <c r="B70" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>125972943</v>
       </c>
       <c r="B71" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8761,37 +8761,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125970447</v>
+        <v>125970625</v>
       </c>
       <c r="B72" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Däremot fanns inga blomstänglar just här.</t>
+          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8890,37 +8890,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125970625</v>
+        <v>125970447</v>
       </c>
       <c r="B73" t="n">
-        <v>98360</v>
+        <v>98341</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Däremot fanns inga blomstänglar just här.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9022,7 +9022,7 @@
         <v>125971792</v>
       </c>
       <c r="B74" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>125969726</v>
       </c>
       <c r="B75" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>125969749</v>
       </c>
       <c r="B76" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>125974109</v>
       </c>
       <c r="B77" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>125971336</v>
       </c>
       <c r="B78" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>125970965</v>
       </c>
       <c r="B79" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>125971419</v>
       </c>
       <c r="B80" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>125968512</v>
       </c>
       <c r="B82" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>125969094</v>
       </c>
       <c r="B83" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>125974426</v>
       </c>
       <c r="B84" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10306,6 +10306,132 @@
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>125971105</v>
+      </c>
+      <c r="B85" t="n">
+        <v>58509</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>512473</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6732483</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>En liten slank ljusbrun groda med mörka fläckar.</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5503,7 +5503,7 @@
         <v>125811035</v>
       </c>
       <c r="B45" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>125813662</v>
       </c>
       <c r="B46" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125812085</v>
+        <v>125812392</v>
       </c>
       <c r="B47" t="n">
-        <v>98362</v>
+        <v>98260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,50 +5769,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>512564</v>
+        <v>512543</v>
       </c>
       <c r="R47" t="n">
-        <v>6732513</v>
+        <v>6732510</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5844,7 +5828,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5854,12 +5838,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5868,7 +5847,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5887,10 +5865,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125812392</v>
+        <v>125812085</v>
       </c>
       <c r="B48" t="n">
-        <v>98258</v>
+        <v>98364</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,34 +5876,50 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>512543</v>
+        <v>512564</v>
       </c>
       <c r="R48" t="n">
-        <v>6732510</v>
+        <v>6732513</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5957,7 +5951,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5967,7 +5961,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5976,6 +5975,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5994,46 +5994,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125809649</v>
+        <v>125816687</v>
       </c>
       <c r="B49" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6041,10 +6037,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512552</v>
+        <v>512426</v>
       </c>
       <c r="R49" t="n">
-        <v>6732505</v>
+        <v>6732697</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6076,7 +6072,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6086,12 +6082,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Några i blom</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6100,7 +6091,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6119,42 +6109,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125816687</v>
+        <v>125809649</v>
       </c>
       <c r="B50" t="n">
-        <v>57652</v>
+        <v>98364</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6162,10 +6156,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512426</v>
+        <v>512552</v>
       </c>
       <c r="R50" t="n">
-        <v>6732697</v>
+        <v>6732505</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6197,7 +6191,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6207,7 +6201,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Några i blom</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6216,6 +6215,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6237,7 +6237,7 @@
         <v>125809802</v>
       </c>
       <c r="B51" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>125810466</v>
       </c>
       <c r="B53" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6590,46 +6590,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125810907</v>
+        <v>125812971</v>
       </c>
       <c r="B54" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6637,10 +6633,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>512578</v>
+        <v>512539</v>
       </c>
       <c r="R54" t="n">
-        <v>6732520</v>
+        <v>6732473</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6672,7 +6668,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6682,12 +6678,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:33</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Några i blom och några utan blommor</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6696,7 +6687,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6715,42 +6705,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125812971</v>
+        <v>125810907</v>
       </c>
       <c r="B55" t="n">
-        <v>57652</v>
+        <v>98364</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6758,10 +6752,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>512539</v>
+        <v>512578</v>
       </c>
       <c r="R55" t="n">
-        <v>6732473</v>
+        <v>6732520</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6793,7 +6787,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6803,7 +6797,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Några i blom och några utan blommor</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6812,6 +6811,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>125810185</v>
       </c>
       <c r="B56" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>125809958</v>
       </c>
       <c r="B57" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>125810697</v>
       </c>
       <c r="B60" t="n">
-        <v>105350</v>
+        <v>105352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>125811364</v>
       </c>
       <c r="B61" t="n">
-        <v>105350</v>
+        <v>105352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>125812445</v>
       </c>
       <c r="B62" t="n">
-        <v>105350</v>
+        <v>105352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>125807286</v>
       </c>
       <c r="B64" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>125967830</v>
       </c>
       <c r="B65" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>125972442</v>
       </c>
       <c r="B67" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>125971458</v>
       </c>
       <c r="B68" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>125968150</v>
       </c>
       <c r="B69" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>125976779</v>
       </c>
       <c r="B70" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>125972943</v>
       </c>
       <c r="B71" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8761,37 +8761,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125970625</v>
+        <v>125970447</v>
       </c>
       <c r="B72" t="n">
-        <v>98362</v>
+        <v>98343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Däremot fanns inga blomstänglar just här.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8890,37 +8890,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125970447</v>
+        <v>125970625</v>
       </c>
       <c r="B73" t="n">
-        <v>98341</v>
+        <v>98364</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Däremot fanns inga blomstänglar just här.</t>
+          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9022,7 +9022,7 @@
         <v>125971792</v>
       </c>
       <c r="B74" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>125969726</v>
       </c>
       <c r="B75" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>125969749</v>
       </c>
       <c r="B76" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>125971336</v>
       </c>
       <c r="B78" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>125970965</v>
       </c>
       <c r="B79" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>125971419</v>
       </c>
       <c r="B80" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>125968512</v>
       </c>
       <c r="B82" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>125969094</v>
       </c>
       <c r="B83" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10432,6 +10432,132 @@
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>125969156</v>
+      </c>
+      <c r="B86" t="n">
+        <v>58509</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>512467</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6732466</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>En liten ljusbrun groda med mörkare fläckar och slank kropp.  Jag såg egentligen två på två olika ställen men jag noterade bara koordinaterna på den ena eftersom jag inte hann ta något foto på den. När jag såg en till rapporterade jag den eftersom jag tycker att grodor är viktiga, men jag hann inte ta någon bild på den heller innan den försvann under blåbärsriset.</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5503,7 +5503,7 @@
         <v>125811035</v>
       </c>
       <c r="B45" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>125813662</v>
       </c>
       <c r="B46" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>125812392</v>
       </c>
       <c r="B47" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>125812085</v>
       </c>
       <c r="B48" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5994,42 +5994,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125816687</v>
+        <v>125809649</v>
       </c>
       <c r="B49" t="n">
-        <v>57652</v>
+        <v>98366</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6037,10 +6041,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512426</v>
+        <v>512552</v>
       </c>
       <c r="R49" t="n">
-        <v>6732697</v>
+        <v>6732505</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6072,7 +6076,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6082,7 +6086,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Några i blom</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6091,6 +6100,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6109,46 +6119,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125809649</v>
+        <v>125816687</v>
       </c>
       <c r="B50" t="n">
-        <v>98364</v>
+        <v>57652</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6156,10 +6162,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512552</v>
+        <v>512426</v>
       </c>
       <c r="R50" t="n">
-        <v>6732505</v>
+        <v>6732697</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6191,7 +6197,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6201,12 +6207,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Några i blom</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6215,7 +6216,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6237,7 +6237,7 @@
         <v>125809802</v>
       </c>
       <c r="B51" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6354,10 +6354,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125810285</v>
+        <v>125810466</v>
       </c>
       <c r="B52" t="n">
-        <v>58021</v>
+        <v>98262</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6365,27 +6365,35 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6428,7 +6436,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6438,12 +6446,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Osäker på antal</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6452,6 +6455,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6470,10 +6474,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125810466</v>
+        <v>125810285</v>
       </c>
       <c r="B53" t="n">
-        <v>98260</v>
+        <v>58021</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6481,35 +6485,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6552,7 +6548,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6562,7 +6558,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Osäker på antal</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6571,7 +6572,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>125810907</v>
       </c>
       <c r="B55" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>125810185</v>
       </c>
       <c r="B56" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>125809958</v>
       </c>
       <c r="B57" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>125810697</v>
       </c>
       <c r="B60" t="n">
-        <v>105352</v>
+        <v>105356</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>125811364</v>
       </c>
       <c r="B61" t="n">
-        <v>105352</v>
+        <v>105356</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>125812445</v>
       </c>
       <c r="B62" t="n">
-        <v>105352</v>
+        <v>105356</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>125807286</v>
       </c>
       <c r="B64" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>125967830</v>
       </c>
       <c r="B65" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>125972442</v>
       </c>
       <c r="B67" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>125971458</v>
       </c>
       <c r="B68" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>125968150</v>
       </c>
       <c r="B69" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>125976779</v>
       </c>
       <c r="B70" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>125972943</v>
       </c>
       <c r="B71" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>125970447</v>
       </c>
       <c r="B72" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>125970625</v>
       </c>
       <c r="B73" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>125971792</v>
       </c>
       <c r="B74" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>125969726</v>
       </c>
       <c r="B75" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>125969749</v>
       </c>
       <c r="B76" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>125971336</v>
       </c>
       <c r="B78" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>125970965</v>
       </c>
       <c r="B79" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>125971419</v>
       </c>
       <c r="B80" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>125968512</v>
       </c>
       <c r="B82" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>125969094</v>
       </c>
       <c r="B83" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -8761,37 +8761,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125970447</v>
+        <v>125970625</v>
       </c>
       <c r="B72" t="n">
-        <v>98345</v>
+        <v>98366</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Däremot fanns inga blomstänglar just här.</t>
+          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8890,37 +8890,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125970625</v>
+        <v>125970447</v>
       </c>
       <c r="B73" t="n">
-        <v>98366</v>
+        <v>98345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Däremot fanns inga blomstänglar just här.</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5503,7 +5503,7 @@
         <v>125811035</v>
       </c>
       <c r="B45" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>125813662</v>
       </c>
       <c r="B46" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>125812392</v>
       </c>
       <c r="B47" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>125812085</v>
       </c>
       <c r="B48" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5994,46 +5994,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125809649</v>
+        <v>125816687</v>
       </c>
       <c r="B49" t="n">
-        <v>98366</v>
+        <v>57656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6041,10 +6037,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512552</v>
+        <v>512426</v>
       </c>
       <c r="R49" t="n">
-        <v>6732505</v>
+        <v>6732697</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6076,7 +6072,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6086,12 +6082,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Några i blom</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6100,7 +6091,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6119,42 +6109,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125816687</v>
+        <v>125809649</v>
       </c>
       <c r="B50" t="n">
-        <v>57652</v>
+        <v>98370</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6162,10 +6156,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512426</v>
+        <v>512552</v>
       </c>
       <c r="R50" t="n">
-        <v>6732697</v>
+        <v>6732505</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6197,7 +6191,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6207,7 +6201,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Några i blom</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6216,6 +6215,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6237,7 +6237,7 @@
         <v>125809802</v>
       </c>
       <c r="B51" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6354,10 +6354,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125810466</v>
+        <v>125810285</v>
       </c>
       <c r="B52" t="n">
-        <v>98262</v>
+        <v>58025</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6365,35 +6365,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6436,7 +6428,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6446,7 +6438,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Osäker på antal</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6455,7 +6452,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6474,10 +6470,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125810285</v>
+        <v>125810466</v>
       </c>
       <c r="B53" t="n">
-        <v>58021</v>
+        <v>98266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6485,27 +6481,35 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6548,7 +6552,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6558,12 +6562,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Osäker på antal</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6572,6 +6571,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6593,7 +6593,7 @@
         <v>125812971</v>
       </c>
       <c r="B54" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>125810907</v>
       </c>
       <c r="B55" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>125810185</v>
       </c>
       <c r="B56" t="n">
-        <v>98249</v>
+        <v>98253</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>125809958</v>
       </c>
       <c r="B57" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>125812932</v>
       </c>
       <c r="B58" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>125813330</v>
       </c>
       <c r="B59" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>125810697</v>
       </c>
       <c r="B60" t="n">
-        <v>105356</v>
+        <v>105369</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>125811364</v>
       </c>
       <c r="B61" t="n">
-        <v>105356</v>
+        <v>105369</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>125812445</v>
       </c>
       <c r="B62" t="n">
-        <v>105356</v>
+        <v>105369</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>125805740</v>
       </c>
       <c r="B63" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>125807286</v>
       </c>
       <c r="B64" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>125967830</v>
       </c>
       <c r="B65" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>125973632</v>
       </c>
       <c r="B66" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>125972442</v>
       </c>
       <c r="B67" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>125971458</v>
       </c>
       <c r="B68" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>125968150</v>
       </c>
       <c r="B69" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>125976779</v>
       </c>
       <c r="B70" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>125972943</v>
       </c>
       <c r="B71" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8761,37 +8761,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125970625</v>
+        <v>125970447</v>
       </c>
       <c r="B72" t="n">
-        <v>98366</v>
+        <v>98349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Däremot fanns inga blomstänglar just här.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8890,37 +8890,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125970447</v>
+        <v>125970625</v>
       </c>
       <c r="B73" t="n">
-        <v>98345</v>
+        <v>98370</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Däremot fanns inga blomstänglar just här.</t>
+          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9022,7 +9022,7 @@
         <v>125971792</v>
       </c>
       <c r="B74" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>125969726</v>
       </c>
       <c r="B75" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>125969749</v>
       </c>
       <c r="B76" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>125974109</v>
       </c>
       <c r="B77" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>125971336</v>
       </c>
       <c r="B78" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>125970965</v>
       </c>
       <c r="B79" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>125971419</v>
       </c>
       <c r="B80" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>125968512</v>
       </c>
       <c r="B82" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>125969094</v>
       </c>
       <c r="B83" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>125974426</v>
       </c>
       <c r="B84" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>125971105</v>
       </c>
       <c r="B85" t="n">
-        <v>58509</v>
+        <v>58513</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>125969156</v>
       </c>
       <c r="B86" t="n">
-        <v>58509</v>
+        <v>58513</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5503,7 +5503,7 @@
         <v>125811035</v>
       </c>
       <c r="B45" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>125813662</v>
       </c>
       <c r="B46" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>125812392</v>
       </c>
       <c r="B47" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>125812085</v>
       </c>
       <c r="B48" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5994,42 +5994,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125816687</v>
+        <v>125809649</v>
       </c>
       <c r="B49" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6037,10 +6041,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512426</v>
+        <v>512552</v>
       </c>
       <c r="R49" t="n">
-        <v>6732697</v>
+        <v>6732505</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6072,7 +6076,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6082,7 +6086,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Några i blom</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6091,6 +6100,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6109,46 +6119,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125809649</v>
+        <v>125816687</v>
       </c>
       <c r="B50" t="n">
-        <v>98370</v>
+        <v>57656</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6156,10 +6162,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512552</v>
+        <v>512426</v>
       </c>
       <c r="R50" t="n">
-        <v>6732505</v>
+        <v>6732697</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6191,7 +6197,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6201,12 +6207,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Några i blom</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6215,7 +6216,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6237,7 +6237,7 @@
         <v>125809802</v>
       </c>
       <c r="B51" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>125810466</v>
       </c>
       <c r="B53" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>125810907</v>
       </c>
       <c r="B55" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>125810185</v>
       </c>
       <c r="B56" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>125809958</v>
       </c>
       <c r="B57" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>125810697</v>
       </c>
       <c r="B60" t="n">
-        <v>105369</v>
+        <v>105372</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>125811364</v>
       </c>
       <c r="B61" t="n">
-        <v>105369</v>
+        <v>105372</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>125812445</v>
       </c>
       <c r="B62" t="n">
-        <v>105369</v>
+        <v>105372</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>125807286</v>
       </c>
       <c r="B64" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>125967830</v>
       </c>
       <c r="B65" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>125972442</v>
       </c>
       <c r="B67" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>125971458</v>
       </c>
       <c r="B68" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>125968150</v>
       </c>
       <c r="B69" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>125972943</v>
       </c>
       <c r="B71" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8761,37 +8761,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125970447</v>
+        <v>125970625</v>
       </c>
       <c r="B72" t="n">
-        <v>98349</v>
+        <v>98373</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Däremot fanns inga blomstänglar just här.</t>
+          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8890,37 +8890,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125970625</v>
+        <v>125970447</v>
       </c>
       <c r="B73" t="n">
-        <v>98370</v>
+        <v>98352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Däremot fanns inga blomstänglar just här.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9022,7 +9022,7 @@
         <v>125971792</v>
       </c>
       <c r="B74" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>125969726</v>
       </c>
       <c r="B75" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>125969749</v>
       </c>
       <c r="B76" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>125971336</v>
       </c>
       <c r="B78" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>125970965</v>
       </c>
       <c r="B79" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>125971419</v>
       </c>
       <c r="B80" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>125968512</v>
       </c>
       <c r="B82" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>125969094</v>
       </c>
       <c r="B83" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5758,10 +5758,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125812392</v>
+        <v>125812085</v>
       </c>
       <c r="B47" t="n">
-        <v>98269</v>
+        <v>98373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,34 +5769,50 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>512543</v>
+        <v>512564</v>
       </c>
       <c r="R47" t="n">
-        <v>6732510</v>
+        <v>6732513</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5828,7 +5844,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5838,7 +5854,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,6 +5868,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5865,10 +5887,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125812085</v>
+        <v>125812392</v>
       </c>
       <c r="B48" t="n">
-        <v>98373</v>
+        <v>98269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5876,50 +5898,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>512564</v>
+        <v>512543</v>
       </c>
       <c r="R48" t="n">
-        <v>6732513</v>
+        <v>6732510</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5951,7 +5957,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5961,12 +5967,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5975,7 +5976,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5994,46 +5994,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125809649</v>
+        <v>125816687</v>
       </c>
       <c r="B49" t="n">
-        <v>98373</v>
+        <v>57656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6041,10 +6037,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512552</v>
+        <v>512426</v>
       </c>
       <c r="R49" t="n">
-        <v>6732505</v>
+        <v>6732697</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6076,7 +6072,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6086,12 +6082,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Några i blom</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6100,7 +6091,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6119,42 +6109,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125816687</v>
+        <v>125809649</v>
       </c>
       <c r="B50" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6162,10 +6156,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512426</v>
+        <v>512552</v>
       </c>
       <c r="R50" t="n">
-        <v>6732697</v>
+        <v>6732505</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6197,7 +6191,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6207,7 +6201,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Några i blom</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6216,6 +6215,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5758,10 +5758,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125812085</v>
+        <v>125812392</v>
       </c>
       <c r="B47" t="n">
-        <v>98373</v>
+        <v>98269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,50 +5769,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>512564</v>
+        <v>512543</v>
       </c>
       <c r="R47" t="n">
-        <v>6732513</v>
+        <v>6732510</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5844,7 +5828,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5854,12 +5838,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5868,7 +5847,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5887,10 +5865,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125812392</v>
+        <v>125812085</v>
       </c>
       <c r="B48" t="n">
-        <v>98269</v>
+        <v>98373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,34 +5876,50 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>512543</v>
+        <v>512564</v>
       </c>
       <c r="R48" t="n">
-        <v>6732510</v>
+        <v>6732513</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5957,7 +5951,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5967,7 +5961,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5976,6 +5975,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5503,7 +5503,7 @@
         <v>125811035</v>
       </c>
       <c r="B45" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>125813662</v>
       </c>
       <c r="B46" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>125812392</v>
       </c>
       <c r="B47" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>125812085</v>
       </c>
       <c r="B48" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5994,42 +5994,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125816687</v>
+        <v>125809649</v>
       </c>
       <c r="B49" t="n">
-        <v>57656</v>
+        <v>98382</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6037,10 +6041,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512426</v>
+        <v>512552</v>
       </c>
       <c r="R49" t="n">
-        <v>6732697</v>
+        <v>6732505</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6072,7 +6076,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6082,7 +6086,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Några i blom</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6091,6 +6100,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6109,46 +6119,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125809649</v>
+        <v>125816687</v>
       </c>
       <c r="B50" t="n">
-        <v>98373</v>
+        <v>57657</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6156,10 +6162,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512552</v>
+        <v>512426</v>
       </c>
       <c r="R50" t="n">
-        <v>6732505</v>
+        <v>6732697</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6191,7 +6197,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6201,12 +6207,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Några i blom</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6215,7 +6216,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6237,7 +6237,7 @@
         <v>125809802</v>
       </c>
       <c r="B51" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>125810285</v>
       </c>
       <c r="B52" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>125810466</v>
       </c>
       <c r="B53" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6590,42 +6590,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125812971</v>
+        <v>125810907</v>
       </c>
       <c r="B54" t="n">
-        <v>57656</v>
+        <v>98382</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6633,10 +6637,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>512539</v>
+        <v>512578</v>
       </c>
       <c r="R54" t="n">
-        <v>6732473</v>
+        <v>6732520</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6668,7 +6672,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6678,7 +6682,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Några i blom och några utan blommor</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6687,6 +6696,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6705,46 +6715,42 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125810907</v>
+        <v>125812971</v>
       </c>
       <c r="B55" t="n">
-        <v>98373</v>
+        <v>57657</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6752,10 +6758,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>512578</v>
+        <v>512539</v>
       </c>
       <c r="R55" t="n">
-        <v>6732520</v>
+        <v>6732473</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6787,7 +6793,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6797,12 +6803,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:33</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Några i blom och några utan blommor</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6811,7 +6812,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>125810185</v>
       </c>
       <c r="B56" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>125809958</v>
       </c>
       <c r="B57" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>125812932</v>
       </c>
       <c r="B58" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>125813330</v>
       </c>
       <c r="B59" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>125810697</v>
       </c>
       <c r="B60" t="n">
-        <v>105372</v>
+        <v>105381</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>125811364</v>
       </c>
       <c r="B61" t="n">
-        <v>105372</v>
+        <v>105381</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>125812445</v>
       </c>
       <c r="B62" t="n">
-        <v>105372</v>
+        <v>105381</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>125805740</v>
       </c>
       <c r="B63" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>125807286</v>
       </c>
       <c r="B64" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>125967830</v>
       </c>
       <c r="B65" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>125973632</v>
       </c>
       <c r="B66" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>125972442</v>
       </c>
       <c r="B67" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>125971458</v>
       </c>
       <c r="B68" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>125968150</v>
       </c>
       <c r="B69" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>125976779</v>
       </c>
       <c r="B70" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>125972943</v>
       </c>
       <c r="B71" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>125970625</v>
       </c>
       <c r="B72" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>125970447</v>
       </c>
       <c r="B73" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>125971792</v>
       </c>
       <c r="B74" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>125969726</v>
       </c>
       <c r="B75" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>125969749</v>
       </c>
       <c r="B76" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>125974109</v>
       </c>
       <c r="B77" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>125971336</v>
       </c>
       <c r="B78" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>125970965</v>
       </c>
       <c r="B79" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>125971419</v>
       </c>
       <c r="B80" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>125968512</v>
       </c>
       <c r="B82" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>125969094</v>
       </c>
       <c r="B83" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>125974426</v>
       </c>
       <c r="B84" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>125971105</v>
       </c>
       <c r="B85" t="n">
-        <v>58513</v>
+        <v>58516</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>125969156</v>
       </c>
       <c r="B86" t="n">
-        <v>58513</v>
+        <v>58516</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5994,46 +5994,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125809649</v>
+        <v>125816687</v>
       </c>
       <c r="B49" t="n">
-        <v>98382</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6041,10 +6037,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512552</v>
+        <v>512426</v>
       </c>
       <c r="R49" t="n">
-        <v>6732505</v>
+        <v>6732697</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6076,7 +6072,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6086,12 +6082,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Några i blom</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6100,7 +6091,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6119,42 +6109,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125816687</v>
+        <v>125809649</v>
       </c>
       <c r="B50" t="n">
-        <v>57657</v>
+        <v>98382</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6162,10 +6156,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512426</v>
+        <v>512552</v>
       </c>
       <c r="R50" t="n">
-        <v>6732697</v>
+        <v>6732505</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6197,7 +6191,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6207,7 +6201,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Några i blom</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6216,6 +6215,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5758,10 +5758,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125812392</v>
+        <v>125812085</v>
       </c>
       <c r="B47" t="n">
-        <v>98278</v>
+        <v>98382</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,34 +5769,50 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>512543</v>
+        <v>512564</v>
       </c>
       <c r="R47" t="n">
-        <v>6732510</v>
+        <v>6732513</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5828,7 +5844,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5838,7 +5854,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,6 +5868,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5865,10 +5887,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125812085</v>
+        <v>125812392</v>
       </c>
       <c r="B48" t="n">
-        <v>98382</v>
+        <v>98278</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5876,50 +5898,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>512564</v>
+        <v>512543</v>
       </c>
       <c r="R48" t="n">
-        <v>6732513</v>
+        <v>6732510</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5951,7 +5957,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5961,12 +5967,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5975,7 +5976,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6590,46 +6590,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125810907</v>
+        <v>125812971</v>
       </c>
       <c r="B54" t="n">
-        <v>98382</v>
+        <v>57657</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6637,10 +6633,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>512578</v>
+        <v>512539</v>
       </c>
       <c r="R54" t="n">
-        <v>6732520</v>
+        <v>6732473</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6672,7 +6668,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6682,12 +6678,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:33</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Några i blom och några utan blommor</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6696,7 +6687,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6715,42 +6705,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125812971</v>
+        <v>125810907</v>
       </c>
       <c r="B55" t="n">
-        <v>57657</v>
+        <v>98382</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6758,10 +6752,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>512539</v>
+        <v>512578</v>
       </c>
       <c r="R55" t="n">
-        <v>6732473</v>
+        <v>6732520</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6793,7 +6787,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6803,7 +6797,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Några i blom och några utan blommor</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6812,6 +6811,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5994,42 +5994,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125816687</v>
+        <v>125809649</v>
       </c>
       <c r="B49" t="n">
-        <v>57657</v>
+        <v>98382</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6037,10 +6041,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512426</v>
+        <v>512552</v>
       </c>
       <c r="R49" t="n">
-        <v>6732697</v>
+        <v>6732505</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6072,7 +6076,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6082,7 +6086,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Några i blom</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6091,6 +6100,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6109,46 +6119,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125809649</v>
+        <v>125816687</v>
       </c>
       <c r="B50" t="n">
-        <v>98382</v>
+        <v>57657</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6156,10 +6162,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512552</v>
+        <v>512426</v>
       </c>
       <c r="R50" t="n">
-        <v>6732505</v>
+        <v>6732697</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6191,7 +6197,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6201,12 +6207,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Några i blom</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6215,7 +6216,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -8761,37 +8761,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125970625</v>
+        <v>125970447</v>
       </c>
       <c r="B72" t="n">
-        <v>98382</v>
+        <v>98361</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Däremot fanns inga blomstänglar just här.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8890,37 +8890,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125970447</v>
+        <v>125970625</v>
       </c>
       <c r="B73" t="n">
-        <v>98361</v>
+        <v>98382</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Däremot fanns inga blomstänglar just här.</t>
+          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -5758,10 +5758,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125812085</v>
+        <v>125812392</v>
       </c>
       <c r="B47" t="n">
-        <v>98382</v>
+        <v>98278</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,50 +5769,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>512564</v>
+        <v>512543</v>
       </c>
       <c r="R47" t="n">
-        <v>6732513</v>
+        <v>6732510</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5844,7 +5828,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5854,12 +5838,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5868,7 +5847,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5887,10 +5865,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125812392</v>
+        <v>125812085</v>
       </c>
       <c r="B48" t="n">
-        <v>98278</v>
+        <v>98382</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,34 +5876,50 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>512543</v>
+        <v>512564</v>
       </c>
       <c r="R48" t="n">
-        <v>6732510</v>
+        <v>6732513</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5957,7 +5951,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5967,7 +5961,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Så små och så sköra. De kan aldrig överleva en avverkning och inte marken de växter i heller. Det finns en hel del blad men alla plantor blommar inte.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5976,6 +5975,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5994,46 +5994,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125809649</v>
+        <v>125816687</v>
       </c>
       <c r="B49" t="n">
-        <v>98382</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6041,10 +6037,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512552</v>
+        <v>512426</v>
       </c>
       <c r="R49" t="n">
-        <v>6732505</v>
+        <v>6732697</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6076,7 +6072,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6086,12 +6082,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Några i blom</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6100,7 +6091,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6119,42 +6109,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125816687</v>
+        <v>125809649</v>
       </c>
       <c r="B50" t="n">
-        <v>57657</v>
+        <v>98382</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6162,10 +6156,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512426</v>
+        <v>512552</v>
       </c>
       <c r="R50" t="n">
-        <v>6732697</v>
+        <v>6732505</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6197,7 +6191,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6207,7 +6201,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Några i blom</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6216,6 +6215,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -8761,37 +8761,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125970447</v>
+        <v>125970625</v>
       </c>
       <c r="B72" t="n">
-        <v>98361</v>
+        <v>98382</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Däremot fanns inga blomstänglar just här.</t>
+          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8890,37 +8890,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125970625</v>
+        <v>125970447</v>
       </c>
       <c r="B73" t="n">
-        <v>98382</v>
+        <v>98361</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Däremot fanns inga blomstänglar just här.</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -8761,37 +8761,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125970625</v>
+        <v>125970447</v>
       </c>
       <c r="B72" t="n">
-        <v>98382</v>
+        <v>98361</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
+          <t>Däremot fanns inga blomstänglar just här.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8890,37 +8890,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125970447</v>
+        <v>125970625</v>
       </c>
       <c r="B73" t="n">
-        <v>98361</v>
+        <v>98382</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Däremot fanns inga blomstänglar just här.</t>
+          <t>Jag hade redan registrerat 100 när jag såg att de var flera. Uppskattat antal, jag kunde inte registrera alla. Det är omöjjligt att räkna alla pyttesmå spindelblomster. Man måste komma nära dem för att se dem och det avverkningsanmälda området är på 3,8 hektar, kontinuitetsskog/fäbodskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -10563,7 +10563,7 @@
         <v>126586715</v>
       </c>
       <c r="B87" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>127085227</v>
       </c>
       <c r="B90" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -10563,7 +10563,7 @@
         <v>126586715</v>
       </c>
       <c r="B87" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>127085227</v>
       </c>
       <c r="B90" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -10563,7 +10563,7 @@
         <v>126586715</v>
       </c>
       <c r="B87" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>127085227</v>
       </c>
       <c r="B90" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -10800,7 +10800,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -10917,7 +10917,7 @@
         <v>127085227</v>
       </c>
       <c r="B90" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -10917,7 +10917,7 @@
         <v>127085227</v>
       </c>
       <c r="B90" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AY92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11009,6 +11009,205 @@
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>127784955</v>
+      </c>
+      <c r="B91" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Hackmorkull, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>512565</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6732458</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>127784976</v>
+      </c>
+      <c r="B92" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Hackmorkull, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>512517</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6732569</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -10917,7 +10917,7 @@
         <v>127085227</v>
       </c>
       <c r="B90" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>127784976</v>
       </c>
       <c r="B92" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -10917,7 +10917,7 @@
         <v>127085227</v>
       </c>
       <c r="B90" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>127784976</v>
       </c>
       <c r="B92" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -11116,7 +11116,7 @@
         <v>127784976</v>
       </c>
       <c r="B92" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -11116,7 +11116,7 @@
         <v>127784976</v>
       </c>
       <c r="B92" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -11116,7 +11116,7 @@
         <v>127784976</v>
       </c>
       <c r="B92" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -11116,7 +11116,7 @@
         <v>127784976</v>
       </c>
       <c r="B92" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -11116,7 +11116,7 @@
         <v>127784976</v>
       </c>
       <c r="B92" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -11116,7 +11116,7 @@
         <v>127784976</v>
       </c>
       <c r="B92" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 61884-2023 artfynd.xlsx
+++ b/artfynd/A 61884-2023 artfynd.xlsx
@@ -10563,7 +10563,7 @@
         <v>126586715</v>
       </c>
       <c r="B87" t="n">
-        <v>97321</v>
+        <v>97314</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10917,7 +10917,7 @@
         <v>127085227</v>
       </c>
       <c r="B90" t="n">
-        <v>97336</v>
+        <v>97314</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
